--- a/reports/claims_context_naive/report.xlsx
+++ b/reports/claims_context_naive/report.xlsx
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0cc55-d398-7ee1-853f-bb3ded91fe9d</t>
+    <t>01a0ccdf-7609-7111-b51a-e5ab87820286</t>
   </si>
   <si>
     <t>Recording</t>
@@ -183,7 +183,7 @@
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-23T03:35:56.284466Z</t>
+    <t>2026-09-23T06:06:28.037095Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,7 +306,7 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0cc55-d3a7-7840-99b2-d6f17deec8e0</t>
+    <t>01a0ccdf-7610-7ac0-86ac-13afb13ef1ea</t>
   </si>
   <si>
     <t>Fresh input</t>
@@ -357,8 +357,8 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"id": "rs_0b0e12b38e322acb006ab3492e1b2487d283b8735b627d6346", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs0ku_Sot4sbIvlDb4goMxWtSPajz9sTBphE5NOnhfKXFEX2t-5DoUP2xwWaUwr7R7PRE_77PmmyuXm9AD684-z1gsLd7ZOZS_M7xGO7wfbCQXUrq7SKqGXxSHftQjZYlnVQMAOB0o8ICfqtm9A4bhp2QaCDODeY-a2AFWEnDT0iYPKofKMgnKzarsLgR69sigXKlBPARcIi4wQo_7oNk1QAFGHCfsolkGQ8tT_8N7MkLLLsAjBKQYRQ__S5emuHYKMV4XJjcVsHnGfecwgnPYGLFswB99hkVUq5to3pSc7jcAoXI91f4Nk4CB7ibcaTgymhW2lr9UvAbLzg9LT_0eRJE4js55prKoEs-QdcGeesNW_UZFqbitimspFMb38S49PIJRjaWrCI0RFcs29wj5aMABHGh_y3EGQMASyNIvwcOGFac3DNMe3TpSPmAUkT2AOnw40zz94GA1gbyr9k5RgD7ZidMa8DLzu6z9mnRdcehV5Cdw9XOep4T6bIg1Yz6yTkhGczQQlrJncPoBW-66xfNzx0T04QFWNEv5UZJvKly48LKONcM9NYo0LBIxKR2CkyeCj4lIhsmg-PvXy4eH8Yndqj0fhIhJmt-XEENnYp4kZvdCqe9j9Ip3yt-HXfaEliNoNuEhsjaDj31DH1ckI6q5KvgJQjBLwr5UAoGfRpRmj7TgGtGtNe-o60L7OoocyLJp7OOgfdct4wewDhcd6A0zD8dXGMSP2TYj6awDMjXKxIb5yT7sse9ZJH_ooOuYCefqRvp6dXWC-V6gwbdswsUU7l1OPQPMWWZNIYubNbIAPklvvG0z6PKWt6XW3VdHiXWnNkRbwngIR5BIq6wZXmXelSqGz0Nibo6O5i0bu46LH67wFNoz-UqEHV7f_REn8xNmnUI0sghpjAuJsNbSYtg78MMHFgm_J-YP287vsu1Z9KhCWBrzF1hXNdw0lOI2lvVtJXJzDJp0mweNIX_U4RQDcFBTyiO0mkYopfjHSiF3ClMSUeiWZ18sA2LHOpzx-B7dByKiVPWADQCnalbL2zQqq8SyKdt0Lg8rxMRbGHRVdFTTgoDywjcnsAeAIDiiWgqm8blRlue3Ibf3YRKJ-bdoFgcnsZM6H-MwMY56tCo3X41qqxp7U6oOIM4gLvQkZSVYLe1rUkWcqdjFZwb829wMtdYl7UuAUg3yOCdFnXoCz-gUKtAWPmFeLorB6IMRlDB"}, {"type": "function_call", "name": "read_policy", "arguments": "{}", "call_id": "call_qCRt1E7Ex73tDSzUAmvkTGss", "id": "fc_0b0e12b38e322acb006ab3492e4aa487d29e659442200f69ee", "index": 1}]
-{"name": "read_policy", "args": {}, "id": "call_qCRt1E7Ex73tDSzUAmvkTGss", "type": "tool_call"}</t>
+    <t>[{"id": "rs_07082eedd1e30c17006ab36c68b76087d29961850299d4f9d4", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2xoffosbRDf0m7ulqGUqYxG6SnyCagkJ2NAaWKSYLdG8pavxidSsTNwJmZS6zyDd6ScNM_WjA0JQ7BDRASuRXyCv8-urV2l6PrPW6rcSUzQaj6cUHpXLqX5MNYlARpAzxvyfZYdTnVqkQoogcNoi5YvEQusE-i_Jd3adLlLDrJKpepgnYNp0CA_W2L6YvRqyEQbWwA42gjzCpnaWpB_f6tevAnQbndYT62MGY7Td1tecew2ApdyN37dkcRScO3Xs65egz_T8M4qokrMBuoKkoNudjiYrlUiMvnzjGPMr3tz0zHaYeG2XDmMXUfBzbXASTLgOymE501Cj21UiZXCadeFEdeFc2f3nJdm7a0CoEtFkxil0j-XDX5ZD757TweTqJV-XLKwk6rNXpKs6k6ulTV7zqi12a7_jWD1wOPyREW9NABJDdbA3U8i2AqAPj8Mn9Toidyd4K_bHXlJg2FOBvU3EMUK6njLpCiOONhOgJmmYCDGt5pJptO4LBfnrkgQsIygYkDktruVX68GbLGDHD36FgIGHXz_oIR_-eSc73ge6UubDsoM4lvQ16GXp65GZpewSSX2K0vnBkuWpsQ9atZrt8uXvpbTQLYBfsnsUJFL5bOMgOT_5YKYrxJ2k8PTyDwvcvyOErDf5M38n631ubEu8rqd7yMf9Y8OJXsAsNLBODE23t-bIsgUb79-OlRAdfEiWh8B5WThyIyhRZzZCMYvnXMMYHtENUrs27HZf9gB36XhZoYz5aLfS4SWrtvLfOT2qUpCrkXqlT5ckyHTigkSOuZ5hIux_UHJTSfCz975nHquUAIuLx9O39CePA8ZPvxp9NkR26nyFw5-4BTt36AZxQzjpP0dgi5MD6Am7ISDGCV41zSKP66U7LTrOepIADBdGCjbFlWkGwFs4Ryc10B-TFa59dKDBy01du3yVQd9jDvnPNvHfNP6EufkGVOzVgpsdKKNsQuVyxh64mUUjENKk8LKq_QDKfIbQFZupHBD_bnp4baxrEJajiShycbrEf-gPrlkLVlQUAZewzwSgPTAC_bwQGu0HpH5imPq-iPYt4mxvAYOwfl1JWRO0mqlzIS3aWbJ9Xs7ZNBo_q3T-nK99wXD5nFUfPvmiIjaLb6MbmT5F25nRDA3LfcaCydWq18dD9zu1LMpomCXSkUPY--DCHJ-zXW7la7DVr5ngGOP3JJpQB1CTrmAu3kg6qDoVUEh"}, {"type": "function_call", "name": "read_policy", "arguments": "{}", "call_id": "call_EW0yGEbP2dxeEvdB0tLw6Jvs", "id": "fc_07082eedd1e30c17006ab36c68e09887d28527d381f0e8516d", "index": 1}]
+{"name": "read_policy", "args": {}, "id": "call_EW0yGEbP2dxeEvdB0tLw6Jvs", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -370,7 +370,7 @@
     <t>Tool · read_policy</t>
   </si>
   <si>
-    <t>01a0cc55-dde8-70c1-9652-d251f8bb5e99</t>
+    <t>01a0ccdf-7aef-7471-b42c-60631ed28818</t>
   </si>
   <si>
     <t xml:space="preserve">    Arguments</t>
@@ -388,7 +388,7 @@
     <t>R2</t>
   </si>
   <si>
-    <t>01a0cc55-ddea-7e80-9df0-a2ffe3c0aa52</t>
+    <t>01a0ccdf-7af7-7831-bfdb-d66da962ffa8</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
@@ -397,7 +397,7 @@
     <t xml:space="preserve">    Tool result</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "Policy POL-001 applies a **CAD 150 deductible** to accidental laptop damage.", "phase": "final_answer", "index": 0, "id": "msg_0b0e12b38e322acb006ab3492fc7f487d2800d38e571d6e3f2"}]</t>
+    <t>[{"type": "text", "text": "Policy POL-001 applies a **CAD 150 deductible** to accidental laptop damage.", "phase": "final_answer", "index": 0, "id": "msg_07082eedd1e30c17006ab36c69af0c87d2a820c59cd0288953"}]</t>
   </si>
   <si>
     <t>Turn 2</t>
@@ -406,20 +406,20 @@
     <t>R3</t>
   </si>
   <si>
-    <t>01a0cc55-e472-7741-b39d-cec7db2c31da</t>
+    <t>01a0ccdf-7e2d-7ec0-be52-f672b489bf5d</t>
   </si>
   <si>
     <t>What happened in claim CLM-001, and what is its status?</t>
   </si>
   <si>
-    <t>[{"id": "rs_0b0e12b38e322acb006ab349312f7487d28edde6227717fad9", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs0kxLFiZOsn0gKyTB3hQUzfFqJ03L4PsF4dr6M5ynPO10KLpcw8GpCVtp7__Cnv3zhaggp6lV4ElZJS9POrwT-YuRmfYIekANI0W9xFUyA9KMaJK-8iaH0Zmbr8HBcp2xZyKFoNAM8gJywxd5IM6hQyqieAZqzrtpQNYrgqrq_yd7U7EyYIbHQ2LVuLeb1HDjVJp6Rfsp7ZUcEnIIFXxUkycJkRyFF6hCw_ZrKRbHXrHtTpmNgLb6D9-n1psU2rFAfEW7EEyEKy1_TUWqRzXn92QdP74p8Nsmeu5ROtSyxKe9e9gnZmUUASWJsjf-_LlI0hRHv99DkW32qFR1T4JVMIfvM6GAq0-DKqrYqSLSbQHmFxk97JQGolb4SjncWt26BFbS1HdXGumlT-xTaw4MhfnrsdfPzCVbKcqEIK5y3TSLFaZYWnnb460HGVrYZsGI363bPOVZrlePpxxayKUFGcgs8oLZ39tL9DpNlPPhPHU8NfRp0SYU-qeVLFacWWnmEj9HeIQaIvjWR-fKOT4i7PdsdSVOzvd45oi8j6Y7qeJy_0AbL1edD3OLm6jP4w0eTB3KrNpib3Ll4LqKVT1Q3nQILgQht2kq1IeXEPLtTci929qOTq2K0CzRgBzqm6NSDAEMH7Pi08PZnnQAT9vdzulqAG_pSBv9Kjpiosjzrmh2-6_NWx6wCNEdkDnuqBfzypKqq1h5kWsjNUhA8LCbDE4wAVhJJngAWcMByDW-pSSG2egmvHe9l9jhJ4Rh0Ffd60Qq0j6Y8QdMaxmgk-ziRXe6BexF4IDWxa4_EW4Qz_AVZz4cRk-sNqPkIC53xO-vDA8v-NFNeynGEhJVJUKPu0ZREUemYBX8zdt00HpGn5zgJMxA2QI5hWKvOz9umZ7_KFGy65dipMDmr4BjfRXdUmEeyP1RY3sWhbiKhHzxwvpPupRkj0flNJvFY91f4vwxgsMwBNKyDbgqipkwLLmnstWH1NRaIaOIzbX_FjDnRHOZqi9a4XrOOD8BzT_bLi-rF5Kg1enEa9EPBv2IZPq13KGzvGJcE9bR7VREocvKUsucujdmsm8LNiuHkiih1W-gmRWwRRHa-uEx0NgH1nV8SemF7XbGc2Uf1obLW0TjxSArXgW_x2dStGqC9vJ8bTqrf2I8FeDhSEWodV8vcFACSsjyMyZpx8R9W6wOYlPpuivIwYtsB5XTHPJvODa3hpSZKWX"}, {"type": "function_call", "name": "read_claim", "arguments": "{}", "call_id": "call_VTnXjtLejlirNuyzaakOgcZP", "id": "fc_0b0e12b38e322acb006ab349314ce087d2b4531812272310fd", "index": 1}]
-{"name": "read_claim", "args": {}, "id": "call_VTnXjtLejlirNuyzaakOgcZP", "type": "tool_call"}</t>
+    <t>[{"id": "rs_07082eedd1e30c17006ab36c6a91e487d291b0070519dfeb29", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2xqshp4iPvmBWxI90sWbo8z5NLcaqpqaKOnv4jPrKjvw-flhsPPBIunv0eFeyXmhVioIFQogny9Zl63Ds_Q4iUhHut8X5RWnYD6W-JxSAYNTJ-GWinZPcnDUsvnIpCEszVA1DOLjXwuXGhqE2_4KhcUwDuBEltkKyHnF03mU8yZybVri0HHh7khCSDC26YhVux_vfvB8eOR1_GpdbqayP_EYogEICSGNHMBbx4Lmxe9pkSf51RA6ehc9eOsiyc5KqDtCNgiOpMWlN5Zd5_X9LsTzpS2DtU3z375d1r0anHlxeokobBqQ1nSCGdq-INg5Nk4cdt7ldxiZCIrVZt2BaBxyz-lTWphsvTZ1910mUQEkunkmhQ8jPWfKQm_r4ObZUQ5ACh6iUyamldP6jm1T-6vAe7fpAPFFu3jbMjgRicT5a43aET3UJGkmGxqvzOYsPScvCOs7NgOjHiJJkxviGmeQn32pyfa-5P2YnbEMntuzv05WVfcPNJBSR3cp0gm4DKmrj_xJ6xm3rRPqGrhzsXStXLZuG9wCLADZm1G7qDXU-s0bQQmkxouSQJzePXLkiOWvO47B4tjoeR3aWMAqNEMrPcxZqOcZjJS4-Z-z4Tg_E8jC6uQ0Jqj9k6LJLNE2_JLqb_79DBWoVIXw6LiaB9CPCCaI_JUKij51E4WyKkIO1QjT82pCVO2LtEjwv5TLxfiaL21Nge-CENYw5-AjGxUk0myDYEv4pJSsbcUWmVldPEA1kaUvxM_jrvF9_abBx3eaubkRpYWl7qz5Qig_ygstMJVJkZ7QOaIV4deRA4QIIElTtRb206eGDFUtjaT-6CKPANJ2jG2jsK2YdQnoef6nkQMLnau9itwKbKmoBd_ExoEmfqRrCWmmlRieM3JdwVoiLFOZTbO4oluKn7UVtPIe-dwwCj54DCnVfqqa0ZOfUX5xiqv1azttcLR-x9o9mN0Db-5Wu7naySJUrd3qUVcXN9AKw2i7b0sfc42Q3DCZvkIjTYXxjqel9K1VFS1ZMXub8WJWaRkgFPuP5NrF_jRx8XbA8nExywQk6z6yQLQjZcDB2TgiAQi7iWf6DRTJVsFDp3CCkjTwKiQR95rftMsfAxVhdKGT217llSrs9lHzXEXOcOQhUlDAlY54Ug6yyMunyLDxtTZmCfFN7hEwL-2DqNaX4oMhTWvPSDoUJ3cXwQoymGj_nX8FgjeHyoGkt79"}, {"type": "function_call", "name": "read_claim", "arguments": "{}", "call_id": "call_1Aw4uAS5H0P7WgtStJvgFw9s", "id": "fc_07082eedd1e30c17006ab36c6ab64087d2ad23691b76c7f9d9", "index": 1}]
+{"name": "read_claim", "args": {}, "id": "call_1Aw4uAS5H0P7WgtStJvgFw9s", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Tool · read_claim</t>
   </si>
   <si>
-    <t>01a0cc55-e98a-7910-8e2f-77dad6a08e34</t>
+    <t>01a0ccdf-81f9-7e70-bb4f-af13695319a4</t>
   </si>
   <si>
     <t>{"claim_id": "CLM-001", "revision": 1, "description": "A laptop was stolen from a parked car.", "status": "pending"}</t>
@@ -428,10 +428,10 @@
     <t>R4</t>
   </si>
   <si>
-    <t>01a0cc55-e98c-72f3-8886-bed0ef9e3beb</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "Claim CLM-001 concerns **a laptop stolen from a parked car**. Its status is **pending**.", "phase": "final_answer", "index": 0, "id": "msg_0b0e12b38e322acb006ab349325c9c87d2aa54fd9914bcb478"}]</t>
+    <t>01a0ccdf-81fb-7210-9785-74cefa828dcd</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "Claim CLM-001 concerns **a laptop stolen from a parked car**. Its status is **pending**.", "phase": "final_answer", "index": 0, "id": "msg_07082eedd1e30c17006ab36c6ba2c087d281aada49443168ed"}]</t>
   </si>
   <si>
     <t>Turn 3</t>
@@ -440,20 +440,20 @@
     <t>R5</t>
   </si>
   <si>
-    <t>01a0cc55-ee56-7692-8815-25cf5c48dc90</t>
+    <t>01a0ccdf-85ca-7942-b006-a77c9cf29b13</t>
   </si>
   <si>
     <t>Correct the claim: the laptop was not stolen. Its screen cracked when it fell from a desk at home. Replace the description with 'The laptop screen cracked when it fell from a desk at home.' and change the status to approved.</t>
   </si>
   <si>
-    <t>[{"id": "rs_0b0e12b38e322acb006ab34934079487d2ab2293bdb30367a9", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs0k0kIYI5mB-hm7Xtse1QssgvNFb9a_OPbbIqkAln37Me8dii0_71HeY65uGwzIbuzzfZjVgTAdtOge4EFJxYjzo6ZeMzDyHF-tDvMyHTkPmr3si4EiiD6B2_PCmzz9ov2qsmSRIcX2hTSTlbUowxGDCfew04Xvc1UMuTs6IKMnoyTTwZsPQKtwQ0LsbTmV92-R2HVqpwEMeUo09oLgwuK8BdTVQKedjkfPFb_N8l-FVRvrVjuDAUen-Bq8AFFmpJfuchpkSQKIK34ZON0g0064arxnWAImRs1VUwhXZDXqacDgN5dggipBgNC9PyrRHHabJAMrnj3ykdAVLLChRGjbG0UrwGCvQMVQ9SCMp2hM1zPCYQTsQ_Zu66JF89Zw4DqdBM-qvVrNQ12ZNSjsDz6HUv1dsAAceksYoLc4CBwd_rwUd-ydgZyzkWPLB3XSt_M-YpJl9N-hCNjAPestJi4iZ9_pzhczURR6O5EwHgGCJyRPzGK8LKCw8wu1e6XDX7Vbh_U7PzfsicupwalKhjsTK9ZPuBJD68YWzhcdP1lly4Xk5fQqBHt4sG2KKDbtJ4JAA2b4VCSySPifz5v6i_K9oxQKLQ5BCEyVSLReQQctWHkg2GIsQfCWdxGtYqEwgmanYTTd2hlPagPakCsWcKrCSoLLtag1PP337Vv9TnB1W0y4hMgYeoODuLn0Im3mIz7rYMmUIsrsRryagsvJGa2hxwMcYS1v6xRLnYxtDoReVLhWY2o_wJWQNvsio-zvXT8iRhBREPo0HlxSpbsbrWcGDsM8XNvJfMrn1WRbqO-CVPIC24tZobuAl0EBekGBaqMVBnzcNhJPNC_S_eV2UIgPxsPmKj7RwLIFWxSWOmReLdL7tFDDA_KWV2LvRLmZ5MoaU_HxndWZriSEJLsqahHFXKI7a29chgiUkIpv04GOqZxGOOmYSptmd5rvz3eBjf6Wf2AmznFWxVHnknfZsLulcZyOMgomxhjAumg5P-lROj_WoFnrFbW2UQDCnBUCS50gm6jwJ6XSlY_hZKj8SzLzeCnGS4oJxxtxoMeGH_8GAsMtr8jYlUlWZwPM1w-cg7c9QD_-FyX20Dpn_NMlHEFXFPmo4eh_KMb7ct2UMxBban3EqHDKnqMXeiyhRX5NxLl-B4loFU8MGSU-lpMUAmK3VYMCQoA3k8BBIV0H6Cb0-rZ4NfEtJlgHcSNHZFF8RPp7hbtRzaiklmMfu4cQuQIQbJIcYavex0JQikKKTq24e0CeX8Tfee9ixEbyvnMklS6HF8xFfuv-3jbfl-aQm8dC6ixuIAyKvlTLKdqtxky1wlZElmGdTLzw16k6hFetGr9zE"}, {"type": "function_call", "name": "edit_claim", "arguments": "{\"expected_revision\":1,\"description\":\"The laptop screen cracked when it fell from a desk at home.\",\"status\":\"approved\"}", "call_id": "call_qRK2jhJuj0sNNer2Gc6Zx8F7", "id": "fc_0b0e12b38e322acb006ab34934683887d289850696f90e8b78", "index": 1}]
-{"name": "edit_claim", "args": {"expected_revision": 1, "description": "The laptop screen cracked when it fell from a desk at home.", "status": "approved"}, "id": "call_qRK2jhJuj0sNNer2Gc6Zx8F7", "type": "tool_call"}</t>
+    <t>[{"id": "rs_07082eedd1e30c17006ab36c6daf3c87d29cf9c38b92688408", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2xtM_EGBKxqbSyXXEC7VkOh7NRjtIDeVuMKKNgkjcgIWexpGwQioMrTk1nx7t_UXHrIfAEkrN6a2v6jmihYg6mHR4qiibxcvh1P8HVbKalBjhZZxCET1AtGjRfHzAn8pwBBU0AoLpIztlF1S6L3me6qeYGRKRLEAhnrfFmYCqnvr-AawV5GuQ3jBDFMINXURcPP5HGMH0QEgkJsoY0_ExTa2cD0Fgmoe879IiiGWGlZECFGnFOea-ySA-kaWibtL9rxC_yUfw8HteVFVrYOuuwI61h3MxiwCye5IvQULX5eGR6HMOOJfwnUNNDNdDbL0sb47UVsIpkG2EJL5icDxqz_6aViNpx-_39TPXouKtEvb-RZxhnqSln71KyOMbUoLcihVftzbdPRMlxXlYqys5UYNxgIK-Slz-37If0g-hHicT2dsYX94Mu_lD8wmdAsN_VquErJxWyWWLWO2lgHzRz5QvYtWpVIZvjZKxXyyfulRdRijd2M1-CDtiyPejfuvReVacpKaEv3dXi0CSUJM-eBw6370BO6aZg9InorLW0AemanLx6vsj1k1Dy0jrBybAgQTYcV0Zfn4b2MsN-feh5kTjE7fMdG4qIRAIftSiGMhjn9UaIlq-Fn8qm1PjBWrJ6oMtktxVQ44mzM6fnLR9U_R9SfBGMjf4wuD54VrMF8tuJwvF8yf6DAq5AyUAk-wOFRKBWaBf-gt2Lh9P9ey0RNILTSVkciuwvWdFJ0vMjNJKxecIrotLS8mRX0EnvoU6GAK3oa8BT7WSuJe7WmcP4nr6cOlmij45w40rlEhpg15Q-bX_nTi6yC2ULuoVic12KKQq9kw9mWphjhMCTttJWFdNiApkd8gXoGILNhggVSolyUGAylPg04a5_eI_j65ObTvCdE5O4_Fw7OY6ixSYasZ4G-1siIC1e_8kzZMC0OVteo1L3Dzm2fzieAutdqApmJv-Swk9wQlO0LYRNMgrGjwVMExT_vKV_HE6tg56R-HqVEOqVKtQGVtehJf4S6TxYXUHkA0ND5jyOrs4RN6bIYtinnkD8v48aDo_EO2v3EMPlIvWFPcMpdaXmzrZ1mVYekaLhb9mvlVxOq4LwW3Dh5Dm8PHL9TtzpgNp_b10r9gGxeucXQWoDtRmrw7W8oGqOSwW_nEi5WhEtdCprh5mfI6IwB6woBDFgCL7EWWvjqZdnApG590wgsizMu6Tcn_P9xcGvW7TlxXfqVRK7qg20YpdbCzONgwPjfgIGzDtOgU13VMbycMiZhqw3kzFhE5G28"}, {"type": "function_call", "name": "edit_claim", "arguments": "{\"expected_revision\":1,\"description\":\"The laptop screen cracked when it fell from a desk at home.\",\"status\":\"approved\"}", "call_id": "call_JZtZ6TaRffjmWnigmaIrd5wp", "id": "fc_07082eedd1e30c17006ab36c6df64487d2b8538dcf1a463412", "index": 1}]
+{"name": "edit_claim", "args": {"expected_revision": 1, "description": "The laptop screen cracked when it fell from a desk at home.", "status": "approved"}, "id": "call_JZtZ6TaRffjmWnigmaIrd5wp", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Tool · edit_claim</t>
   </si>
   <si>
-    <t>01a0cc55-f5ed-7d82-a951-26bc61eb52cf</t>
+    <t>01a0ccdf-91fc-7641-a5ba-b3efeea24ac0</t>
   </si>
   <si>
     <t>{'expected_revision': 1, 'description': 'The laptop screen cracked when it fell from a desk at home.', 'status': 'approved'}</t>
@@ -465,10 +465,10 @@
     <t>R6</t>
   </si>
   <si>
-    <t>01a0cc55-f5ef-7433-9a66-b898a35b46fc</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "Claim CLM-001 was updated:\n\n- **Description:** The laptop screen cracked when it fell from a desk at home.\n- **Status:** Approved", "phase": "final_answer", "index": 0, "id": "msg_0b0e12b38e322acb006ab34935ef3087d2a5725a976dd35a4c"}]</t>
+    <t>01a0ccdf-9200-7122-adb3-21537727f466</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "Claim CLM-001 was corrected: **\u201cThe laptop screen cracked when it fell from a desk at home.\u201d**  \nStatus: **approved**.", "phase": "final_answer", "index": 0, "id": "msg_07082eedd1e30c17006ab36c705a8087d288394620700d45fb"}]</t>
   </si>
   <si>
     <t>Turn 4</t>
@@ -477,13 +477,13 @@
     <t>R7</t>
   </si>
   <si>
-    <t>01a0cc55-fc3a-7d21-b5ae-36e823d574f9</t>
+    <t>01a0ccdf-9a1f-75a3-b72d-785facf51d68</t>
   </si>
   <si>
     <t>What is the policy's coverage limit?</t>
   </si>
   <si>
-    <t>[{"id": "rs_0b0e12b38e322acb006ab34936d45c87d2bed420b9c34978c7", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs0k37czbfK-CtNDcODm2gxkwzKtcUPC2N9p3jL2Xp3JhkbfKfwsfw9RdqX8NJ2dMYDXqWRGoBK6WfZuR6zjmreBOSpo_xDF2p7BE0mLvwurqMs_bVY58g8pYcmZOPs5GgY0kVIefh-ZB7VolkNe8u9fJhThMyl8jnHC02uU1S5X2sXKNoMp_4BD9yTxZF3z0a9cU0UCBIPvuVKttzPpJ1TsdzhiGRH513JGc2VchCSVqgnR54FHzpyIm7hN8XK9B4SfHqqBST5Sg5UMOGRZBNaWQt-xBmRfDIXsn_7H02SyOuTSGb2DYXeHufo7FkuSO73aKOuoBQpzhd6pWCJ3xEakoh84UHa_7QeJ6vCFcQDidaVmu4aedMoZd7OHLyXOJ11b0HVz-rCLm1n___hqeRx5ZS0amSpM3YEoO-S8-p3xis9eyg1aQxWi1MJB9TjmAPP1gUPDEu7xflhfaMhFoMQie2sIl40QWvVs5GWPGQwTVjxS0LUhd5bn3hUx4Uqfj-iLbJSpeFOadbALSvX5cBBV7ZWRK1Nar9f-HW2BDRB385FIfai5MFg19KrOJRq6HnjUZycMoZFDynUBbbfrnOo5hffTuEt_Cku3E_WBmROtlx_sYPgJB0e_idYbmBMXAmQzqtHuUK8WFjZwMztwVh12mI0VXxCgOysQ1yR8VnvyB9q6LDmxfIIH5jiJCGn8T0kL9WnyBjY3CtUGkmkfqwWQXOLFBD7y07n3O25fWaK-jnIuL_5FNpCUhby2MCnCSkUrCWt3ugEoVlPVaAuFmBWUxtgIWAEJ3xfQDyCoWyCf2VuDwotNrJmePFo2eVtz_ZwcqXYxQFDTZ7TZw9juOhnmJNPxzz5WDERRRf5U1JaPBvQUHu70SctyyBxadW_lcbxLohC0oyiVhsMpZSia26_dY372fGsH4Y1Xr0YXObepXNLc44nTxcqwJD_LPgTWxSMISdspS39WKq2kQZAXPxXD7oOQi2xom4HOdLPZ-OSl8bbmAGXMOmPh0tH3SKZdXX8b0H39D_WT4Kqxrd-UY31DmWojAPLU5MubT2ZdLRYzY7PJVc1iHDEC2ZN_-H9Cw2fAe-2fg03vsdrlQ9E9CkEMZDU72-4wT8WoKV9_mhL7ULhrZp0XIAU776l3941mvm9_LKq5AU75Mruzzow_6yqN-ObdAEPz1AOTGZRmFiSLwM5lp6ZkCpBj0CbuYmoy4RLqaclQacwfpclYfQ7uUJ6n8TgvN_gilWAF0m6-SDQcMhLZYlYu-uplOrDNYYwYoyEbB"}, {"type": "text", "text": "Policy POL-001 has a **CAD 2,000 coverage limit**.", "phase": "final_answer", "index": 1, "id": "msg_0b0e12b38e322acb006ab3493704b087d294ccd07ed10389ed"}]</t>
+    <t>[{"id": "rs_07082eedd1e30c17006ab36c71f76487d283078a5f4805493c", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2xyTX-aa7sMklQD50gAQz6y-sXfxPpK8tg2vn9Cz1uGWSqPdl6y-Q53rPV3KiyjWkS7he2sJrAHRnZTmOoyjYZZTcVXFH5OV8z_RV-x6XyT6IWFnTpdJFqVoGddMJMRZDWxgam5_VSEoeRiJFHm10zHkd7YD_-lMYeMaow-51Bh047_bhJ17ONUqtRbN-FLD5SzBd5IaZBTgFcNNqGbUUcQIDxRgT9Mz2lgr_QjErd_7XU8ev7IF0A2y_rOln8w4aVSUwPQxlBRAb9cIqvAz0PhsOCmijNLg8N-ugYgnzYsiWjkH9L4ZBRC46TS_UN6tBvY2G03NtGIaxSL5kQQHjlthHHAQRwjedTbLqt0B0JW3NbbVZQ5mbzTSoew1OhKcNXtTyflKLquL4ga-7jC32kj37EqR85jXf8B9O3AdVNG3ym3XciFTiIvqZnQW-m_yot9tGFt8K6NqD2I0nfIc9YCkHybI7rikBZerZfInNAoW-0LF-AuqWjsy0EmVt0nLgR-FskvQi_hfUfMpet7NJVVkavsUzR30-MiY-Ts3rxEbowcJewslrK0OMwxKiXbOh6MAzkzLoYg7vnhNLAIILgTcfz1Mf8hTT7cojhMRf7krCdNZpiAQ_HZ76xZxg5wnGOZqaAAjLnDJ3iHt-q8cot7y75c0I3gQhgPe1CrT1uyQp0Tro_MK3fS4jlp7zyXUW7azANUbJ2i0yihxrGtdVxWJdijV8ZtZNO1D_l5iMiDH7DK3QQqFO96VOcW9dRxFc4uukUrEkGxX7Tim4IifuukrA6b6juG1qlP6acZqOanbcKzQPoy19bLkZbPcpnoUg8uHomXNMW47vNQGgc5pzbsWr5-lMPQpZMuclAh4F-bV5lkKTBJ4XRWj9v9NuufNifIf8tlzVy_UtNLPqGuF4eOM6rCR_zOAOdAX8KrMZ2ANIsx4VxuVmxDT-JmgRyt6YnSrIeH-w9lpZxJCVvsGtvSg3Wb7sYSLCuohDazDPvCN-fliiVvmbU_rIBl6UAXqAg1T6LfuuXQEcAOA4kGnxz6fS0qp4q1lewLoEvpIwLXbM-Mzi3B_Nkl5g9aRLlNDhrCq6vuAJkv2HYHOEQqvS7mzuDYNOvjnRDDKxOg-9QDpXZ5VRfknWtNXrfYN2n0-SZO4swytx-4qeP8AA1r8jNfhcmjwpOUJ3r3X9UtwdlNxJhIPOG3bcoGlVDFCAm2zOhkmLFu6aMXPJAa5o8RQuz4HCVzINMfhl_3aa8CpUa3CRatJsC2vn9oqLA8uWkxj9fX"}, {"type": "text", "text": "Policy POL-001\u2019s coverage limit is **CAD 2,000**.", "phase": "final_answer", "index": 1, "id": "msg_07082eedd1e30c17006ab36c722e8c87d2829b6dfb1daaa6f4"}]</t>
   </si>
   <si>
     <t>Turn 5</t>
@@ -492,13 +492,13 @@
     <t>R8</t>
   </si>
   <si>
-    <t>01a0cc56-0002-7000-9342-9277e47ca1a4</t>
+    <t>01a0ccdf-9fd9-72f2-9693-da133696e5bc</t>
   </si>
   <si>
     <t>What happened to the laptop, where did it happen, and what is the current claim status?</t>
   </si>
   <si>
-    <t>[{"id": "rs_0b0e12b38e322acb006ab34937cf8087d2a3fee0a217ce7614", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs0k4nSsqPiWbrrN8OUPvsd06b719uiFYi8-gdZh_iBLLYR1a-KlKn-oVhS_MN1sDNlfEpnhuAARC6FAZXlVluU5N_CpDBu-jTQ6J6E1pwzyDp7466bDT5Qk_55KSm6ow5azaab6oC27ZFkygv9b_TGgRHy3366T4jZjyTf7j10ZWesqyxo23gCwlOgYwyhAFVMhNP9BUaJl9ovBXQjB09vS86yJvLEZnGEwd1TueCohU0P2StVn-yBlWJVXxDhjzj2RW3BVm9hhz80ncGvP2dE6pgHCrOuVkDtFg7gyxbwzbZAQsQin7L7Jpa0H4DxFBa2vZyIHj0FQXDyxHyK5RTmq_I6KwxdTHLeT-4OygF7w-YjgTVW15RE2rQEPc9QGOOlEi6FLZtl02w53Iko3igcZ-XF0qQpiLE7Nol4a_HvuarFBwhhUwoXnMCyecvlNWvG59wauyKYgoy8Py-bNA2UnrL_hclwhUF6A80cgdr0fyA6Ap7tCGt2wrEDQd70bA-KKO7ZYNjPnoh_5ks51uYbQLtB_uUHZbZVjxL_psYJiQ-TSkbzNIamKvNEpqQYI9hZqGO2_D-5BR6nILxEDZ_t-GNJjLabP4m3sZ8BXaWXB2LXqDnD5JnO3kRFKXZ21AP4b1Femq7auf2kYUE3L1yV-87Y5pbUubRq4QezoQ1NmxJDxYCUEC1GnGGSSOefTen0gKkUqCnW30THg9ZqlQyOTpIBfBTZB3xORWdeZIoulNhymW0QWGVKzFQB1JH4RDVtCsj8ObpI-in82psNlioKHU1y3A4m5qx6V3zA29Gzqia-rWgvWIumliJQfHHh8WAUaX2RFSpPafw_J_oL6n8r-JlKVx9Vu9eIv7bDjQ-NZ9mIv5FZqniqn4SJ72QmX4j6QDUIEwGsP4v1a7PHTMIOXgBZHfLvcYViu-sTJJfZTxF3M_5oxsXac1HJTDSaHNtvriOt8xvb6Qc2xwIuQBWWSEAxref8vH-ekWhYxEyFLWf-pkWxGqinqi8Wq7o3_QAgqvweGQiiAiFOVYcxWmSQFl9DV_MA7Dn-Mw_sIZDjnIHp3bs6K9r3nEnyMMSZqGCVG-3T3m3j8mlMED7Ibs20GEJjBiwXxTBM3A7FLEsp66oGNqZ1w2NCQPI4CkKZmN2ELCZ0RYcZTnSbRbblJENCuWhx_oOvYsi-bWyLBqAr_MUPpJNhWCk1lVGtBFAJX82gY1qceBB8lXlWdix9ne035BDVKeuyQKRNzQM3ZTwnDCf8pVfvd24vg74ODePXxVdzlFqgtSacBNTDEl-IGOML_xefNbq9gTPraNG3ZRlIX8VtEAwBjke0Wx5CkAFU0jOXo4v4LbuJ0NjHkEWrLZyMOJWeaY0oQXV8y5i5rFpdHCIOQAoKO2ImmqMh9pgVEczyKI0Rb7rOzpkf1sf8aym7xKqwbGMBxkuHyiaXSPhQLZ75Akfr9vi0Y9I2ajA5L2sBdlbxK40EwFFaER20lPS9e0iFdNCFAVKd_RPeCOkwsQVRq63guNVoOvZa8oiSI-pgefSiKFu7jH3t2M5Id8QkC8mA=="}, {"type": "text", "text": "The laptop screen cracked when it fell from a desk at home. The current claim status is **approved**.", "phase": "final_answer", "index": 1, "id": "msg_0b0e12b38e322acb006ab3493866cc87d2913119e004247570"}]</t>
+    <t>[{"id": "rs_07082eedd1e30c17006ab36c73399087d2a5486ca28bfa4857", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2xzEPedItm8rKfxfWyfxyR3S0e4r78-v99CCD-eRTCPGz8oZnBtSRVgbG_1l6FkB-N4K8z1_pIPbTFA7JB77pvAa7o0SlOgTesuzBzZtboNXM6gFJt76xs9bacNIUkvNFdOQ2rvbiTIIgx2SLXWztAL6f3atNexyyP6892yOal86fHWcYwKcbLPcgU49OS9yHj6dG9RMkXzpzgxsPCPcf3nNnL8s7WGDqT15Bx-xdX7fSVtNCf6e5VuDgoSA-YG0hEg_lor3YE5dZLaghcEAnGqS6nlBxx5MpkcAOT7qdmX2BB7FLsY5aRn5Ld5-FScqJhJfhNtOWuwUNx0wJwWE0XoIdTJXUfGUt8i97n_kDpR-rI7WpBMXIMzpKPMztUJx5bMEQV00QddQpcQVLSCmohmvgJY7MobmfMg60BHRr4EI6QPSOW0kZQBmgYMX4LbIU4YQXya1Lu5rfOzyvffiGvEKTyKqgtC8WYHHtAbtZM99823Qfm1PC6oBTR8fXf8987DXtlei79kNtnt4IsyLX-OwzcCpf8TATZb5Nh5D2eu3dhqNylQaLeTnADZlvX3oHu1efLG8JLNFFygpQIJ2e0CO3g0CPpGfdY4Q02OUoihkwFZCuX-lP7DKi6B9QUqxPSQ4GgcQFy5lEftN2B2SbjSWO6b0CaSprlKBXzChHy3rAkFQaPgu14iQyJ9aq_hxbwEt86-7_W-V8GgJlQh-40mRH93teV2exNfG5JARrotkg7TTS2z6zgfRywWLI6r2BGC1xlAEdXddkjCACTcSP45wrg8USEbxMja-KDhzlk1sgfVD7HaAHtoOpoS6UGBiz7mIvxGUikt1lSRkvRCYrvXLqzUe1mXyqD3BclVvaeMRZL4KNAllPG0EJYcJTd6HCHWIACGZlJuwJNXHu3nBF_ybkEaRbjjiD2mRvtMLPLtNr5p6KU6lf2ZtTPsT-3sXfVN9_q-dlwWPVvKv_K-DtLNBtgknsPYO2wO3_OEKkTgQsr_-A5bmU_Qs1sYdK8tuTaiu7ZLZUShjF2dk2MxF5Ut0gqo6Tdo5wtlPvrdzHRQo4gskzBnMEyJGCrmisk0evET-COpun9Jmx6TGd9oTrFbbMT7fjRf6YtjNpN02yd2Sh8twFDY8XRwbuWUXPUijWbIh5ITArqNe1lO12NU5sTRXl25VV-buAC9oUvUmK8D3ue2fNexCWI7coKx6gRuikPX5oHjTbWMy1lx7GA2OFpv9vce6RL0K2pjAvZMwwMsQ8fIRj7T9Yu46SMG_5TVH70F4MvH0Y89QdRrJH286P6a6iX3AUx7OFWiKTiBfsVNEZAnOQGbDuFsGvK_LT6PvE5RtGFe-c8gy2M0Y7RmlL06ry4d7OrX3bd3RKl47i2VoPetbd8sV0x-JcnXEY4DKfzpksE47CD8cBpbDZErzkOI8GXajE2DP-_SmRkesWlTQ4A5oH80DaUeP5LFDK05fuZ2ZMPxKLjsZJpbzxsc8FHOxw=="}, {"type": "text", "text": "The laptop\u2019s screen cracked when it fell from a desk at home. The current claim status is **approved**.", "phase": "final_answer", "index": 1, "id": "msg_07082eedd1e30c17006ab36c73b1b487d2bb82755d1801cdc4"}]</t>
   </si>
   <si>
     <t>LangGraph</t>
@@ -519,7 +519,7 @@
     <t>Execute the claim_turn workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cc55-d3a1-71a2-b91c-f10f87cd59d4</t>
+    <t>01a0ccdf-760d-77d2-ba3c-2a3ad3f0984b</t>
   </si>
   <si>
     <t xml:space="preserve">        claims_agent</t>
@@ -528,7 +528,7 @@
     <t>Execute the claims_agent workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0cc55-d3a2-7192-a574-5845cb86658f</t>
+    <t>01a0ccdf-760d-77d2-ba3c-2a4f6c885a25</t>
   </si>
   <si>
     <t xml:space="preserve">            model</t>
@@ -537,7 +537,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0cc55-d3a4-73c2-9dad-0d442ee50dfd</t>
+    <t>01a0ccdf-760e-7852-89a8-45b668666213</t>
   </si>
   <si>
     <t xml:space="preserve">                ChatOpenAI</t>
@@ -558,7 +558,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0cc55-dde7-7a13-bdbc-b7977032a028</t>
+    <t>01a0ccdf-7aee-7121-ab6f-b9cd597b28c8</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -573,22 +573,22 @@
     <t>Read fictional policy POL-001, including coverage, deductible, and limit.</t>
   </si>
   <si>
-    <t>01a0cc55-dde9-7860-92ed-af83bb2a3ade</t>
-  </si>
-  <si>
-    <t>01a0cc55-e46e-7403-a061-76823dd0448a</t>
-  </si>
-  <si>
-    <t>01a0cc55-e46f-7543-8098-2660311cd0b9</t>
-  </si>
-  <si>
-    <t>01a0cc55-e470-7c83-a768-df98917795dc</t>
-  </si>
-  <si>
-    <t>01a0cc55-e471-7763-b7ae-6efaf2655b22</t>
-  </si>
-  <si>
-    <t>01a0cc55-e988-7b22-ac6a-bbc9457b07ad</t>
+    <t>01a0ccdf-7af4-7763-940d-545dbd65f092</t>
+  </si>
+  <si>
+    <t>01a0ccdf-7e29-7952-bdcc-47c584c519ad</t>
+  </si>
+  <si>
+    <t>01a0ccdf-7e2b-7563-9c86-4ccd1856cca7</t>
+  </si>
+  <si>
+    <t>01a0ccdf-7e2b-7563-9c86-4cdd14dc2663</t>
+  </si>
+  <si>
+    <t>01a0ccdf-7e2c-75e0-9a3c-06a00149a100</t>
+  </si>
+  <si>
+    <t>01a0ccdf-81f7-7c93-9f06-a765fd98bdb5</t>
   </si>
   <si>
     <t xml:space="preserve">                read_claim</t>
@@ -597,22 +597,22 @@
     <t>Read the complete current claim, including its authoritative revision.</t>
   </si>
   <si>
-    <t>01a0cc55-e98b-7c52-9a10-7690f1475879</t>
-  </si>
-  <si>
-    <t>01a0cc55-ee50-7531-ba3d-8697639e6ab5</t>
-  </si>
-  <si>
-    <t>01a0cc55-ee52-70f0-a6af-6933bc31805e</t>
-  </si>
-  <si>
-    <t>01a0cc55-ee53-75b0-b62f-74a7f287a9b6</t>
-  </si>
-  <si>
-    <t>01a0cc55-ee54-7ab2-9192-869430b7bfa3</t>
-  </si>
-  <si>
-    <t>01a0cc55-f5eb-7640-a0d7-c31fe9d6f3be</t>
+    <t>01a0ccdf-81fa-7ed3-94c1-3e274cf39440</t>
+  </si>
+  <si>
+    <t>01a0ccdf-85c6-7862-baed-301765d112aa</t>
+  </si>
+  <si>
+    <t>01a0ccdf-85c7-7782-abdc-78fd513c3777</t>
+  </si>
+  <si>
+    <t>01a0ccdf-85c7-7782-abdc-790d370859b9</t>
+  </si>
+  <si>
+    <t>01a0ccdf-85c9-7182-aa0c-9dab604376e6</t>
+  </si>
+  <si>
+    <t>01a0ccdf-91fa-7292-931c-5e558e69f89a</t>
   </si>
   <si>
     <t xml:space="preserve">                edit_claim</t>
@@ -624,31 +624,31 @@
             revision, not the resulting claim contents.</t>
   </si>
   <si>
-    <t>01a0cc55-f5ee-7933-af6f-f492598e3514</t>
-  </si>
-  <si>
-    <t>01a0cc55-fc32-7713-9e87-a99da39e0a5f</t>
-  </si>
-  <si>
-    <t>01a0cc55-fc35-79c1-a8a7-b3ae2f01a11c</t>
-  </si>
-  <si>
-    <t>01a0cc55-fc36-7de3-92c3-cd802570a95c</t>
-  </si>
-  <si>
-    <t>01a0cc55-fc39-72e0-8939-f975daf4ef9b</t>
-  </si>
-  <si>
-    <t>01a0cc55-fffe-7702-bb4e-832b0344927b</t>
-  </si>
-  <si>
-    <t>01a0cc55-ffff-7b63-92de-1c59bf849f3e</t>
-  </si>
-  <si>
-    <t>01a0cc56-0000-7ff2-bca1-dec16fe83477</t>
-  </si>
-  <si>
-    <t>01a0cc56-0001-7591-8b4f-5be9f62927ff</t>
+    <t>01a0ccdf-91fe-7a30-89f8-706639ebafe2</t>
+  </si>
+  <si>
+    <t>01a0ccdf-9a1a-7593-b981-9be74d1569ba</t>
+  </si>
+  <si>
+    <t>01a0ccdf-9a1c-7143-860e-a0bd5d609eec</t>
+  </si>
+  <si>
+    <t>01a0ccdf-9a1c-7143-860e-a0c6a467b237</t>
+  </si>
+  <si>
+    <t>01a0ccdf-9a1d-7683-9cd0-332f961394f7</t>
+  </si>
+  <si>
+    <t>01a0ccdf-9fd5-7193-84f2-d72f72501a4b</t>
+  </si>
+  <si>
+    <t>01a0ccdf-9fd7-7050-9ea0-a98df021ab5e</t>
+  </si>
+  <si>
+    <t>01a0ccdf-9fd7-7050-9ea0-a99fe0d9a3fa</t>
+  </si>
+  <si>
+    <t>01a0ccdf-9fd8-7640-9a8c-046a0981b8a9</t>
   </si>
 </sst>
 </file>
@@ -1116,19 +1116,19 @@
       </c>
       <c r="E2" s="2">
         <f>IF(COUNT('Turns'!E17,'Turns'!E32,'Turns'!E46,'Turns'!E61,'Turns'!E75,'Turns'!E90,'Turns'!E104,'Turns'!E118)=8,SUM('Turns'!E17,'Turns'!E32,'Turns'!E46,'Turns'!E61,'Turns'!E75,'Turns'!E90,'Turns'!E104,'Turns'!E118),"Unknown")</f>
-        <v>0.001136174688</v>
+        <v>0.001117331496</v>
       </c>
       <c r="F2" s="2">
         <f>IF(COUNT('Turns'!F17,'Turns'!F32,'Turns'!F46,'Turns'!F61,'Turns'!F75,'Turns'!F90,'Turns'!F104,'Turns'!F118)=8,SUM('Turns'!F17,'Turns'!F32,'Turns'!F46,'Turns'!F61,'Turns'!F75,'Turns'!F90,'Turns'!F104,'Turns'!F118),"Unknown")</f>
-        <v>0.0013024</v>
+        <v>0.0012808</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>114.0</v>
+        <v>112.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>130.0</v>
+        <v>128.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -2219,19 +2219,19 @@
       </c>
       <c r="E62" s="2">
         <f>IF(COUNT('Turns'!E75,'Turns'!E90)=2,SUM('Turns'!E75,'Turns'!E90),"Unknown")</f>
-        <v>0.000331675074</v>
+        <v>0.000321730056</v>
       </c>
       <c r="F62" s="2">
         <f>IF(COUNT('Turns'!F75,'Turns'!F90)=2,SUM('Turns'!F75,'Turns'!F90),"Unknown")</f>
-        <v>0.0003802</v>
+        <v>0.0003688</v>
       </c>
       <c r="G62" s="5">
         <f>IF(ISNUMBER(E62),ROUND(E62*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
       <c r="H62" s="5">
         <f>IF(ISNUMBER(F62),ROUND(F62*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>38.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="63" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -2361,7 +2361,7 @@
         <v>105</v>
       </c>
       <c r="D69" s="4">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="24" customHeight="1">
@@ -2375,23 +2375,23 @@
         <v>106</v>
       </c>
       <c r="D70" s="5">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E70" s="2">
         <f>IF(AND(ISNUMBER(F70),ISNUMBER('Reference data'!$B$3)),F70*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.8264788e-05</v>
+        <v>1.8843192e-05</v>
       </c>
       <c r="F70" s="2">
         <f>IF(D70=0,0,IF(ISNUMBER('Reference data'!F17),D70*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>3.24e-05</v>
+        <v>2.16e-05</v>
       </c>
       <c r="G70" s="5">
         <f>IF(ISNUMBER(E70),ROUND(E70*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H70" s="5">
         <f>IF(ISNUMBER(F70),ROUND(F70*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="24" customHeight="1">
@@ -2424,7 +2424,7 @@
         <v>5.0</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="320" customHeight="1">
+    <row r="72" spans="1:13" ht="307" customHeight="1">
       <c r="A72" t="s">
         <v>135</v>
       </c>
@@ -2472,19 +2472,19 @@
       </c>
       <c r="E75" s="2">
         <f>IF(COUNT('Turns'!E64,'Turns'!E65,'Turns'!E70,'Turns'!E71)=4,SUM('Turns'!E64,'Turns'!E65,'Turns'!E70,'Turns'!E71),"Unknown")</f>
-        <v>0.00017534637</v>
+        <v>0.000165924774</v>
       </c>
       <c r="F75" s="2">
         <f>IF(COUNT('Turns'!F64,'Turns'!F65,'Turns'!F70,'Turns'!F71)=4,SUM('Turns'!F64,'Turns'!F65,'Turns'!F70,'Turns'!F71),"Unknown")</f>
-        <v>0.000201</v>
+        <v>0.0001902</v>
       </c>
       <c r="G75" s="5">
         <f>IF(ISNUMBER(E75),ROUND(E75*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="H75" s="5">
         <f>IF(ISNUMBER(F75),ROUND(F75*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="K75" s="4" t="s">
         <v>111</v>
@@ -2537,7 +2537,7 @@
         <v>94</v>
       </c>
       <c r="D79" s="4">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="J79" s="4" t="s">
         <v>95</v>
@@ -2587,15 +2587,15 @@
         <v>97</v>
       </c>
       <c r="D81" s="5">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="E81" s="2">
         <f>IF(AND(ISNUMBER(F81),ISNUMBER('Reference data'!$B$3)),F81*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000120736008</v>
+        <v>0.000119165742</v>
       </c>
       <c r="F81" s="2">
         <f>IF(D81=0,0,IF(ISNUMBER('Reference data'!B17),D81*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>0.0001384</v>
+        <v>0.0001366</v>
       </c>
       <c r="G81" s="5">
         <f>IF(ISNUMBER(E81),ROUND(E81*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2653,7 +2653,7 @@
         <v>105</v>
       </c>
       <c r="D85" s="4">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="24" customHeight="1">
@@ -2667,15 +2667,15 @@
         <v>107</v>
       </c>
       <c r="D86" s="5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E86" s="2">
         <f>IF(AND(ISNUMBER(F86),ISNUMBER('Reference data'!$B$3)),F86*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.5592696e-05</v>
+        <v>3.663954e-05</v>
       </c>
       <c r="F86" s="2">
         <f>IF(D86=0,0,IF(ISNUMBER('Reference data'!E17),D86*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>4.08e-05</v>
+        <v>4.2e-05</v>
       </c>
       <c r="G86" s="5">
         <f>IF(ISNUMBER(E86),ROUND(E86*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2734,11 +2734,11 @@
       </c>
       <c r="E90" s="2">
         <f>IF(COUNT('Turns'!E80,'Turns'!E81,'Turns'!E86)=3,SUM('Turns'!E80,'Turns'!E81,'Turns'!E86),"Unknown")</f>
-        <v>0.000156328704</v>
+        <v>0.000155805282</v>
       </c>
       <c r="F90" s="2">
         <f>IF(COUNT('Turns'!F80,'Turns'!F81,'Turns'!F86)=3,SUM('Turns'!F80,'Turns'!F81,'Turns'!F86),"Unknown")</f>
-        <v>0.0001792</v>
+        <v>0.0001786</v>
       </c>
       <c r="G90" s="5">
         <f>IF(ISNUMBER(E90),ROUND(E90*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2761,11 +2761,11 @@
       </c>
       <c r="E91" s="2">
         <f>IF(COUNT('Turns'!E104)=1,SUM('Turns'!E104),"Unknown")</f>
-        <v>0.000174125052</v>
+        <v>0.000173776104</v>
       </c>
       <c r="F91" s="2">
         <f>IF(COUNT('Turns'!F104)=1,SUM('Turns'!F104),"Unknown")</f>
-        <v>0.0001996</v>
+        <v>0.0001992</v>
       </c>
       <c r="G91" s="5">
         <f>IF(ISNUMBER(E91),ROUND(E91*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2787,7 +2787,7 @@
         <v>94</v>
       </c>
       <c r="D92" s="4">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="J92" s="4" t="s">
         <v>95</v>
@@ -2837,15 +2837,15 @@
         <v>97</v>
       </c>
       <c r="D94" s="5">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="E94" s="2">
         <f>IF(AND(ISNUMBER(F94),ISNUMBER('Reference data'!$B$3)),F94*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.00012911076</v>
+        <v>0.000127714968</v>
       </c>
       <c r="F94" s="2">
         <f>IF(D94=0,0,IF(ISNUMBER('Reference data'!B17),D94*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>0.000148</v>
+        <v>0.0001464</v>
       </c>
       <c r="G94" s="5">
         <f>IF(ISNUMBER(E94),ROUND(E94*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2903,7 +2903,7 @@
         <v>105</v>
       </c>
       <c r="D98" s="4">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="24" customHeight="1">
@@ -2917,15 +2917,15 @@
         <v>106</v>
       </c>
       <c r="D99" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E99" s="2">
         <f>IF(AND(ISNUMBER(F99),ISNUMBER('Reference data'!$B$3)),F99*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.1983724e-05</v>
+        <v>2.3030568e-05</v>
       </c>
       <c r="F99" s="2">
         <f>IF(D99=0,0,IF(ISNUMBER('Reference data'!F17),D99*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>2.52e-05</v>
+        <v>2.64e-05</v>
       </c>
       <c r="G99" s="5">
         <f>IF(ISNUMBER(E99),ROUND(E99*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3014,11 +3014,11 @@
       </c>
       <c r="E104" s="2">
         <f>IF(COUNT('Turns'!E93,'Turns'!E94,'Turns'!E99,'Turns'!E100)=4,SUM('Turns'!E93,'Turns'!E94,'Turns'!E99,'Turns'!E100),"Unknown")</f>
-        <v>0.000174125052</v>
+        <v>0.000173776104</v>
       </c>
       <c r="F104" s="2">
         <f>IF(COUNT('Turns'!F93,'Turns'!F94,'Turns'!F99,'Turns'!F100)=4,SUM('Turns'!F93,'Turns'!F94,'Turns'!F99,'Turns'!F100),"Unknown")</f>
-        <v>0.0001996</v>
+        <v>0.0001992</v>
       </c>
       <c r="G104" s="5">
         <f>IF(ISNUMBER(E104),ROUND(E104*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3041,19 +3041,19 @@
       </c>
       <c r="E105" s="2">
         <f>IF(COUNT('Turns'!E118)=1,SUM('Turns'!E118),"Unknown")</f>
-        <v>0.000227863044</v>
+        <v>0.000219313818</v>
       </c>
       <c r="F105" s="2">
         <f>IF(COUNT('Turns'!F118)=1,SUM('Turns'!F118),"Unknown")</f>
-        <v>0.0002612</v>
+        <v>0.0002514</v>
       </c>
       <c r="G105" s="5">
         <f>IF(ISNUMBER(E105),ROUND(E105*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="H105" s="5">
         <f>IF(ISNUMBER(F105),ROUND(F105*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="106" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -3067,7 +3067,7 @@
         <v>94</v>
       </c>
       <c r="D106" s="4">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="J106" s="4" t="s">
         <v>95</v>
@@ -3117,15 +3117,15 @@
         <v>97</v>
       </c>
       <c r="D108" s="5">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="E108" s="2">
         <f>IF(AND(ISNUMBER(F108),ISNUMBER('Reference data'!$B$3)),F108*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000140974992</v>
+        <v>0.000139753674</v>
       </c>
       <c r="F108" s="2">
         <f>IF(D108=0,0,IF(ISNUMBER('Reference data'!B17),D108*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>0.0001616</v>
+        <v>0.0001602</v>
       </c>
       <c r="G108" s="5">
         <f>IF(ISNUMBER(E108),ROUND(E108*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3183,7 +3183,7 @@
         <v>105</v>
       </c>
       <c r="D112" s="4">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="24" customHeight="1">
@@ -3197,23 +3197,23 @@
         <v>106</v>
       </c>
       <c r="D113" s="5">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E113" s="2">
         <f>IF(AND(ISNUMBER(F113),ISNUMBER('Reference data'!$B$3)),F113*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.757642e-05</v>
+        <v>4.9201668e-05</v>
       </c>
       <c r="F113" s="2">
         <f>IF(D113=0,0,IF(ISNUMBER('Reference data'!F17),D113*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>6.6e-05</v>
+        <v>5.64e-05</v>
       </c>
       <c r="G113" s="5">
         <f>IF(ISNUMBER(E113),ROUND(E113*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="H113" s="5">
         <f>IF(ISNUMBER(F113),ROUND(F113*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="24" customHeight="1">
@@ -3227,15 +3227,15 @@
         <v>107</v>
       </c>
       <c r="D114" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E114" s="2">
         <f>IF(AND(ISNUMBER(F114),ISNUMBER('Reference data'!$B$3)),F114*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.9311632e-05</v>
+        <v>3.0358476e-05</v>
       </c>
       <c r="F114" s="2">
         <f>IF(D114=0,0,IF(ISNUMBER('Reference data'!E17),D114*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>3.36e-05</v>
+        <v>3.48e-05</v>
       </c>
       <c r="G114" s="5">
         <f>IF(ISNUMBER(E114),ROUND(E114*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3246,7 +3246,7 @@
         <v>3.0</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="307" customHeight="1">
+    <row r="115" spans="1:11" ht="294" customHeight="1">
       <c r="A115" t="s">
         <v>152</v>
       </c>
@@ -3294,19 +3294,19 @@
       </c>
       <c r="E118" s="2">
         <f>IF(COUNT('Turns'!E107,'Turns'!E108,'Turns'!E113,'Turns'!E114)=4,SUM('Turns'!E107,'Turns'!E108,'Turns'!E113,'Turns'!E114),"Unknown")</f>
-        <v>0.000227863044</v>
+        <v>0.000219313818</v>
       </c>
       <c r="F118" s="2">
         <f>IF(COUNT('Turns'!F107,'Turns'!F108,'Turns'!F113,'Turns'!F114)=4,SUM('Turns'!F107,'Turns'!F108,'Turns'!F113,'Turns'!F114),"Unknown")</f>
-        <v>0.0002612</v>
+        <v>0.0002514</v>
       </c>
       <c r="G118" s="5">
         <f>IF(ISNUMBER(E118),ROUND(E118*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="H118" s="5">
         <f>IF(ISNUMBER(F118),ROUND(F118*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
       <c r="K118" s="4" t="s">
         <v>111</v>
@@ -3528,7 +3528,7 @@
         <v>21.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>4281.585</v>
+        <v>2057.073</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>159</v>
@@ -3633,7 +3633,7 @@
         <v>21.0</v>
       </c>
       <c r="AD3" s="1">
-        <v>4278.235</v>
+        <v>2053.805</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>159</v>
@@ -3738,7 +3738,7 @@
         <v>21.0</v>
       </c>
       <c r="AD4" s="1">
-        <v>4276.488</v>
+        <v>2052.502</v>
       </c>
       <c r="AE4" s="1" t="s">
         <v>159</v>
@@ -3840,7 +3840,7 @@
         <v>10.0</v>
       </c>
       <c r="AD5" s="1">
-        <v>2625.627</v>
+        <v>1245.423</v>
       </c>
       <c r="AE5" s="1" t="s">
         <v>159</v>
@@ -3948,7 +3948,7 @@
         <v>93</v>
       </c>
       <c r="AD6" s="1">
-        <v>2621.619</v>
+        <v>1239.611</v>
       </c>
       <c r="AE6" s="1" t="s">
         <v>172</v>
@@ -3980,7 +3980,7 @@
         <v>165</v>
       </c>
       <c r="AD7" s="1">
-        <v>1.945</v>
+        <v>4.191</v>
       </c>
       <c r="AE7" s="1" t="s">
         <v>176</v>
@@ -4012,7 +4012,7 @@
         <v>175</v>
       </c>
       <c r="AD8" s="1">
-        <v>0.493</v>
+        <v>1.12</v>
       </c>
       <c r="AE8" s="1" t="s">
         <v>176</v>
@@ -4114,7 +4114,7 @@
         <v>11.0</v>
       </c>
       <c r="AD9" s="1">
-        <v>1642.798</v>
+        <v>796.875</v>
       </c>
       <c r="AE9" s="1" t="s">
         <v>159</v>
@@ -4222,7 +4222,7 @@
         <v>118</v>
       </c>
       <c r="AD10" s="1">
-        <v>1640.031</v>
+        <v>793.284</v>
       </c>
       <c r="AE10" s="1" t="s">
         <v>172</v>
@@ -4324,7 +4324,7 @@
         <v>26.0</v>
       </c>
       <c r="AD11" s="1">
-        <v>2494.402</v>
+        <v>1929.992</v>
       </c>
       <c r="AE11" s="1" t="s">
         <v>159</v>
@@ -4429,7 +4429,7 @@
         <v>26.0</v>
       </c>
       <c r="AD12" s="1">
-        <v>2491.928</v>
+        <v>1927.933</v>
       </c>
       <c r="AE12" s="1" t="s">
         <v>159</v>
@@ -4534,7 +4534,7 @@
         <v>26.0</v>
       </c>
       <c r="AD13" s="1">
-        <v>2490.426</v>
+        <v>1926.7</v>
       </c>
       <c r="AE13" s="1" t="s">
         <v>159</v>
@@ -4639,7 +4639,7 @@
         <v>12.0</v>
       </c>
       <c r="AD14" s="1">
-        <v>1301.694</v>
+        <v>970.307</v>
       </c>
       <c r="AE14" s="1" t="s">
         <v>159</v>
@@ -4750,7 +4750,7 @@
         <v>124</v>
       </c>
       <c r="AD15" s="1">
-        <v>1299.012</v>
+        <v>967.854</v>
       </c>
       <c r="AE15" s="1" t="s">
         <v>172</v>
@@ -4782,7 +4782,7 @@
         <v>183</v>
       </c>
       <c r="AD16" s="1">
-        <v>2.281</v>
+        <v>2.488</v>
       </c>
       <c r="AE16" s="1" t="s">
         <v>176</v>
@@ -4814,7 +4814,7 @@
         <v>185</v>
       </c>
       <c r="AD17" s="1">
-        <v>0.461</v>
+        <v>0.53</v>
       </c>
       <c r="AE17" s="1" t="s">
         <v>176</v>
@@ -4916,7 +4916,7 @@
         <v>14.0</v>
       </c>
       <c r="AD18" s="1">
-        <v>1181.696</v>
+        <v>949.933</v>
       </c>
       <c r="AE18" s="1" t="s">
         <v>159</v>
@@ -5024,7 +5024,7 @@
         <v>131</v>
       </c>
       <c r="AD19" s="1">
-        <v>1179.909</v>
+        <v>947.78</v>
       </c>
       <c r="AE19" s="1" t="s">
         <v>172</v>
@@ -5054,15 +5054,15 @@
       </c>
       <c r="J20" s="2">
         <f>IF(COUNT('Turns'!D65,'Turns'!D81)=2,SUM('Turns'!D65,'Turns'!D81),"Unknown")</f>
-        <v>1295.0</v>
+        <v>1286.0</v>
       </c>
       <c r="K20" s="2">
         <f>IF(COUNT('Turns'!E65,'Turns'!E81)=2,SUM('Turns'!E65,'Turns'!E81),"Unknown")</f>
-        <v>0.00022594383</v>
+        <v>0.000224373564</v>
       </c>
       <c r="L20" s="2">
         <f>IF(COUNT('Turns'!F65,'Turns'!F81)=2,SUM('Turns'!F65,'Turns'!F81),"Unknown")</f>
-        <v>0.000259</v>
+        <v>0.0002572</v>
       </c>
       <c r="M20" s="2">
         <f>IF(COUNT('Turns'!D64,'Turns'!D80)=2,SUM('Turns'!D64,'Turns'!D80),"Unknown")</f>
@@ -5087,46 +5087,46 @@
       </c>
       <c r="S20" s="2">
         <f>IF(COUNT('Turns'!D71,'Turns'!D86)=2,SUM('Turns'!D71,'Turns'!D86),"Unknown")</f>
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="T20" s="2">
         <f>IF(COUNT('Turns'!E71,'Turns'!E86)=2,SUM('Turns'!E71,'Turns'!E86),"Unknown")</f>
-        <v>7.7466456e-05</v>
+        <v>7.85133e-05</v>
       </c>
       <c r="U20" s="2">
         <f>IF(COUNT('Turns'!F71,'Turns'!F86)=2,SUM('Turns'!F71,'Turns'!F86),"Unknown")</f>
-        <v>8.88e-05</v>
+        <v>9e-05</v>
       </c>
       <c r="V20" s="2">
         <f>IF(COUNT('Turns'!D70)=1,SUM('Turns'!D70),"Unknown")</f>
-        <v>27.0</v>
+        <v>18.0</v>
       </c>
       <c r="W20" s="2">
         <f>IF(COUNT('Turns'!E70)=1,SUM('Turns'!E70),"Unknown")</f>
-        <v>2.8264788e-05</v>
+        <v>1.8843192e-05</v>
       </c>
       <c r="X20" s="2">
         <f>IF(COUNT('Turns'!F70)=1,SUM('Turns'!F70),"Unknown")</f>
-        <v>3.24e-05</v>
+        <v>2.16e-05</v>
       </c>
       <c r="Y20" s="2">
         <f>IF(COUNT('Turns'!E75,'Turns'!E90)=2,SUM('Turns'!E75,'Turns'!E90),"Unknown")</f>
-        <v>0.000331675074</v>
+        <v>0.000321730056</v>
       </c>
       <c r="Z20" s="2">
         <f>IF(COUNT('Turns'!F75,'Turns'!F90)=2,SUM('Turns'!F75,'Turns'!F90),"Unknown")</f>
-        <v>0.0003802</v>
+        <v>0.0003688</v>
       </c>
       <c r="AA20" s="5">
         <f>IF(ISNUMBER(Y20),ROUND(Y20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
       <c r="AB20" s="5">
         <f>IF(ISNUMBER(Z20),ROUND(Z20*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>38.0</v>
+        <v>37.0</v>
       </c>
       <c r="AD20" s="1">
-        <v>3516.912</v>
+        <v>5181.025</v>
       </c>
       <c r="AE20" s="1" t="s">
         <v>159</v>
@@ -5159,15 +5159,15 @@
       </c>
       <c r="J21" s="2">
         <f>IF(COUNT('Turns'!D65,'Turns'!D81)=2,SUM('Turns'!D65,'Turns'!D81),"Unknown")</f>
-        <v>1295.0</v>
+        <v>1286.0</v>
       </c>
       <c r="K21" s="2">
         <f>IF(COUNT('Turns'!E65,'Turns'!E81)=2,SUM('Turns'!E65,'Turns'!E81),"Unknown")</f>
-        <v>0.00022594383</v>
+        <v>0.000224373564</v>
       </c>
       <c r="L21" s="2">
         <f>IF(COUNT('Turns'!F65,'Turns'!F81)=2,SUM('Turns'!F65,'Turns'!F81),"Unknown")</f>
-        <v>0.000259</v>
+        <v>0.0002572</v>
       </c>
       <c r="M21" s="2">
         <f>IF(COUNT('Turns'!D64,'Turns'!D80)=2,SUM('Turns'!D64,'Turns'!D80),"Unknown")</f>
@@ -5192,46 +5192,46 @@
       </c>
       <c r="S21" s="2">
         <f>IF(COUNT('Turns'!D71,'Turns'!D86)=2,SUM('Turns'!D71,'Turns'!D86),"Unknown")</f>
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="T21" s="2">
         <f>IF(COUNT('Turns'!E71,'Turns'!E86)=2,SUM('Turns'!E71,'Turns'!E86),"Unknown")</f>
-        <v>7.7466456e-05</v>
+        <v>7.85133e-05</v>
       </c>
       <c r="U21" s="2">
         <f>IF(COUNT('Turns'!F71,'Turns'!F86)=2,SUM('Turns'!F71,'Turns'!F86),"Unknown")</f>
-        <v>8.88e-05</v>
+        <v>9e-05</v>
       </c>
       <c r="V21" s="2">
         <f>IF(COUNT('Turns'!D70)=1,SUM('Turns'!D70),"Unknown")</f>
-        <v>27.0</v>
+        <v>18.0</v>
       </c>
       <c r="W21" s="2">
         <f>IF(COUNT('Turns'!E70)=1,SUM('Turns'!E70),"Unknown")</f>
-        <v>2.8264788e-05</v>
+        <v>1.8843192e-05</v>
       </c>
       <c r="X21" s="2">
         <f>IF(COUNT('Turns'!F70)=1,SUM('Turns'!F70),"Unknown")</f>
-        <v>3.24e-05</v>
+        <v>2.16e-05</v>
       </c>
       <c r="Y21" s="2">
         <f>IF(COUNT('Turns'!E75,'Turns'!E90)=2,SUM('Turns'!E75,'Turns'!E90),"Unknown")</f>
-        <v>0.000331675074</v>
+        <v>0.000321730056</v>
       </c>
       <c r="Z21" s="2">
         <f>IF(COUNT('Turns'!F75,'Turns'!F90)=2,SUM('Turns'!F75,'Turns'!F90),"Unknown")</f>
-        <v>0.0003802</v>
+        <v>0.0003688</v>
       </c>
       <c r="AA21" s="5">
         <f>IF(ISNUMBER(Y21),ROUND(Y21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
       <c r="AB21" s="5">
         <f>IF(ISNUMBER(Z21),ROUND(Z21*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>38.0</v>
+        <v>37.0</v>
       </c>
       <c r="AD21" s="1">
-        <v>3513.306</v>
+        <v>5178.645</v>
       </c>
       <c r="AE21" s="1" t="s">
         <v>159</v>
@@ -5264,15 +5264,15 @@
       </c>
       <c r="J22" s="2">
         <f>IF(COUNT('Turns'!D65,'Turns'!D81)=2,SUM('Turns'!D65,'Turns'!D81),"Unknown")</f>
-        <v>1295.0</v>
+        <v>1286.0</v>
       </c>
       <c r="K22" s="2">
         <f>IF(COUNT('Turns'!E65,'Turns'!E81)=2,SUM('Turns'!E65,'Turns'!E81),"Unknown")</f>
-        <v>0.00022594383</v>
+        <v>0.000224373564</v>
       </c>
       <c r="L22" s="2">
         <f>IF(COUNT('Turns'!F65,'Turns'!F81)=2,SUM('Turns'!F65,'Turns'!F81),"Unknown")</f>
-        <v>0.000259</v>
+        <v>0.0002572</v>
       </c>
       <c r="M22" s="2">
         <f>IF(COUNT('Turns'!D64,'Turns'!D80)=2,SUM('Turns'!D64,'Turns'!D80),"Unknown")</f>
@@ -5297,46 +5297,46 @@
       </c>
       <c r="S22" s="2">
         <f>IF(COUNT('Turns'!D71,'Turns'!D86)=2,SUM('Turns'!D71,'Turns'!D86),"Unknown")</f>
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="T22" s="2">
         <f>IF(COUNT('Turns'!E71,'Turns'!E86)=2,SUM('Turns'!E71,'Turns'!E86),"Unknown")</f>
-        <v>7.7466456e-05</v>
+        <v>7.85133e-05</v>
       </c>
       <c r="U22" s="2">
         <f>IF(COUNT('Turns'!F71,'Turns'!F86)=2,SUM('Turns'!F71,'Turns'!F86),"Unknown")</f>
-        <v>8.88e-05</v>
+        <v>9e-05</v>
       </c>
       <c r="V22" s="2">
         <f>IF(COUNT('Turns'!D70)=1,SUM('Turns'!D70),"Unknown")</f>
-        <v>27.0</v>
+        <v>18.0</v>
       </c>
       <c r="W22" s="2">
         <f>IF(COUNT('Turns'!E70)=1,SUM('Turns'!E70),"Unknown")</f>
-        <v>2.8264788e-05</v>
+        <v>1.8843192e-05</v>
       </c>
       <c r="X22" s="2">
         <f>IF(COUNT('Turns'!F70)=1,SUM('Turns'!F70),"Unknown")</f>
-        <v>3.24e-05</v>
+        <v>2.16e-05</v>
       </c>
       <c r="Y22" s="2">
         <f>IF(COUNT('Turns'!E75,'Turns'!E90)=2,SUM('Turns'!E75,'Turns'!E90),"Unknown")</f>
-        <v>0.000331675074</v>
+        <v>0.000321730056</v>
       </c>
       <c r="Z22" s="2">
         <f>IF(COUNT('Turns'!F75,'Turns'!F90)=2,SUM('Turns'!F75,'Turns'!F90),"Unknown")</f>
-        <v>0.0003802</v>
+        <v>0.0003688</v>
       </c>
       <c r="AA22" s="5">
         <f>IF(ISNUMBER(Y22),ROUND(Y22*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
       <c r="AB22" s="5">
         <f>IF(ISNUMBER(Z22),ROUND(Z22*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>38.0</v>
+        <v>37.0</v>
       </c>
       <c r="AD22" s="1">
-        <v>3511.435</v>
+        <v>5176.686</v>
       </c>
       <c r="AE22" s="1" t="s">
         <v>159</v>
@@ -5414,34 +5414,34 @@
       </c>
       <c r="V23" s="2">
         <f>IF(COUNT('Turns'!D70)=1,SUM('Turns'!D70),"Unknown")</f>
-        <v>27.0</v>
+        <v>18.0</v>
       </c>
       <c r="W23" s="2">
         <f>IF(COUNT('Turns'!E70)=1,SUM('Turns'!E70),"Unknown")</f>
-        <v>2.8264788e-05</v>
+        <v>1.8843192e-05</v>
       </c>
       <c r="X23" s="2">
         <f>IF(COUNT('Turns'!F70)=1,SUM('Turns'!F70),"Unknown")</f>
-        <v>3.24e-05</v>
+        <v>2.16e-05</v>
       </c>
       <c r="Y23" s="2">
         <f>IF(COUNT('Turns'!E75)=1,SUM('Turns'!E75),"Unknown")</f>
-        <v>0.00017534637</v>
+        <v>0.000165924774</v>
       </c>
       <c r="Z23" s="2">
         <f>IF(COUNT('Turns'!F75)=1,SUM('Turns'!F75),"Unknown")</f>
-        <v>0.000201</v>
+        <v>0.0001902</v>
       </c>
       <c r="AA23" s="5">
         <f>IF(ISNUMBER(Y23),ROUND(Y23*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="AB23" s="5">
         <f>IF(ISNUMBER(Z23),ROUND(Z23*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="AD23" s="1">
-        <v>1942.219</v>
+        <v>3118.554</v>
       </c>
       <c r="AE23" s="1" t="s">
         <v>159</v>
@@ -5522,37 +5522,37 @@
       </c>
       <c r="V24" s="2">
         <f>IF(COUNT('Turns'!D70)=1,SUM('Turns'!D70),"Unknown")</f>
-        <v>27.0</v>
+        <v>18.0</v>
       </c>
       <c r="W24" s="2">
         <f>IF(COUNT('Turns'!E70)=1,SUM('Turns'!E70),"Unknown")</f>
-        <v>2.8264788e-05</v>
+        <v>1.8843192e-05</v>
       </c>
       <c r="X24" s="2">
         <f>IF(COUNT('Turns'!F70)=1,SUM('Turns'!F70),"Unknown")</f>
-        <v>3.24e-05</v>
+        <v>2.16e-05</v>
       </c>
       <c r="Y24" s="2">
         <f>IF(COUNT('Turns'!E75)=1,SUM('Turns'!E75),"Unknown")</f>
-        <v>0.00017534637</v>
+        <v>0.000165924774</v>
       </c>
       <c r="Z24" s="2">
         <f>IF(COUNT('Turns'!F75)=1,SUM('Turns'!F75),"Unknown")</f>
-        <v>0.000201</v>
+        <v>0.0001902</v>
       </c>
       <c r="AA24" s="5">
         <f>IF(ISNUMBER(Y24),ROUND(Y24*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>18.0</v>
+        <v>17.0</v>
       </c>
       <c r="AB24" s="5">
         <f>IF(ISNUMBER(Z24),ROUND(Z24*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="AC24" s="1" t="s">
         <v>135</v>
       </c>
       <c r="AD24" s="1">
-        <v>1939.829</v>
+        <v>3115.678</v>
       </c>
       <c r="AE24" s="1" t="s">
         <v>172</v>
@@ -5584,7 +5584,7 @@
         <v>191</v>
       </c>
       <c r="AD25" s="1">
-        <v>2.38</v>
+        <v>3.727</v>
       </c>
       <c r="AE25" s="1" t="s">
         <v>176</v>
@@ -5616,7 +5616,7 @@
         <v>193</v>
       </c>
       <c r="AD26" s="1">
-        <v>0.541</v>
+        <v>1.037</v>
       </c>
       <c r="AE26" s="1" t="s">
         <v>176</v>
@@ -5649,15 +5649,15 @@
       </c>
       <c r="J27" s="2">
         <f>IF(COUNT('Turns'!D81)=1,SUM('Turns'!D81),"Unknown")</f>
-        <v>692.0</v>
+        <v>683.0</v>
       </c>
       <c r="K27" s="2">
         <f>IF(COUNT('Turns'!E81)=1,SUM('Turns'!E81),"Unknown")</f>
-        <v>0.000120736008</v>
+        <v>0.000119165742</v>
       </c>
       <c r="L27" s="2">
         <f>IF(COUNT('Turns'!F81)=1,SUM('Turns'!F81),"Unknown")</f>
-        <v>0.0001384</v>
+        <v>0.0001366</v>
       </c>
       <c r="M27" s="2">
         <f>IF(COUNT('Turns'!D80)=1,SUM('Turns'!D80),"Unknown")</f>
@@ -5682,15 +5682,15 @@
       </c>
       <c r="S27" s="2">
         <f>IF(COUNT('Turns'!D86)=1,SUM('Turns'!D86),"Unknown")</f>
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="T27" s="2">
         <f>IF(COUNT('Turns'!E86)=1,SUM('Turns'!E86),"Unknown")</f>
-        <v>3.5592696e-05</v>
+        <v>3.663954e-05</v>
       </c>
       <c r="U27" s="2">
         <f>IF(COUNT('Turns'!F86)=1,SUM('Turns'!F86),"Unknown")</f>
-        <v>4.08e-05</v>
+        <v>4.2e-05</v>
       </c>
       <c r="V27" s="2">
         <v>0</v>
@@ -5703,11 +5703,11 @@
       </c>
       <c r="Y27" s="2">
         <f>IF(COUNT('Turns'!E90)=1,SUM('Turns'!E90),"Unknown")</f>
-        <v>0.000156328704</v>
+        <v>0.000155805282</v>
       </c>
       <c r="Z27" s="2">
         <f>IF(COUNT('Turns'!F90)=1,SUM('Turns'!F90),"Unknown")</f>
-        <v>0.0001792</v>
+        <v>0.0001786</v>
       </c>
       <c r="AA27" s="5">
         <f>IF(ISNUMBER(Y27),ROUND(Y27*'Reference data'!$B$2,0),"Unknown")</f>
@@ -5718,7 +5718,7 @@
         <v>18.0</v>
       </c>
       <c r="AD27" s="1">
-        <v>1561.802</v>
+        <v>2048.263</v>
       </c>
       <c r="AE27" s="1" t="s">
         <v>159</v>
@@ -5741,7 +5741,7 @@
         <v>111</v>
       </c>
       <c r="F28" s="1">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>171</v>
@@ -5754,15 +5754,15 @@
       </c>
       <c r="J28" s="2">
         <f>IF(COUNT('Turns'!D81)=1,SUM('Turns'!D81),"Unknown")</f>
-        <v>692.0</v>
+        <v>683.0</v>
       </c>
       <c r="K28" s="2">
         <f>IF(COUNT('Turns'!E81)=1,SUM('Turns'!E81),"Unknown")</f>
-        <v>0.000120736008</v>
+        <v>0.000119165742</v>
       </c>
       <c r="L28" s="2">
         <f>IF(COUNT('Turns'!F81)=1,SUM('Turns'!F81),"Unknown")</f>
-        <v>0.0001384</v>
+        <v>0.0001366</v>
       </c>
       <c r="M28" s="2">
         <f>IF(COUNT('Turns'!D80)=1,SUM('Turns'!D80),"Unknown")</f>
@@ -5787,15 +5787,15 @@
       </c>
       <c r="S28" s="2">
         <f>IF(COUNT('Turns'!D86)=1,SUM('Turns'!D86),"Unknown")</f>
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="T28" s="2">
         <f>IF(COUNT('Turns'!E86)=1,SUM('Turns'!E86),"Unknown")</f>
-        <v>3.5592696e-05</v>
+        <v>3.663954e-05</v>
       </c>
       <c r="U28" s="2">
         <f>IF(COUNT('Turns'!F86)=1,SUM('Turns'!F86),"Unknown")</f>
-        <v>4.08e-05</v>
+        <v>4.2e-05</v>
       </c>
       <c r="V28" s="2">
         <v>0</v>
@@ -5808,11 +5808,11 @@
       </c>
       <c r="Y28" s="2">
         <f>IF(COUNT('Turns'!E90)=1,SUM('Turns'!E90),"Unknown")</f>
-        <v>0.000156328704</v>
+        <v>0.000155805282</v>
       </c>
       <c r="Z28" s="2">
         <f>IF(COUNT('Turns'!F90)=1,SUM('Turns'!F90),"Unknown")</f>
-        <v>0.0001792</v>
+        <v>0.0001786</v>
       </c>
       <c r="AA28" s="5">
         <f>IF(ISNUMBER(Y28),ROUND(Y28*'Reference data'!$B$2,0),"Unknown")</f>
@@ -5826,7 +5826,7 @@
         <v>143</v>
       </c>
       <c r="AD28" s="1">
-        <v>1558.87</v>
+        <v>2045.756</v>
       </c>
       <c r="AE28" s="1" t="s">
         <v>172</v>
@@ -5856,15 +5856,15 @@
       </c>
       <c r="J29" s="2">
         <f>IF(COUNT('Turns'!D94)=1,SUM('Turns'!D94),"Unknown")</f>
-        <v>740.0</v>
+        <v>732.0</v>
       </c>
       <c r="K29" s="2">
         <f>IF(COUNT('Turns'!E94)=1,SUM('Turns'!E94),"Unknown")</f>
-        <v>0.00012911076</v>
+        <v>0.000127714968</v>
       </c>
       <c r="L29" s="2">
         <f>IF(COUNT('Turns'!F94)=1,SUM('Turns'!F94),"Unknown")</f>
-        <v>0.000148</v>
+        <v>0.0001464</v>
       </c>
       <c r="M29" s="2">
         <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
@@ -5901,23 +5901,23 @@
       </c>
       <c r="V29" s="2">
         <f>IF(COUNT('Turns'!D99)=1,SUM('Turns'!D99),"Unknown")</f>
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="W29" s="2">
         <f>IF(COUNT('Turns'!E99)=1,SUM('Turns'!E99),"Unknown")</f>
-        <v>2.1983724e-05</v>
+        <v>2.3030568e-05</v>
       </c>
       <c r="X29" s="2">
         <f>IF(COUNT('Turns'!F99)=1,SUM('Turns'!F99),"Unknown")</f>
-        <v>2.52e-05</v>
+        <v>2.64e-05</v>
       </c>
       <c r="Y29" s="2">
         <f>IF(COUNT('Turns'!E104)=1,SUM('Turns'!E104),"Unknown")</f>
-        <v>0.000174125052</v>
+        <v>0.000173776104</v>
       </c>
       <c r="Z29" s="2">
         <f>IF(COUNT('Turns'!F104)=1,SUM('Turns'!F104),"Unknown")</f>
-        <v>0.0001996</v>
+        <v>0.0001992</v>
       </c>
       <c r="AA29" s="5">
         <f>IF(ISNUMBER(Y29),ROUND(Y29*'Reference data'!$B$2,0),"Unknown")</f>
@@ -5928,7 +5928,7 @@
         <v>20.0</v>
       </c>
       <c r="AD29" s="1">
-        <v>953.615</v>
+        <v>1449.498</v>
       </c>
       <c r="AE29" s="1" t="s">
         <v>159</v>
@@ -5961,15 +5961,15 @@
       </c>
       <c r="J30" s="2">
         <f>IF(COUNT('Turns'!D94)=1,SUM('Turns'!D94),"Unknown")</f>
-        <v>740.0</v>
+        <v>732.0</v>
       </c>
       <c r="K30" s="2">
         <f>IF(COUNT('Turns'!E94)=1,SUM('Turns'!E94),"Unknown")</f>
-        <v>0.00012911076</v>
+        <v>0.000127714968</v>
       </c>
       <c r="L30" s="2">
         <f>IF(COUNT('Turns'!F94)=1,SUM('Turns'!F94),"Unknown")</f>
-        <v>0.000148</v>
+        <v>0.0001464</v>
       </c>
       <c r="M30" s="2">
         <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
@@ -6006,23 +6006,23 @@
       </c>
       <c r="V30" s="2">
         <f>IF(COUNT('Turns'!D99)=1,SUM('Turns'!D99),"Unknown")</f>
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="W30" s="2">
         <f>IF(COUNT('Turns'!E99)=1,SUM('Turns'!E99),"Unknown")</f>
-        <v>2.1983724e-05</v>
+        <v>2.3030568e-05</v>
       </c>
       <c r="X30" s="2">
         <f>IF(COUNT('Turns'!F99)=1,SUM('Turns'!F99),"Unknown")</f>
-        <v>2.52e-05</v>
+        <v>2.64e-05</v>
       </c>
       <c r="Y30" s="2">
         <f>IF(COUNT('Turns'!E104)=1,SUM('Turns'!E104),"Unknown")</f>
-        <v>0.000174125052</v>
+        <v>0.000173776104</v>
       </c>
       <c r="Z30" s="2">
         <f>IF(COUNT('Turns'!F104)=1,SUM('Turns'!F104),"Unknown")</f>
-        <v>0.0001996</v>
+        <v>0.0001992</v>
       </c>
       <c r="AA30" s="5">
         <f>IF(ISNUMBER(Y30),ROUND(Y30*'Reference data'!$B$2,0),"Unknown")</f>
@@ -6033,7 +6033,7 @@
         <v>20.0</v>
       </c>
       <c r="AD30" s="1">
-        <v>950.852</v>
+        <v>1447.526</v>
       </c>
       <c r="AE30" s="1" t="s">
         <v>159</v>
@@ -6066,15 +6066,15 @@
       </c>
       <c r="J31" s="2">
         <f>IF(COUNT('Turns'!D94)=1,SUM('Turns'!D94),"Unknown")</f>
-        <v>740.0</v>
+        <v>732.0</v>
       </c>
       <c r="K31" s="2">
         <f>IF(COUNT('Turns'!E94)=1,SUM('Turns'!E94),"Unknown")</f>
-        <v>0.00012911076</v>
+        <v>0.000127714968</v>
       </c>
       <c r="L31" s="2">
         <f>IF(COUNT('Turns'!F94)=1,SUM('Turns'!F94),"Unknown")</f>
-        <v>0.000148</v>
+        <v>0.0001464</v>
       </c>
       <c r="M31" s="2">
         <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
@@ -6111,23 +6111,23 @@
       </c>
       <c r="V31" s="2">
         <f>IF(COUNT('Turns'!D99)=1,SUM('Turns'!D99),"Unknown")</f>
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="W31" s="2">
         <f>IF(COUNT('Turns'!E99)=1,SUM('Turns'!E99),"Unknown")</f>
-        <v>2.1983724e-05</v>
+        <v>2.3030568e-05</v>
       </c>
       <c r="X31" s="2">
         <f>IF(COUNT('Turns'!F99)=1,SUM('Turns'!F99),"Unknown")</f>
-        <v>2.52e-05</v>
+        <v>2.64e-05</v>
       </c>
       <c r="Y31" s="2">
         <f>IF(COUNT('Turns'!E104)=1,SUM('Turns'!E104),"Unknown")</f>
-        <v>0.000174125052</v>
+        <v>0.000173776104</v>
       </c>
       <c r="Z31" s="2">
         <f>IF(COUNT('Turns'!F104)=1,SUM('Turns'!F104),"Unknown")</f>
-        <v>0.0001996</v>
+        <v>0.0001992</v>
       </c>
       <c r="AA31" s="5">
         <f>IF(ISNUMBER(Y31),ROUND(Y31*'Reference data'!$B$2,0),"Unknown")</f>
@@ -6138,7 +6138,7 @@
         <v>20.0</v>
       </c>
       <c r="AD31" s="1">
-        <v>949.497</v>
+        <v>1446.481</v>
       </c>
       <c r="AE31" s="1" t="s">
         <v>159</v>
@@ -6171,15 +6171,15 @@
       </c>
       <c r="J32" s="2">
         <f>IF(COUNT('Turns'!D94)=1,SUM('Turns'!D94),"Unknown")</f>
-        <v>740.0</v>
+        <v>732.0</v>
       </c>
       <c r="K32" s="2">
         <f>IF(COUNT('Turns'!E94)=1,SUM('Turns'!E94),"Unknown")</f>
-        <v>0.00012911076</v>
+        <v>0.000127714968</v>
       </c>
       <c r="L32" s="2">
         <f>IF(COUNT('Turns'!F94)=1,SUM('Turns'!F94),"Unknown")</f>
-        <v>0.000148</v>
+        <v>0.0001464</v>
       </c>
       <c r="M32" s="2">
         <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
@@ -6216,23 +6216,23 @@
       </c>
       <c r="V32" s="2">
         <f>IF(COUNT('Turns'!D99)=1,SUM('Turns'!D99),"Unknown")</f>
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="W32" s="2">
         <f>IF(COUNT('Turns'!E99)=1,SUM('Turns'!E99),"Unknown")</f>
-        <v>2.1983724e-05</v>
+        <v>2.3030568e-05</v>
       </c>
       <c r="X32" s="2">
         <f>IF(COUNT('Turns'!F99)=1,SUM('Turns'!F99),"Unknown")</f>
-        <v>2.52e-05</v>
+        <v>2.64e-05</v>
       </c>
       <c r="Y32" s="2">
         <f>IF(COUNT('Turns'!E104)=1,SUM('Turns'!E104),"Unknown")</f>
-        <v>0.000174125052</v>
+        <v>0.000173776104</v>
       </c>
       <c r="Z32" s="2">
         <f>IF(COUNT('Turns'!F104)=1,SUM('Turns'!F104),"Unknown")</f>
-        <v>0.0001996</v>
+        <v>0.0001992</v>
       </c>
       <c r="AA32" s="5">
         <f>IF(ISNUMBER(Y32),ROUND(Y32*'Reference data'!$B$2,0),"Unknown")</f>
@@ -6243,7 +6243,7 @@
         <v>20.0</v>
       </c>
       <c r="AD32" s="1">
-        <v>945.4829999999999</v>
+        <v>1443.792</v>
       </c>
       <c r="AE32" s="1" t="s">
         <v>159</v>
@@ -6266,7 +6266,7 @@
         <v>111</v>
       </c>
       <c r="F33" s="1">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>171</v>
@@ -6279,15 +6279,15 @@
       </c>
       <c r="J33" s="2">
         <f>IF(COUNT('Turns'!D94)=1,SUM('Turns'!D94),"Unknown")</f>
-        <v>740.0</v>
+        <v>732.0</v>
       </c>
       <c r="K33" s="2">
         <f>IF(COUNT('Turns'!E94)=1,SUM('Turns'!E94),"Unknown")</f>
-        <v>0.00012911076</v>
+        <v>0.000127714968</v>
       </c>
       <c r="L33" s="2">
         <f>IF(COUNT('Turns'!F94)=1,SUM('Turns'!F94),"Unknown")</f>
-        <v>0.000148</v>
+        <v>0.0001464</v>
       </c>
       <c r="M33" s="2">
         <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
@@ -6324,23 +6324,23 @@
       </c>
       <c r="V33" s="2">
         <f>IF(COUNT('Turns'!D99)=1,SUM('Turns'!D99),"Unknown")</f>
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="W33" s="2">
         <f>IF(COUNT('Turns'!E99)=1,SUM('Turns'!E99),"Unknown")</f>
-        <v>2.1983724e-05</v>
+        <v>2.3030568e-05</v>
       </c>
       <c r="X33" s="2">
         <f>IF(COUNT('Turns'!F99)=1,SUM('Turns'!F99),"Unknown")</f>
-        <v>2.52e-05</v>
+        <v>2.64e-05</v>
       </c>
       <c r="Y33" s="2">
         <f>IF(COUNT('Turns'!E104)=1,SUM('Turns'!E104),"Unknown")</f>
-        <v>0.000174125052</v>
+        <v>0.000173776104</v>
       </c>
       <c r="Z33" s="2">
         <f>IF(COUNT('Turns'!F104)=1,SUM('Turns'!F104),"Unknown")</f>
-        <v>0.0001996</v>
+        <v>0.0001992</v>
       </c>
       <c r="AA33" s="5">
         <f>IF(ISNUMBER(Y33),ROUND(Y33*'Reference data'!$B$2,0),"Unknown")</f>
@@ -6354,7 +6354,7 @@
         <v>147</v>
       </c>
       <c r="AD33" s="1">
-        <v>942.019</v>
+        <v>1441.526</v>
       </c>
       <c r="AE33" s="1" t="s">
         <v>172</v>
@@ -6384,15 +6384,15 @@
       </c>
       <c r="J34" s="2">
         <f>IF(COUNT('Turns'!D108)=1,SUM('Turns'!D108),"Unknown")</f>
-        <v>808.0</v>
+        <v>801.0</v>
       </c>
       <c r="K34" s="2">
         <f>IF(COUNT('Turns'!E108)=1,SUM('Turns'!E108),"Unknown")</f>
-        <v>0.000140974992</v>
+        <v>0.000139753674</v>
       </c>
       <c r="L34" s="2">
         <f>IF(COUNT('Turns'!F108)=1,SUM('Turns'!F108),"Unknown")</f>
-        <v>0.0001616</v>
+        <v>0.0001602</v>
       </c>
       <c r="M34" s="2">
         <f>IF(COUNT('Turns'!D107)=1,SUM('Turns'!D107),"Unknown")</f>
@@ -6417,46 +6417,46 @@
       </c>
       <c r="S34" s="2">
         <f>IF(COUNT('Turns'!D114)=1,SUM('Turns'!D114),"Unknown")</f>
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="T34" s="2">
         <f>IF(COUNT('Turns'!E114)=1,SUM('Turns'!E114),"Unknown")</f>
-        <v>2.9311632e-05</v>
+        <v>3.0358476e-05</v>
       </c>
       <c r="U34" s="2">
         <f>IF(COUNT('Turns'!F114)=1,SUM('Turns'!F114),"Unknown")</f>
-        <v>3.36e-05</v>
+        <v>3.48e-05</v>
       </c>
       <c r="V34" s="2">
         <f>IF(COUNT('Turns'!D113)=1,SUM('Turns'!D113),"Unknown")</f>
-        <v>55.0</v>
+        <v>47.0</v>
       </c>
       <c r="W34" s="2">
         <f>IF(COUNT('Turns'!E113)=1,SUM('Turns'!E113),"Unknown")</f>
-        <v>5.757642e-05</v>
+        <v>4.9201668e-05</v>
       </c>
       <c r="X34" s="2">
         <f>IF(COUNT('Turns'!F113)=1,SUM('Turns'!F113),"Unknown")</f>
-        <v>6.6e-05</v>
+        <v>5.64e-05</v>
       </c>
       <c r="Y34" s="2">
         <f>IF(COUNT('Turns'!E118)=1,SUM('Turns'!E118),"Unknown")</f>
-        <v>0.000227863044</v>
+        <v>0.000219313818</v>
       </c>
       <c r="Z34" s="2">
         <f>IF(COUNT('Turns'!F118)=1,SUM('Turns'!F118),"Unknown")</f>
-        <v>0.0002612</v>
+        <v>0.0002514</v>
       </c>
       <c r="AA34" s="5">
         <f>IF(ISNUMBER(Y34),ROUND(Y34*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="AB34" s="5">
         <f>IF(ISNUMBER(Z34),ROUND(Z34*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
       <c r="AD34" s="1">
-        <v>1441.095</v>
+        <v>1427.932</v>
       </c>
       <c r="AE34" s="1" t="s">
         <v>159</v>
@@ -6489,15 +6489,15 @@
       </c>
       <c r="J35" s="2">
         <f>IF(COUNT('Turns'!D108)=1,SUM('Turns'!D108),"Unknown")</f>
-        <v>808.0</v>
+        <v>801.0</v>
       </c>
       <c r="K35" s="2">
         <f>IF(COUNT('Turns'!E108)=1,SUM('Turns'!E108),"Unknown")</f>
-        <v>0.000140974992</v>
+        <v>0.000139753674</v>
       </c>
       <c r="L35" s="2">
         <f>IF(COUNT('Turns'!F108)=1,SUM('Turns'!F108),"Unknown")</f>
-        <v>0.0001616</v>
+        <v>0.0001602</v>
       </c>
       <c r="M35" s="2">
         <f>IF(COUNT('Turns'!D107)=1,SUM('Turns'!D107),"Unknown")</f>
@@ -6522,46 +6522,46 @@
       </c>
       <c r="S35" s="2">
         <f>IF(COUNT('Turns'!D114)=1,SUM('Turns'!D114),"Unknown")</f>
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="T35" s="2">
         <f>IF(COUNT('Turns'!E114)=1,SUM('Turns'!E114),"Unknown")</f>
-        <v>2.9311632e-05</v>
+        <v>3.0358476e-05</v>
       </c>
       <c r="U35" s="2">
         <f>IF(COUNT('Turns'!F114)=1,SUM('Turns'!F114),"Unknown")</f>
-        <v>3.36e-05</v>
+        <v>3.48e-05</v>
       </c>
       <c r="V35" s="2">
         <f>IF(COUNT('Turns'!D113)=1,SUM('Turns'!D113),"Unknown")</f>
-        <v>55.0</v>
+        <v>47.0</v>
       </c>
       <c r="W35" s="2">
         <f>IF(COUNT('Turns'!E113)=1,SUM('Turns'!E113),"Unknown")</f>
-        <v>5.757642e-05</v>
+        <v>4.9201668e-05</v>
       </c>
       <c r="X35" s="2">
         <f>IF(COUNT('Turns'!F113)=1,SUM('Turns'!F113),"Unknown")</f>
-        <v>6.6e-05</v>
+        <v>5.64e-05</v>
       </c>
       <c r="Y35" s="2">
         <f>IF(COUNT('Turns'!E118)=1,SUM('Turns'!E118),"Unknown")</f>
-        <v>0.000227863044</v>
+        <v>0.000219313818</v>
       </c>
       <c r="Z35" s="2">
         <f>IF(COUNT('Turns'!F118)=1,SUM('Turns'!F118),"Unknown")</f>
-        <v>0.0002612</v>
+        <v>0.0002514</v>
       </c>
       <c r="AA35" s="5">
         <f>IF(ISNUMBER(Y35),ROUND(Y35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="AB35" s="5">
         <f>IF(ISNUMBER(Z35),ROUND(Z35*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
       <c r="AD35" s="1">
-        <v>1437.997</v>
+        <v>1426.061</v>
       </c>
       <c r="AE35" s="1" t="s">
         <v>159</v>
@@ -6594,15 +6594,15 @@
       </c>
       <c r="J36" s="2">
         <f>IF(COUNT('Turns'!D108)=1,SUM('Turns'!D108),"Unknown")</f>
-        <v>808.0</v>
+        <v>801.0</v>
       </c>
       <c r="K36" s="2">
         <f>IF(COUNT('Turns'!E108)=1,SUM('Turns'!E108),"Unknown")</f>
-        <v>0.000140974992</v>
+        <v>0.000139753674</v>
       </c>
       <c r="L36" s="2">
         <f>IF(COUNT('Turns'!F108)=1,SUM('Turns'!F108),"Unknown")</f>
-        <v>0.0001616</v>
+        <v>0.0001602</v>
       </c>
       <c r="M36" s="2">
         <f>IF(COUNT('Turns'!D107)=1,SUM('Turns'!D107),"Unknown")</f>
@@ -6627,46 +6627,46 @@
       </c>
       <c r="S36" s="2">
         <f>IF(COUNT('Turns'!D114)=1,SUM('Turns'!D114),"Unknown")</f>
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="T36" s="2">
         <f>IF(COUNT('Turns'!E114)=1,SUM('Turns'!E114),"Unknown")</f>
-        <v>2.9311632e-05</v>
+        <v>3.0358476e-05</v>
       </c>
       <c r="U36" s="2">
         <f>IF(COUNT('Turns'!F114)=1,SUM('Turns'!F114),"Unknown")</f>
-        <v>3.36e-05</v>
+        <v>3.48e-05</v>
       </c>
       <c r="V36" s="2">
         <f>IF(COUNT('Turns'!D113)=1,SUM('Turns'!D113),"Unknown")</f>
-        <v>55.0</v>
+        <v>47.0</v>
       </c>
       <c r="W36" s="2">
         <f>IF(COUNT('Turns'!E113)=1,SUM('Turns'!E113),"Unknown")</f>
-        <v>5.757642e-05</v>
+        <v>4.9201668e-05</v>
       </c>
       <c r="X36" s="2">
         <f>IF(COUNT('Turns'!F113)=1,SUM('Turns'!F113),"Unknown")</f>
-        <v>6.6e-05</v>
+        <v>5.64e-05</v>
       </c>
       <c r="Y36" s="2">
         <f>IF(COUNT('Turns'!E118)=1,SUM('Turns'!E118),"Unknown")</f>
-        <v>0.000227863044</v>
+        <v>0.000219313818</v>
       </c>
       <c r="Z36" s="2">
         <f>IF(COUNT('Turns'!F118)=1,SUM('Turns'!F118),"Unknown")</f>
-        <v>0.0002612</v>
+        <v>0.0002514</v>
       </c>
       <c r="AA36" s="5">
         <f>IF(ISNUMBER(Y36),ROUND(Y36*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="AB36" s="5">
         <f>IF(ISNUMBER(Z36),ROUND(Z36*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
       <c r="AD36" s="1">
-        <v>1436.424</v>
+        <v>1425.191</v>
       </c>
       <c r="AE36" s="1" t="s">
         <v>159</v>
@@ -6699,15 +6699,15 @@
       </c>
       <c r="J37" s="2">
         <f>IF(COUNT('Turns'!D108)=1,SUM('Turns'!D108),"Unknown")</f>
-        <v>808.0</v>
+        <v>801.0</v>
       </c>
       <c r="K37" s="2">
         <f>IF(COUNT('Turns'!E108)=1,SUM('Turns'!E108),"Unknown")</f>
-        <v>0.000140974992</v>
+        <v>0.000139753674</v>
       </c>
       <c r="L37" s="2">
         <f>IF(COUNT('Turns'!F108)=1,SUM('Turns'!F108),"Unknown")</f>
-        <v>0.0001616</v>
+        <v>0.0001602</v>
       </c>
       <c r="M37" s="2">
         <f>IF(COUNT('Turns'!D107)=1,SUM('Turns'!D107),"Unknown")</f>
@@ -6732,46 +6732,46 @@
       </c>
       <c r="S37" s="2">
         <f>IF(COUNT('Turns'!D114)=1,SUM('Turns'!D114),"Unknown")</f>
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="T37" s="2">
         <f>IF(COUNT('Turns'!E114)=1,SUM('Turns'!E114),"Unknown")</f>
-        <v>2.9311632e-05</v>
+        <v>3.0358476e-05</v>
       </c>
       <c r="U37" s="2">
         <f>IF(COUNT('Turns'!F114)=1,SUM('Turns'!F114),"Unknown")</f>
-        <v>3.36e-05</v>
+        <v>3.48e-05</v>
       </c>
       <c r="V37" s="2">
         <f>IF(COUNT('Turns'!D113)=1,SUM('Turns'!D113),"Unknown")</f>
-        <v>55.0</v>
+        <v>47.0</v>
       </c>
       <c r="W37" s="2">
         <f>IF(COUNT('Turns'!E113)=1,SUM('Turns'!E113),"Unknown")</f>
-        <v>5.757642e-05</v>
+        <v>4.9201668e-05</v>
       </c>
       <c r="X37" s="2">
         <f>IF(COUNT('Turns'!F113)=1,SUM('Turns'!F113),"Unknown")</f>
-        <v>6.6e-05</v>
+        <v>5.64e-05</v>
       </c>
       <c r="Y37" s="2">
         <f>IF(COUNT('Turns'!E118)=1,SUM('Turns'!E118),"Unknown")</f>
-        <v>0.000227863044</v>
+        <v>0.000219313818</v>
       </c>
       <c r="Z37" s="2">
         <f>IF(COUNT('Turns'!F118)=1,SUM('Turns'!F118),"Unknown")</f>
-        <v>0.0002612</v>
+        <v>0.0002514</v>
       </c>
       <c r="AA37" s="5">
         <f>IF(ISNUMBER(Y37),ROUND(Y37*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="AB37" s="5">
         <f>IF(ISNUMBER(Z37),ROUND(Z37*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
       <c r="AD37" s="1">
-        <v>1433.059</v>
+        <v>1423.234</v>
       </c>
       <c r="AE37" s="1" t="s">
         <v>159</v>
@@ -6794,7 +6794,7 @@
         <v>111</v>
       </c>
       <c r="F38" s="1">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>171</v>
@@ -6807,15 +6807,15 @@
       </c>
       <c r="J38" s="2">
         <f>IF(COUNT('Turns'!D108)=1,SUM('Turns'!D108),"Unknown")</f>
-        <v>808.0</v>
+        <v>801.0</v>
       </c>
       <c r="K38" s="2">
         <f>IF(COUNT('Turns'!E108)=1,SUM('Turns'!E108),"Unknown")</f>
-        <v>0.000140974992</v>
+        <v>0.000139753674</v>
       </c>
       <c r="L38" s="2">
         <f>IF(COUNT('Turns'!F108)=1,SUM('Turns'!F108),"Unknown")</f>
-        <v>0.0001616</v>
+        <v>0.0001602</v>
       </c>
       <c r="M38" s="2">
         <f>IF(COUNT('Turns'!D107)=1,SUM('Turns'!D107),"Unknown")</f>
@@ -6840,49 +6840,49 @@
       </c>
       <c r="S38" s="2">
         <f>IF(COUNT('Turns'!D114)=1,SUM('Turns'!D114),"Unknown")</f>
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="T38" s="2">
         <f>IF(COUNT('Turns'!E114)=1,SUM('Turns'!E114),"Unknown")</f>
-        <v>2.9311632e-05</v>
+        <v>3.0358476e-05</v>
       </c>
       <c r="U38" s="2">
         <f>IF(COUNT('Turns'!F114)=1,SUM('Turns'!F114),"Unknown")</f>
-        <v>3.36e-05</v>
+        <v>3.48e-05</v>
       </c>
       <c r="V38" s="2">
         <f>IF(COUNT('Turns'!D113)=1,SUM('Turns'!D113),"Unknown")</f>
-        <v>55.0</v>
+        <v>47.0</v>
       </c>
       <c r="W38" s="2">
         <f>IF(COUNT('Turns'!E113)=1,SUM('Turns'!E113),"Unknown")</f>
-        <v>5.757642e-05</v>
+        <v>4.9201668e-05</v>
       </c>
       <c r="X38" s="2">
         <f>IF(COUNT('Turns'!F113)=1,SUM('Turns'!F113),"Unknown")</f>
-        <v>6.6e-05</v>
+        <v>5.64e-05</v>
       </c>
       <c r="Y38" s="2">
         <f>IF(COUNT('Turns'!E118)=1,SUM('Turns'!E118),"Unknown")</f>
-        <v>0.000227863044</v>
+        <v>0.000219313818</v>
       </c>
       <c r="Z38" s="2">
         <f>IF(COUNT('Turns'!F118)=1,SUM('Turns'!F118),"Unknown")</f>
-        <v>0.0002612</v>
+        <v>0.0002514</v>
       </c>
       <c r="AA38" s="5">
         <f>IF(ISNUMBER(Y38),ROUND(Y38*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="AB38" s="5">
         <f>IF(ISNUMBER(Z38),ROUND(Z38*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
       <c r="AC38" s="1" t="s">
         <v>152</v>
       </c>
       <c r="AD38" s="1">
-        <v>1430.354</v>
+        <v>1421.315</v>
       </c>
       <c r="AE38" s="1" t="s">
         <v>172</v>

--- a/reports/claims_context_naive/report.xlsx
+++ b/reports/claims_context_naive/report.xlsx
@@ -75,13 +75,13 @@
     <t>Parent ID</t>
   </si>
   <si>
-    <t>Fresh input tokens</t>
-  </si>
-  <si>
-    <t>Fresh input EUR</t>
-  </si>
-  <si>
-    <t>Fresh input USD</t>
+    <t>Input at standard rate tokens</t>
+  </si>
+  <si>
+    <t>Input at standard rate EUR</t>
+  </si>
+  <si>
+    <t>Input at standard rate USD</t>
   </si>
   <si>
     <t>Cache read tokens</t>
@@ -165,7 +165,7 @@
     <t>Run ID</t>
   </si>
   <si>
-    <t>01a0ccdf-7609-7111-b51a-e5ab87820286</t>
+    <t>01a0d12d-1e51-7301-958f-25f71690174d</t>
   </si>
   <si>
     <t>Recording</t>
@@ -177,13 +177,13 @@
     <t>FX reference date</t>
   </si>
   <si>
-    <t>2026-09-22</t>
+    <t>2026-09-23</t>
   </si>
   <si>
     <t>FX fetched at</t>
   </si>
   <si>
-    <t>2026-09-23T06:06:28.037095Z</t>
+    <t>2026-09-24T02:09:35.117183Z</t>
   </si>
   <si>
     <t>UTC</t>
@@ -306,10 +306,10 @@
     <t>gpt-5.6-luna</t>
   </si>
   <si>
-    <t>01a0ccdf-7610-7ac0-86ac-13afb13ef1ea</t>
-  </si>
-  <si>
-    <t>Fresh input</t>
+    <t>01a0d12d-1e58-7912-8e64-4e2b720c32a9</t>
+  </si>
+  <si>
+    <t>Input at standard rate</t>
   </si>
   <si>
     <t xml:space="preserve">    Tool definitions</t>
@@ -357,8 +357,8 @@
     <t xml:space="preserve">    Output content</t>
   </si>
   <si>
-    <t>[{"id": "rs_07082eedd1e30c17006ab36c68b76087d29961850299d4f9d4", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2xoffosbRDf0m7ulqGUqYxG6SnyCagkJ2NAaWKSYLdG8pavxidSsTNwJmZS6zyDd6ScNM_WjA0JQ7BDRASuRXyCv8-urV2l6PrPW6rcSUzQaj6cUHpXLqX5MNYlARpAzxvyfZYdTnVqkQoogcNoi5YvEQusE-i_Jd3adLlLDrJKpepgnYNp0CA_W2L6YvRqyEQbWwA42gjzCpnaWpB_f6tevAnQbndYT62MGY7Td1tecew2ApdyN37dkcRScO3Xs65egz_T8M4qokrMBuoKkoNudjiYrlUiMvnzjGPMr3tz0zHaYeG2XDmMXUfBzbXASTLgOymE501Cj21UiZXCadeFEdeFc2f3nJdm7a0CoEtFkxil0j-XDX5ZD757TweTqJV-XLKwk6rNXpKs6k6ulTV7zqi12a7_jWD1wOPyREW9NABJDdbA3U8i2AqAPj8Mn9Toidyd4K_bHXlJg2FOBvU3EMUK6njLpCiOONhOgJmmYCDGt5pJptO4LBfnrkgQsIygYkDktruVX68GbLGDHD36FgIGHXz_oIR_-eSc73ge6UubDsoM4lvQ16GXp65GZpewSSX2K0vnBkuWpsQ9atZrt8uXvpbTQLYBfsnsUJFL5bOMgOT_5YKYrxJ2k8PTyDwvcvyOErDf5M38n631ubEu8rqd7yMf9Y8OJXsAsNLBODE23t-bIsgUb79-OlRAdfEiWh8B5WThyIyhRZzZCMYvnXMMYHtENUrs27HZf9gB36XhZoYz5aLfS4SWrtvLfOT2qUpCrkXqlT5ckyHTigkSOuZ5hIux_UHJTSfCz975nHquUAIuLx9O39CePA8ZPvxp9NkR26nyFw5-4BTt36AZxQzjpP0dgi5MD6Am7ISDGCV41zSKP66U7LTrOepIADBdGCjbFlWkGwFs4Ryc10B-TFa59dKDBy01du3yVQd9jDvnPNvHfNP6EufkGVOzVgpsdKKNsQuVyxh64mUUjENKk8LKq_QDKfIbQFZupHBD_bnp4baxrEJajiShycbrEf-gPrlkLVlQUAZewzwSgPTAC_bwQGu0HpH5imPq-iPYt4mxvAYOwfl1JWRO0mqlzIS3aWbJ9Xs7ZNBo_q3T-nK99wXD5nFUfPvmiIjaLb6MbmT5F25nRDA3LfcaCydWq18dD9zu1LMpomCXSkUPY--DCHJ-zXW7la7DVr5ngGOP3JJpQB1CTrmAu3kg6qDoVUEh"}, {"type": "function_call", "name": "read_policy", "arguments": "{}", "call_id": "call_EW0yGEbP2dxeEvdB0tLw6Jvs", "id": "fc_07082eedd1e30c17006ab36c68e09887d28527d381f0e8516d", "index": 1}]
-{"name": "read_policy", "args": {}, "id": "call_EW0yGEbP2dxeEvdB0tLw6Jvs", "type": "tool_call"}</t>
+    <t>[{"id": "rs_031f5ec7cdea1be9006ab4866f033c87d2bab5a52a6657f484", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIZvTnudEOmDESS6cw31-zgL3V_Yc2xS-qsvgajWR6yRMoTupYR4HMVd0Cni_4Rr6niCoLd5g_WrIN3ZiOPGOBhmpOSbEkGf6PPihRMjdfRtNk1uusLHpgctzKyNAFILyrkrRQU0fZ-AjQWU-R2ERYRot1QDQceBmI5n5c_cOryFKqqY5lEgh1p5to_6SpzSu3J8GkMXoQUlteJeg3n-9qGbkXok3bgZKhrVqcRgIaZBcUuehx5c3HOcERqqFvCJ33tYPrlMGSnQ7iVfolbLxPgQAAz8_vgAiEx_RidehbRpZJuRs4QOek07hg0SedsrQCwgkxx2iS_FdxwqHK3KWm1uYxuo8-BbwnnDuBXY5lCqFgVJBSoRPrHe81-PtNHSMArOi5sbpfCqVXJM_f5WQd3MJ96wo6mcEwuDhSvdysrJ5XVAlgLysiUkngOE3oZXCCPx0K0VyEj-ONG3RZO9C7YolG7NPz2m2AXIaDMBOpuAcnvryS-laqtq35myRNHu6w2-0nIuOkEu0hX7ZjKmU_fhJiv3F9XendO9l6OML90ZkGK0SpPrZuUQ5NgjC5-bLM3QdVnfz1so3ikZnxRU3hQp2Nx0Y-KjmslB75BQ6DdFz8fRnL7y5hBM-pqNSWyDTFpLdCoAm_Ck9f9ImuGlAXtMMFWAT9HloXzQqd1OoxrA-gadIS58xkbHX0lFmFwM58gO3GfPuo0Q4H9845SemaQMiVRdWuSVXKkjWxc-QGZ3SL_AndljbHrHArNquzfkxdMsx_XF5GmZcS3ZUgweCn6Pb9st1Opkjp4mr0N8YU3G9IGtyxWdIB6_jIQIgY6JMyU4a6KGd9diTD1xy7W16wijM1ale35V8gG1Nv38lya_9NBan75L1iUe5PhsKPqCOilaCbC29WwDyTcrAcuPdGrSzkSpaSgB0DRLeVT7uH1yWELYr0h924sqRDh49tu29XT1W7QlxR73qEvFRJpBFyuPZ1FQcHpzkV7Ibt33ZOIFjZS0nFt9lJpbHdKAB8FMhvkquw_v1Dllwl6OD_FMBn8utY8KProHBWGukUhG5DLiJaQCxo__VlvQLxJaz_oOX70LIGtfz0VNCmsoQn1tmon_oAWMhAakEeuKz3eNsNIaBR_1E2DRsSxaP9Zf70oX-YsIeo7ytk0bB_atqtOZSFzz3jjALrt0pkAuGwYDViF9-Uc4WTHJcj8QF1gm2HjuBIlF"}, {"type": "function_call", "name": "read_policy", "arguments": "{}", "call_id": "call_F3S6U2sZnFbauysBje55lKYe", "id": "fc_031f5ec7cdea1be9006ab4866f375c87d2841f384a416ba2fe", "index": 1}]
+{"name": "read_policy", "args": {}, "id": "call_F3S6U2sZnFbauysBje55lKYe", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Call total</t>
@@ -370,7 +370,7 @@
     <t>Tool · read_policy</t>
   </si>
   <si>
-    <t>01a0ccdf-7aef-7471-b42c-60631ed28818</t>
+    <t>01a0d12d-233a-7701-ad35-25943e452960</t>
   </si>
   <si>
     <t xml:space="preserve">    Arguments</t>
@@ -388,7 +388,7 @@
     <t>R2</t>
   </si>
   <si>
-    <t>01a0ccdf-7af7-7831-bfdb-d66da962ffa8</t>
+    <t>01a0d12d-233c-7230-baa8-5e5d61c03ce7</t>
   </si>
   <si>
     <t>Conversation history · cache read</t>
@@ -397,7 +397,7 @@
     <t xml:space="preserve">    Tool result</t>
   </si>
   <si>
-    <t>[{"type": "text", "text": "Policy POL-001 applies a **CAD 150 deductible** to accidental laptop damage.", "phase": "final_answer", "index": 0, "id": "msg_07082eedd1e30c17006ab36c69af0c87d2a820c59cd0288953"}]</t>
+    <t>[{"type": "text", "text": "Policy POL-001 has a **CAD 150 deductible** for accidental laptop damage.", "phase": "final_answer", "index": 0, "id": "msg_031f5ec7cdea1be9006ab486701a4087d2b76815b73471d4b4"}]</t>
   </si>
   <si>
     <t>Turn 2</t>
@@ -406,20 +406,20 @@
     <t>R3</t>
   </si>
   <si>
-    <t>01a0ccdf-7e2d-7ec0-be52-f672b489bf5d</t>
+    <t>01a0d12d-273b-7150-842e-eb613abecdf1</t>
   </si>
   <si>
     <t>What happened in claim CLM-001, and what is its status?</t>
   </si>
   <si>
-    <t>[{"id": "rs_07082eedd1e30c17006ab36c6a91e487d291b0070519dfeb29", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2xqshp4iPvmBWxI90sWbo8z5NLcaqpqaKOnv4jPrKjvw-flhsPPBIunv0eFeyXmhVioIFQogny9Zl63Ds_Q4iUhHut8X5RWnYD6W-JxSAYNTJ-GWinZPcnDUsvnIpCEszVA1DOLjXwuXGhqE2_4KhcUwDuBEltkKyHnF03mU8yZybVri0HHh7khCSDC26YhVux_vfvB8eOR1_GpdbqayP_EYogEICSGNHMBbx4Lmxe9pkSf51RA6ehc9eOsiyc5KqDtCNgiOpMWlN5Zd5_X9LsTzpS2DtU3z375d1r0anHlxeokobBqQ1nSCGdq-INg5Nk4cdt7ldxiZCIrVZt2BaBxyz-lTWphsvTZ1910mUQEkunkmhQ8jPWfKQm_r4ObZUQ5ACh6iUyamldP6jm1T-6vAe7fpAPFFu3jbMjgRicT5a43aET3UJGkmGxqvzOYsPScvCOs7NgOjHiJJkxviGmeQn32pyfa-5P2YnbEMntuzv05WVfcPNJBSR3cp0gm4DKmrj_xJ6xm3rRPqGrhzsXStXLZuG9wCLADZm1G7qDXU-s0bQQmkxouSQJzePXLkiOWvO47B4tjoeR3aWMAqNEMrPcxZqOcZjJS4-Z-z4Tg_E8jC6uQ0Jqj9k6LJLNE2_JLqb_79DBWoVIXw6LiaB9CPCCaI_JUKij51E4WyKkIO1QjT82pCVO2LtEjwv5TLxfiaL21Nge-CENYw5-AjGxUk0myDYEv4pJSsbcUWmVldPEA1kaUvxM_jrvF9_abBx3eaubkRpYWl7qz5Qig_ygstMJVJkZ7QOaIV4deRA4QIIElTtRb206eGDFUtjaT-6CKPANJ2jG2jsK2YdQnoef6nkQMLnau9itwKbKmoBd_ExoEmfqRrCWmmlRieM3JdwVoiLFOZTbO4oluKn7UVtPIe-dwwCj54DCnVfqqa0ZOfUX5xiqv1azttcLR-x9o9mN0Db-5Wu7naySJUrd3qUVcXN9AKw2i7b0sfc42Q3DCZvkIjTYXxjqel9K1VFS1ZMXub8WJWaRkgFPuP5NrF_jRx8XbA8nExywQk6z6yQLQjZcDB2TgiAQi7iWf6DRTJVsFDp3CCkjTwKiQR95rftMsfAxVhdKGT217llSrs9lHzXEXOcOQhUlDAlY54Ug6yyMunyLDxtTZmCfFN7hEwL-2DqNaX4oMhTWvPSDoUJ3cXwQoymGj_nX8FgjeHyoGkt79"}, {"type": "function_call", "name": "read_claim", "arguments": "{}", "call_id": "call_1Aw4uAS5H0P7WgtStJvgFw9s", "id": "fc_07082eedd1e30c17006ab36c6ab64087d2ad23691b76c7f9d9", "index": 1}]
-{"name": "read_claim", "args": {}, "id": "call_1Aw4uAS5H0P7WgtStJvgFw9s", "type": "tool_call"}</t>
+    <t>[{"id": "rs_031f5ec7cdea1be9006ab4867115b887d28a1c2e005291db83", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIZxAUD5wl2_4QTY_8uzk_GICRyVXUtk6fdqmUoj1V6GCJ6sLIIX3jkczNSC2A0D6GPWkvExAzuMooOVcRx2aLhUNrKjxAoR7UePIqODLrXlRsYMqNMYRWdZVJmXvdA8g2VHPM3TZA5OvYOQtZ6SdukBOz7PuGyVfN61-MISRn7K8v-HUFj27B2IeuexqB58mbCOCeCwV-vs0bz4zRUHw4u-63-D-LcGeKDYOWn9hj2rQYT2xqdGgCXI55qKXMPVmAmLULW1dNGTeDJ01J0EcL2uieak3xUrMc961lEoCpP7nt4-R0xnhA2RqVO4hResYhCRwPThbCD1q1yDr4vTlnPlWbvDcFkRlw5CK95JNYfJ_R30zrC6xgMHxTahYvkfLuZOu6XhswCMau6mQqVMgLAHwp4k9mNUpl0zxT_sOzs3e52Faq3T_aZ9_ivpXNVTddws0lOzcByaPpM3_zclyC1FqayYjhQMsYDAKFOge78gYZHG0v5gfOgLpOdymAbdlvVx7Q1Q5jewLsq99OvovlOcrWV8ymDqx4DmP-rF8C8iQ5mlfbuSjvD9NfFPAGrThE47_-BWCNzoo7alLecbQ2t49SdVxmLnIeX-KS7swgus0UYU6UGa_8TO1WSTtm_oODKGUIii8t4DE0H9BvMSvVTsMhyw0Uobko1yuja722f8Ph0XNa7mjZK7rs8JaHy_Lt_QMeqa85ymsQ9jd9De7mJ_oMnrUb3y_zshA_2D6KbV7-PUZg5UfrMBRWg9joSl6CGUIwUO84YWZoxS4oli4anFFx2VgyO6nD_eyUC_OLT3zvE2KT8wlhcKVBS8Kq9Lzp13s_ih5YzwAx2_JGSV45rwF2TD4t-uECHh5Fh2NvI_plkTjaHQn6pwO5Y0MxITWTEC9BLoTV1tmJHtDzqRkdaEWhTZF-6EkLs6uJjReq5ej1PD32zRcBkHes2P48OC89ZRwpzTZCxSl0pT3vgZfysu7M2zdyNZAZG2FGBBStdBUtm2kQaUSQ4JRrQuf2p2gQ_SFtbkMSKMXAlemF2BpQSEnKeWHrEMXzpAL39XJRT7UAozzqd4T1Nn-Cr2SrIAuu-hp-zqx2f60nywIE_xxtH2hSOKZWUz7bD-JYpj_4t_eSc8VwlnkJ7HnKH-22xI7LBcyCYhEba4t0ewKo8TqWP6TNj99m6gUpFv14fUHMgfT91kjbp2wGYponZJh660UhEj"}, {"type": "function_call", "name": "read_claim", "arguments": "{}", "call_id": "call_DuSuom6wRUS8pW6KzITW5lXn", "id": "fc_031f5ec7cdea1be9006ab486713d4487d2820d38809e954173", "index": 1}]
+{"name": "read_claim", "args": {}, "id": "call_DuSuom6wRUS8pW6KzITW5lXn", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Tool · read_claim</t>
   </si>
   <si>
-    <t>01a0ccdf-81f9-7e70-bb4f-af13695319a4</t>
+    <t>01a0d12d-2b3e-7b02-aa6f-2154e18c2920</t>
   </si>
   <si>
     <t>{"claim_id": "CLM-001", "revision": 1, "description": "A laptop was stolen from a parked car.", "status": "pending"}</t>
@@ -428,10 +428,10 @@
     <t>R4</t>
   </si>
   <si>
-    <t>01a0ccdf-81fb-7210-9785-74cefa828dcd</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "Claim CLM-001 concerns **a laptop stolen from a parked car**. Its status is **pending**.", "phase": "final_answer", "index": 0, "id": "msg_07082eedd1e30c17006ab36c6ba2c087d281aada49443168ed"}]</t>
+    <t>01a0d12d-2b40-78b2-b342-cdd09704103c</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "Claim CLM-001 concerns **a laptop stolen from a parked car**. Its status is **pending**.", "phase": "final_answer", "index": 0, "id": "msg_031f5ec7cdea1be9006ab4867225c487d28f20758a26eafdc8"}]</t>
   </si>
   <si>
     <t>Turn 3</t>
@@ -440,20 +440,20 @@
     <t>R5</t>
   </si>
   <si>
-    <t>01a0ccdf-85ca-7942-b006-a77c9cf29b13</t>
+    <t>01a0d12d-2efd-7f30-9329-e9637c1b867a</t>
   </si>
   <si>
     <t>Correct the claim: the laptop was not stolen. Its screen cracked when it fell from a desk at home. Replace the description with 'The laptop screen cracked when it fell from a desk at home.' and change the status to approved.</t>
   </si>
   <si>
-    <t>[{"id": "rs_07082eedd1e30c17006ab36c6daf3c87d29cf9c38b92688408", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2xtM_EGBKxqbSyXXEC7VkOh7NRjtIDeVuMKKNgkjcgIWexpGwQioMrTk1nx7t_UXHrIfAEkrN6a2v6jmihYg6mHR4qiibxcvh1P8HVbKalBjhZZxCET1AtGjRfHzAn8pwBBU0AoLpIztlF1S6L3me6qeYGRKRLEAhnrfFmYCqnvr-AawV5GuQ3jBDFMINXURcPP5HGMH0QEgkJsoY0_ExTa2cD0Fgmoe879IiiGWGlZECFGnFOea-ySA-kaWibtL9rxC_yUfw8HteVFVrYOuuwI61h3MxiwCye5IvQULX5eGR6HMOOJfwnUNNDNdDbL0sb47UVsIpkG2EJL5icDxqz_6aViNpx-_39TPXouKtEvb-RZxhnqSln71KyOMbUoLcihVftzbdPRMlxXlYqys5UYNxgIK-Slz-37If0g-hHicT2dsYX94Mu_lD8wmdAsN_VquErJxWyWWLWO2lgHzRz5QvYtWpVIZvjZKxXyyfulRdRijd2M1-CDtiyPejfuvReVacpKaEv3dXi0CSUJM-eBw6370BO6aZg9InorLW0AemanLx6vsj1k1Dy0jrBybAgQTYcV0Zfn4b2MsN-feh5kTjE7fMdG4qIRAIftSiGMhjn9UaIlq-Fn8qm1PjBWrJ6oMtktxVQ44mzM6fnLR9U_R9SfBGMjf4wuD54VrMF8tuJwvF8yf6DAq5AyUAk-wOFRKBWaBf-gt2Lh9P9ey0RNILTSVkciuwvWdFJ0vMjNJKxecIrotLS8mRX0EnvoU6GAK3oa8BT7WSuJe7WmcP4nr6cOlmij45w40rlEhpg15Q-bX_nTi6yC2ULuoVic12KKQq9kw9mWphjhMCTttJWFdNiApkd8gXoGILNhggVSolyUGAylPg04a5_eI_j65ObTvCdE5O4_Fw7OY6ixSYasZ4G-1siIC1e_8kzZMC0OVteo1L3Dzm2fzieAutdqApmJv-Swk9wQlO0LYRNMgrGjwVMExT_vKV_HE6tg56R-HqVEOqVKtQGVtehJf4S6TxYXUHkA0ND5jyOrs4RN6bIYtinnkD8v48aDo_EO2v3EMPlIvWFPcMpdaXmzrZ1mVYekaLhb9mvlVxOq4LwW3Dh5Dm8PHL9TtzpgNp_b10r9gGxeucXQWoDtRmrw7W8oGqOSwW_nEi5WhEtdCprh5mfI6IwB6woBDFgCL7EWWvjqZdnApG590wgsizMu6Tcn_P9xcGvW7TlxXfqVRK7qg20YpdbCzONgwPjfgIGzDtOgU13VMbycMiZhqw3kzFhE5G28"}, {"type": "function_call", "name": "edit_claim", "arguments": "{\"expected_revision\":1,\"description\":\"The laptop screen cracked when it fell from a desk at home.\",\"status\":\"approved\"}", "call_id": "call_JZtZ6TaRffjmWnigmaIrd5wp", "id": "fc_07082eedd1e30c17006ab36c6df64487d2b8538dcf1a463412", "index": 1}]
-{"name": "edit_claim", "args": {"expected_revision": 1, "description": "The laptop screen cracked when it fell from a desk at home.", "status": "approved"}, "id": "call_JZtZ6TaRffjmWnigmaIrd5wp", "type": "tool_call"}</t>
+    <t>[{"id": "rs_031f5ec7cdea1be9006ab48673541887d2ba6042d4c7f958dd", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIZz2w9qpAsq2g4rVeLwSeDGHzvhqFdiTKKmxb3f9dZA59dRKBE53t4Df7tFmG7Apah5eSPF8IrWRqKPkZJbpLYphy1v_FG1vnFTWHuvBIORASHwqc4ZiY7Wl4UWqpn_0qxyuhZ9_c4RzxeCtP0s46DEqX5HlvmsN2knuEkG7qFspLNCAinLnp81flvsUKd1mH2X61v6RRnPd3motixohnY8CAO7Dl-2w8X0gDZCurtZmeCP2qZxYrIJ6E9Q-qU22tVf2NUbku54V0dAnQSuUmW3iwf-JkYDXSB5Y7erDMpywwNffWuqi05HSnJp1Q-lFzlT95uvzR5XGxzF3kZ22A4oiMDG8sQ3GAOsKlNZOt4My84pPpMu5TuhYbh6lNU4r3FiV1SnObnEfS9rvk4i11RfNpAZG6qGg_OI7xWeRMCsXjKZXG9Rot3sOC7BiAnsw-J14L5LR2VVB_1aZ6h6PYQJ3P-QzT0t00JqJSHzshoRNekY3yAVPpQXSsXxAP01Uf8hEmlz5Sfm9oVUZeZvQxqVTVNC73WIZaYukJ1TphuzHYz3xQvCjDZKAWj2w_laClqTr-DTBofz6otJNetyPHa0oVya5AGjpGrjZB-A0A8lOdT0PNcs81v81M7S_uTgGWd-pFVIyxkoYF_Imd9G67vj5HKnIti8rXvC903cw_792zzWslR51OBMm69TYUtxutoSuDbn_IJeandJ16MK7ObNO_QXjVtvndmoFokypUY9mYtINi--QiICQLIN46ASiKETFbT9zyScDQt4JwLXdHOQ_mAOmrmlqQot-M17yKw327Jywbr-zK2y5h9eTaI9sug-5pm-BvNQN4ovHiCy8YbRWm_I1sQq6o71CKYpPl80JVPhSqadPPBH_Biij3Y8f2EVeIxQsp5-VagjhO692jIR14DdOZXrslu0ZIczEZpAYgAZWmOq8q90CHWSIj7rlRrfnxvCLVDl1sIs91TftuytAJZVS8p6WzaND1VmnPHOutbwT3GRPgc0foFCLPLXNTutPtElz0KCZzNJR1CD2VqATaRp0SVpFpWgYME4pdfqkEsliwUN3NqUcw4Hro8qCQmo0EaR0ARLNxZtV-0WvlTvrY2Fl5GZDTZ7gNwBZ_IhuBCaaIwgHaIurZRl9agGUSIA3OVOqn3VA6PN5zzrgR_59DDO8uHqHRE48WqNBljIn26x1rDDxvGpcxBazymY3cFKcR_wP7v449wuylNppmkOqNcqEK4rJ6x9-EnUClvc-8qdohM5o72IzP-VO1_wpUx6"}, {"type": "function_call", "name": "edit_claim", "arguments": "{\"expected_revision\":1,\"description\":\"The laptop screen cracked when it fell from a desk at home.\",\"status\":\"approved\"}", "call_id": "call_VTDitpXYnkdr9RGPn9seKZaF", "id": "fc_031f5ec7cdea1be9006ab48673915487d2a64ae7cda5f7a781", "index": 1}]
+{"name": "edit_claim", "args": {"expected_revision": 1, "description": "The laptop screen cracked when it fell from a desk at home.", "status": "approved"}, "id": "call_VTDitpXYnkdr9RGPn9seKZaF", "type": "tool_call"}</t>
   </si>
   <si>
     <t>Tool · edit_claim</t>
   </si>
   <si>
-    <t>01a0ccdf-91fc-7641-a5ba-b3efeea24ac0</t>
+    <t>01a0d12d-349e-7133-92f2-595ff694bb24</t>
   </si>
   <si>
     <t>{'expected_revision': 1, 'description': 'The laptop screen cracked when it fell from a desk at home.', 'status': 'approved'}</t>
@@ -465,10 +465,10 @@
     <t>R6</t>
   </si>
   <si>
-    <t>01a0ccdf-9200-7122-adb3-21537727f466</t>
-  </si>
-  <si>
-    <t>[{"type": "text", "text": "Claim CLM-001 was corrected: **\u201cThe laptop screen cracked when it fell from a desk at home.\u201d**  \nStatus: **approved**.", "phase": "final_answer", "index": 0, "id": "msg_07082eedd1e30c17006ab36c705a8087d288394620700d45fb"}]</t>
+    <t>01a0d12d-34a0-7ef1-8f6a-7ca70a7c67ea</t>
+  </si>
+  <si>
+    <t>[{"type": "text", "text": "Claim CLM-001 was updated:\n\n- **Description:** The laptop screen cracked when it fell from a desk at home.\n- **Status:** Approved", "phase": "final_answer", "index": 0, "id": "msg_031f5ec7cdea1be9006ab4867476a487d28e00b1c123b33137"}]</t>
   </si>
   <si>
     <t>Turn 4</t>
@@ -477,13 +477,13 @@
     <t>R7</t>
   </si>
   <si>
-    <t>01a0ccdf-9a1f-75a3-b72d-785facf51d68</t>
+    <t>01a0d12d-387b-7881-967b-ebb7a84d6803</t>
   </si>
   <si>
     <t>What is the policy's coverage limit?</t>
   </si>
   <si>
-    <t>[{"id": "rs_07082eedd1e30c17006ab36c71f76487d283078a5f4805493c", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2xyTX-aa7sMklQD50gAQz6y-sXfxPpK8tg2vn9Cz1uGWSqPdl6y-Q53rPV3KiyjWkS7he2sJrAHRnZTmOoyjYZZTcVXFH5OV8z_RV-x6XyT6IWFnTpdJFqVoGddMJMRZDWxgam5_VSEoeRiJFHm10zHkd7YD_-lMYeMaow-51Bh047_bhJ17ONUqtRbN-FLD5SzBd5IaZBTgFcNNqGbUUcQIDxRgT9Mz2lgr_QjErd_7XU8ev7IF0A2y_rOln8w4aVSUwPQxlBRAb9cIqvAz0PhsOCmijNLg8N-ugYgnzYsiWjkH9L4ZBRC46TS_UN6tBvY2G03NtGIaxSL5kQQHjlthHHAQRwjedTbLqt0B0JW3NbbVZQ5mbzTSoew1OhKcNXtTyflKLquL4ga-7jC32kj37EqR85jXf8B9O3AdVNG3ym3XciFTiIvqZnQW-m_yot9tGFt8K6NqD2I0nfIc9YCkHybI7rikBZerZfInNAoW-0LF-AuqWjsy0EmVt0nLgR-FskvQi_hfUfMpet7NJVVkavsUzR30-MiY-Ts3rxEbowcJewslrK0OMwxKiXbOh6MAzkzLoYg7vnhNLAIILgTcfz1Mf8hTT7cojhMRf7krCdNZpiAQ_HZ76xZxg5wnGOZqaAAjLnDJ3iHt-q8cot7y75c0I3gQhgPe1CrT1uyQp0Tro_MK3fS4jlp7zyXUW7azANUbJ2i0yihxrGtdVxWJdijV8ZtZNO1D_l5iMiDH7DK3QQqFO96VOcW9dRxFc4uukUrEkGxX7Tim4IifuukrA6b6juG1qlP6acZqOanbcKzQPoy19bLkZbPcpnoUg8uHomXNMW47vNQGgc5pzbsWr5-lMPQpZMuclAh4F-bV5lkKTBJ4XRWj9v9NuufNifIf8tlzVy_UtNLPqGuF4eOM6rCR_zOAOdAX8KrMZ2ANIsx4VxuVmxDT-JmgRyt6YnSrIeH-w9lpZxJCVvsGtvSg3Wb7sYSLCuohDazDPvCN-fliiVvmbU_rIBl6UAXqAg1T6LfuuXQEcAOA4kGnxz6fS0qp4q1lewLoEvpIwLXbM-Mzi3B_Nkl5g9aRLlNDhrCq6vuAJkv2HYHOEQqvS7mzuDYNOvjnRDDKxOg-9QDpXZ5VRfknWtNXrfYN2n0-SZO4swytx-4qeP8AA1r8jNfhcmjwpOUJ3r3X9UtwdlNxJhIPOG3bcoGlVDFCAm2zOhkmLFu6aMXPJAa5o8RQuz4HCVzINMfhl_3aa8CpUa3CRatJsC2vn9oqLA8uWkxj9fX"}, {"type": "text", "text": "Policy POL-001\u2019s coverage limit is **CAD 2,000**.", "phase": "final_answer", "index": 1, "id": "msg_07082eedd1e30c17006ab36c722e8c87d2829b6dfb1daaa6f4"}]</t>
+    <t>[{"id": "rs_031f5ec7cdea1be9006ab48677bd7487d2a76a96e7e2d87a88", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIZ47Gh6hjLUGEoXlPAiGrLD9s6Y_CORknz2aD0emp3ur_GOOwYsQ1WwLmhn4efhpXcV3AcTuYzIrUNJRixlkcBCC-s9xBGHIfk1uRw66eQdx1w_4E7snYoaVNVnpBwdiAJgdTBNKeWLCZKplCDvFPNhzVXzbhD4_c-RZtUKSXDjVeA5_AQuZ7ZrrTNRbHo6GfesmAXsCqy_IoYY6VFj2Ky8fkfWDpVHE9R9Gjg9v1DnArk_wFhrp2MCHyC0IpQJfxtCum5ITiQQ8Ln5gqPuBhR3jyE7bpMF7l7h7t5v3G2ETMsZ2qkUF5mTs_Ar3LgyiT3Y-OaAKygQCiO3xS7gQs0QhaPJvUeiMGc8z5sHJ6DCX-U6ZiY8cVstKkCd4V-h6RKwZKyp8o02jTFFa0bLuA4dxgfJQ_cq2pW7po9srBrlVcebkvHPiOW-GefYpJNw0dDiD_qEtDsCnuuNpK7VglNHn9HsLUnAcy_abevs9R3p53DY1sSfcir3Pfiy-7pghgWFXcs7tYNf-GLH4FUOwd6DnWhqbxYM0QOTgyITUmt9NIJOjAvmBUl12Veyu28GgoW2NZjY8GfKB2nsuWkQF2V2gRay_x5HZUaX30LBSvTTLuPKgQ2hQxxUFTYNLLBtyxnep_OOl9QpsnsMjjcwuV0HalpFegtWdt86A1vs0GRECbvACnzrmh01KGMcHFvXAk2UdIjp3koLO-5QLQD1PbrBdKPDgkN3C-jb2MK1BJ55fTB7Nxz9UChDov8CPa7uZiPJp_lYRdu82y4k2sD9-PYKj23AYQRiQyC26lPVWlMF_o1c8lKmUG6ot6LI2HbVyyoaGsZtW-ClD71ZpRcoelWL_ibiQ1ZkhN6hG5BL7DiX5q5rHT7fK5BA-OYlPCX6IkSkkdBnJqKIajDYHgtK_L87LuZcsPcsUtrtTVhjZYxQ4ht_vl2AZjIgGIy6axbGelcPDYtghlR1-8-7GkGn_FRvCfbJJk2Ikrfj1KT9YNtE1BE3YG07pc-2ZjpCFgcgRWlUFKpUalf6Czad0lj-cl_5UTD_OzgJSvHqYhV8_6GsDwPHZ231S7umzuznsAtYAlR7iPtub2gniBTIEFbhTRW1IHddDUuRoWxrtKm0fkhks_jL3VNDI_yd-Qt1lcfS0WheB_Bnr7f_7G04VkZwi4B0mJjZGpzRO1qm7j6i1j-fTU_DinTLE3WEgku6vcsRRc8jc95K-mOwHuGvZbkrOUJER3JH7weCtRABXaJIW0R-2Ys="}, {"type": "text", "text": "Policy POL-001\u2019s coverage limit is **CAD 2,000**.", "phase": "final_answer", "index": 1, "id": "msg_031f5ec7cdea1be9006ab48678105487d2be931efaafc51690"}]</t>
   </si>
   <si>
     <t>Turn 5</t>
@@ -492,13 +492,13 @@
     <t>R8</t>
   </si>
   <si>
-    <t>01a0ccdf-9fd9-72f2-9693-da133696e5bc</t>
+    <t>01a0d12d-472b-78d2-9109-57ef484b06f7</t>
   </si>
   <si>
     <t>What happened to the laptop, where did it happen, and what is the current claim status?</t>
   </si>
   <si>
-    <t>[{"id": "rs_07082eedd1e30c17006ab36c73399087d2a5486ca28bfa4857", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqs2xzEPedItm8rKfxfWyfxyR3S0e4r78-v99CCD-eRTCPGz8oZnBtSRVgbG_1l6FkB-N4K8z1_pIPbTFA7JB77pvAa7o0SlOgTesuzBzZtboNXM6gFJt76xs9bacNIUkvNFdOQ2rvbiTIIgx2SLXWztAL6f3atNexyyP6892yOal86fHWcYwKcbLPcgU49OS9yHj6dG9RMkXzpzgxsPCPcf3nNnL8s7WGDqT15Bx-xdX7fSVtNCf6e5VuDgoSA-YG0hEg_lor3YE5dZLaghcEAnGqS6nlBxx5MpkcAOT7qdmX2BB7FLsY5aRn5Ld5-FScqJhJfhNtOWuwUNx0wJwWE0XoIdTJXUfGUt8i97n_kDpR-rI7WpBMXIMzpKPMztUJx5bMEQV00QddQpcQVLSCmohmvgJY7MobmfMg60BHRr4EI6QPSOW0kZQBmgYMX4LbIU4YQXya1Lu5rfOzyvffiGvEKTyKqgtC8WYHHtAbtZM99823Qfm1PC6oBTR8fXf8987DXtlei79kNtnt4IsyLX-OwzcCpf8TATZb5Nh5D2eu3dhqNylQaLeTnADZlvX3oHu1efLG8JLNFFygpQIJ2e0CO3g0CPpGfdY4Q02OUoihkwFZCuX-lP7DKi6B9QUqxPSQ4GgcQFy5lEftN2B2SbjSWO6b0CaSprlKBXzChHy3rAkFQaPgu14iQyJ9aq_hxbwEt86-7_W-V8GgJlQh-40mRH93teV2exNfG5JARrotkg7TTS2z6zgfRywWLI6r2BGC1xlAEdXddkjCACTcSP45wrg8USEbxMja-KDhzlk1sgfVD7HaAHtoOpoS6UGBiz7mIvxGUikt1lSRkvRCYrvXLqzUe1mXyqD3BclVvaeMRZL4KNAllPG0EJYcJTd6HCHWIACGZlJuwJNXHu3nBF_ybkEaRbjjiD2mRvtMLPLtNr5p6KU6lf2ZtTPsT-3sXfVN9_q-dlwWPVvKv_K-DtLNBtgknsPYO2wO3_OEKkTgQsr_-A5bmU_Qs1sYdK8tuTaiu7ZLZUShjF2dk2MxF5Ut0gqo6Tdo5wtlPvrdzHRQo4gskzBnMEyJGCrmisk0evET-COpun9Jmx6TGd9oTrFbbMT7fjRf6YtjNpN02yd2Sh8twFDY8XRwbuWUXPUijWbIh5ITArqNe1lO12NU5sTRXl25VV-buAC9oUvUmK8D3ue2fNexCWI7coKx6gRuikPX5oHjTbWMy1lx7GA2OFpv9vce6RL0K2pjAvZMwwMsQ8fIRj7T9Yu46SMG_5TVH70F4MvH0Y89QdRrJH286P6a6iX3AUx7OFWiKTiBfsVNEZAnOQGbDuFsGvK_LT6PvE5RtGFe-c8gy2M0Y7RmlL06ry4d7OrX3bd3RKl47i2VoPetbd8sV0x-JcnXEY4DKfzpksE47CD8cBpbDZErzkOI8GXajE2DP-_SmRkesWlTQ4A5oH80DaUeP5LFDK05fuZ2ZMPxKLjsZJpbzxsc8FHOxw=="}, {"type": "text", "text": "The laptop\u2019s screen cracked when it fell from a desk at home. The current claim status is **approved**.", "phase": "final_answer", "index": 1, "id": "msg_07082eedd1e30c17006ab36c73b1b487d2bb82755d1801cdc4"}]</t>
+    <t>[{"id": "rs_031f5ec7cdea1be9006ab48679585887d2a59dc7568183e1d5", "summary": [], "type": "reasoning", "content": [], "index": 0, "encrypted_content": "gAAAAABqtIZ5-XLJeQofZY8w2lw4mtq48UEKkbK-U8tIKcscd9Sf-pDYSxNx9sj_-CUJ9i8XgN3zZrUDDNqt1Xty4_BLctPU3qoStcUrf1IpeX40uVMv2l721-3_vpul00VHh4FEfWwW-Wk93gGd5mS6uHrpLY-dhpWYm2sw9OA-KtwllDdCfUUu3WIz8yrsmvyVDov_yYHoAQBFQ_qTI4wlwSuNper5knV2bmYPbCr2hcKkKVwzS_4U9auk-bec2YUWMHLLofX0Kp6LHxetGtVxZS3W6vxGChHaI9bB7w8Uj2D9hX21jRAA7tg1mbGukBwDygd2YsxzfZHA_lDkhCl_7ScI7ngaPExBXoqgkNSRNKQiuStqVcsviKZQHiGtQoW7v_SrSwTxE85woZlSdgsJ0kfeqXY5F_DMt-BL12jFCL6DlsqFwritmwRz7wlgE_ro_jG_vNKPPU9yW9onHfBrg5MkoisBkbOSwk6t4FVzP1geLPotWU18KgJTcDWXx_JWyoW5dNLROXOchlG4wH0DJrQdv844Xv6HcxMPMTEwT8OONB733e4ckyFa9ev-3pzqupJKOZ-A7yLjk_deqWcpI9KUGhWd2NXQ2hi8CypisCN5qHsL8aOK61-nRb_BOlnsuTom6ZG2p_ThlL_ZlcwMKJuN3dS5nd4BCkT_HuZ6g9bjDRNWgMIwtKovty-BrDrzhQ82RgfYs2Mb8b-j1hm5bgcKRmo7InkGalO1ZiCtdr6NzAIwSEOJmAX8-DTCNCM4IJ5QDPlr_-7RV7O-sMVEt7r7STpObS9mG30CrMKgbmiUjPMK_AxBB-QrgQgawD_cl_72EblWAFR8b4GlpU30D9Bz3Kl5vCdkgWpI-P_Nam0QOv35z2VkSaAIsf4oOeIaPDP8t8rU98OICjkQN9cR1i1clRzqmCix0SXqm-b0E01noSylVsGEG_Vwm4EgwT2aDKl8v_sWTNOraaMmZniewMQ-Tc0EfBU6u6GHA1tfseB-0qzWEfAndiKXWRrqc3Mvin_5xh3Nsk9uGKOiVwD69eEZb_KoHV53sWIyeF9LzOnHw8DjYBFH_88oo5Ry8U2WKM1Vqvof0K1u0hh3bD57PBW-ahp-sUe0uRd9h2WpbHhSA9M3z7k3As6hSbydbvH_PPU2xmkjU1WKNzUT2uGX1XyyQww_H52pp7xOt1c1fnXkhAF20bv40K2Lu0f49quvGbV1fgDOcTJo0JesI3FX8X1-xp6R7Iju3poQf8qwRPpa0nFSaarvkIDRJThkZ0IfXTCubMN-Ms1No1T1_mbqvvo5EAz92Pk_it8MDPM7y6C4zt-iwrsUhV9qUm0biZaCEWHm-e2QG6UJ0vG9oajF90WO52jGUmh1g6JVoWfvLP9_eGXDgG8RHCdh0F87siWN-LAvhHhtHrj2FqzptJmnPclfRIEPulMZ0Io6-yD__a9pZFihtNjbCLDx-gx-DJwvDf_J9akMnU2m07CkFJUAS2QnpQiTfiOq7I3kyjZrgsLkfax4KjU="}, {"type": "text", "text": "The laptop\u2019s screen cracked when it fell from a desk at home. The current claim status is **approved**.", "phase": "final_answer", "index": 1, "id": "msg_031f5ec7cdea1be9006ab48679e61087d2b1390ecefad45efd"}]</t>
   </si>
   <si>
     <t>LangGraph</t>
@@ -519,7 +519,7 @@
     <t>Execute the claim_turn workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0ccdf-760d-77d2-ba3c-2a3ad3f0984b</t>
+    <t>01a0d12d-1e53-7be0-b0b8-53a90d08795e</t>
   </si>
   <si>
     <t xml:space="preserve">        claims_agent</t>
@@ -528,7 +528,7 @@
     <t>Execute the claims_agent workflow operation and pass its result to the next graph step.</t>
   </si>
   <si>
-    <t>01a0ccdf-760d-77d2-ba3c-2a4f6c885a25</t>
+    <t>01a0d12d-1e54-7ee2-bccd-0b384ade44ec</t>
   </si>
   <si>
     <t xml:space="preserve">            model</t>
@@ -537,7 +537,7 @@
     <t>Prepare the current conversation, run model middleware, and invoke the chat model.</t>
   </si>
   <si>
-    <t>01a0ccdf-760e-7852-89a8-45b668666213</t>
+    <t>01a0d12d-1e55-7160-a850-597a38161b0c</t>
   </si>
   <si>
     <t xml:space="preserve">                ChatOpenAI</t>
@@ -558,7 +558,7 @@
     <t>Execute tool calls requested by the preceding model response and return their observations.</t>
   </si>
   <si>
-    <t>01a0ccdf-7aee-7121-ab6f-b9cd597b28c8</t>
+    <t>01a0d12d-2339-7822-a861-c43b346de319</t>
   </si>
   <si>
     <t>No model charge</t>
@@ -573,22 +573,22 @@
     <t>Read fictional policy POL-001, including coverage, deductible, and limit.</t>
   </si>
   <si>
-    <t>01a0ccdf-7af4-7763-940d-545dbd65f092</t>
-  </si>
-  <si>
-    <t>01a0ccdf-7e29-7952-bdcc-47c584c519ad</t>
-  </si>
-  <si>
-    <t>01a0ccdf-7e2b-7563-9c86-4ccd1856cca7</t>
-  </si>
-  <si>
-    <t>01a0ccdf-7e2b-7563-9c86-4cdd14dc2663</t>
-  </si>
-  <si>
-    <t>01a0ccdf-7e2c-75e0-9a3c-06a00149a100</t>
-  </si>
-  <si>
-    <t>01a0ccdf-81f7-7c93-9f06-a765fd98bdb5</t>
+    <t>01a0d12d-233c-7230-baa8-5e4a9901a142</t>
+  </si>
+  <si>
+    <t>01a0d12d-2737-7bc3-9504-f39d819f8101</t>
+  </si>
+  <si>
+    <t>01a0d12d-2738-73b3-95ec-b364cf473021</t>
+  </si>
+  <si>
+    <t>01a0d12d-2739-7f11-84b7-c11d17808b84</t>
+  </si>
+  <si>
+    <t>01a0d12d-273a-7e03-ab9c-8a3ad8805aec</t>
+  </si>
+  <si>
+    <t>01a0d12d-2b3d-7161-855b-a1eaf6ca3e27</t>
   </si>
   <si>
     <t xml:space="preserve">                read_claim</t>
@@ -597,22 +597,22 @@
     <t>Read the complete current claim, including its authoritative revision.</t>
   </si>
   <si>
-    <t>01a0ccdf-81fa-7ed3-94c1-3e274cf39440</t>
-  </si>
-  <si>
-    <t>01a0ccdf-85c6-7862-baed-301765d112aa</t>
-  </si>
-  <si>
-    <t>01a0ccdf-85c7-7782-abdc-78fd513c3777</t>
-  </si>
-  <si>
-    <t>01a0ccdf-85c7-7782-abdc-790d370859b9</t>
-  </si>
-  <si>
-    <t>01a0ccdf-85c9-7182-aa0c-9dab604376e6</t>
-  </si>
-  <si>
-    <t>01a0ccdf-91fa-7292-931c-5e558e69f89a</t>
+    <t>01a0d12d-2b3f-7081-abde-bb662757156c</t>
+  </si>
+  <si>
+    <t>01a0d12d-2ef9-7992-a850-011af4be24c3</t>
+  </si>
+  <si>
+    <t>01a0d12d-2efa-77e3-8a32-6e0cef98f89e</t>
+  </si>
+  <si>
+    <t>01a0d12d-2efb-7731-b4ea-c2e5acf70592</t>
+  </si>
+  <si>
+    <t>01a0d12d-2efc-7b92-840a-699fb5fa80cd</t>
+  </si>
+  <si>
+    <t>01a0d12d-349d-7a82-9224-7863c1bbcffa</t>
   </si>
   <si>
     <t xml:space="preserve">                edit_claim</t>
@@ -624,31 +624,31 @@
             revision, not the resulting claim contents.</t>
   </si>
   <si>
-    <t>01a0ccdf-91fe-7a30-89f8-706639ebafe2</t>
-  </si>
-  <si>
-    <t>01a0ccdf-9a1a-7593-b981-9be74d1569ba</t>
-  </si>
-  <si>
-    <t>01a0ccdf-9a1c-7143-860e-a0bd5d609eec</t>
-  </si>
-  <si>
-    <t>01a0ccdf-9a1c-7143-860e-a0c6a467b237</t>
-  </si>
-  <si>
-    <t>01a0ccdf-9a1d-7683-9cd0-332f961394f7</t>
-  </si>
-  <si>
-    <t>01a0ccdf-9fd5-7193-84f2-d72f72501a4b</t>
-  </si>
-  <si>
-    <t>01a0ccdf-9fd7-7050-9ea0-a98df021ab5e</t>
-  </si>
-  <si>
-    <t>01a0ccdf-9fd7-7050-9ea0-a99fe0d9a3fa</t>
-  </si>
-  <si>
-    <t>01a0ccdf-9fd8-7640-9a8c-046a0981b8a9</t>
+    <t>01a0d12d-349f-7ef2-9ec5-8d8238f353f5</t>
+  </si>
+  <si>
+    <t>01a0d12d-3877-7e01-aa3b-0c02cb0a5dbf</t>
+  </si>
+  <si>
+    <t>01a0d12d-3879-7840-a023-b65eb731d72d</t>
+  </si>
+  <si>
+    <t>01a0d12d-3879-7840-a023-b66b60c7adb4</t>
+  </si>
+  <si>
+    <t>01a0d12d-387a-7c22-8f01-9d6fcee1fcf2</t>
+  </si>
+  <si>
+    <t>01a0d12d-4727-7230-bce0-fa8611a65cba</t>
+  </si>
+  <si>
+    <t>01a0d12d-4728-7ac1-853e-ca07f1e04d42</t>
+  </si>
+  <si>
+    <t>01a0d12d-4729-7db2-8d2f-56e0bfc59985</t>
+  </si>
+  <si>
+    <t>01a0d12d-472a-7441-903b-f99353e09d45</t>
   </si>
 </sst>
 </file>
@@ -1116,19 +1116,19 @@
       </c>
       <c r="E2" s="2">
         <f>IF(COUNT('Turns'!E17,'Turns'!E32,'Turns'!E46,'Turns'!E61,'Turns'!E75,'Turns'!E90,'Turns'!E104,'Turns'!E118)=8,SUM('Turns'!E17,'Turns'!E32,'Turns'!E46,'Turns'!E61,'Turns'!E75,'Turns'!E90,'Turns'!E104,'Turns'!E118),"Unknown")</f>
-        <v>0.001117331496</v>
+        <v>0.00111419139</v>
       </c>
       <c r="F2" s="2">
         <f>IF(COUNT('Turns'!F17,'Turns'!F32,'Turns'!F46,'Turns'!F61,'Turns'!F75,'Turns'!F90,'Turns'!F104,'Turns'!F118)=8,SUM('Turns'!F17,'Turns'!F32,'Turns'!F46,'Turns'!F61,'Turns'!F75,'Turns'!F90,'Turns'!F104,'Turns'!F118),"Unknown")</f>
-        <v>0.0012808</v>
+        <v>0.0012714</v>
       </c>
       <c r="G2" s="5">
         <f>IF(ISNUMBER(E2),ROUND(E2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>112.0</v>
+        <v>111.0</v>
       </c>
       <c r="H2" s="5">
         <f>IF(ISNUMBER(F2),ROUND(F2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>128.0</v>
+        <v>127.0</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1140,11 +1140,11 @@
       </c>
       <c r="E3" s="2">
         <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
-        <v>0.00017883585</v>
+        <v>0.00017842486</v>
       </c>
       <c r="F3" s="2">
         <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
-        <v>0.000205</v>
+        <v>0.0002036</v>
       </c>
       <c r="G3" s="5">
         <f>IF(ISNUMBER(E3),ROUND(E3*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="H3" s="5">
         <f>IF(ISNUMBER(F3),ROUND(F3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="E5" s="2">
         <f>IF(AND(ISNUMBER(F5),ISNUMBER('Reference data'!$B$3)),F5*'Reference data'!$B$3,"Unknown")</f>
-        <v>5.7925368e-05</v>
+        <v>5.818964e-05</v>
       </c>
       <c r="F5" s="2">
         <f>IF(D5=0,0,IF(ISNUMBER('Reference data'!B17),D5*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -1277,7 +1277,7 @@
         <v>105</v>
       </c>
       <c r="D11" s="4">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="24" customHeight="1">
@@ -1291,15 +1291,15 @@
         <v>106</v>
       </c>
       <c r="D12" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER('Reference data'!$B$3)),F12*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.046844e-05</v>
+        <v>9.46458e-06</v>
       </c>
       <c r="F12" s="2">
         <f>IF(D12=0,0,IF(ISNUMBER('Reference data'!F17),D12*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>1.2e-05</v>
+        <v>1.08e-05</v>
       </c>
       <c r="G12" s="5">
         <f>IF(ISNUMBER(E12),ROUND(E12*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="E13" s="2">
         <f>IF(AND(ISNUMBER(F13),ISNUMBER('Reference data'!$B$3)),F13*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.6749504e-05</v>
+        <v>1.682592e-05</v>
       </c>
       <c r="F13" s="2">
         <f>IF(D13=0,0,IF(ISNUMBER('Reference data'!E17),D13*'Reference data'!E17/1000000,"Unknown"))</f>
@@ -1388,15 +1388,15 @@
       </c>
       <c r="E17" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E12,'Turns'!E13)=3,SUM('Turns'!E5,'Turns'!E12,'Turns'!E13),"Unknown")</f>
-        <v>8.5143312e-05</v>
+        <v>8.448014e-05</v>
       </c>
       <c r="F17" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F12,'Turns'!F13)=3,SUM('Turns'!F5,'Turns'!F12,'Turns'!F13),"Unknown")</f>
-        <v>9.76e-05</v>
+        <v>9.64e-05</v>
       </c>
       <c r="G17" s="5">
         <f>IF(ISNUMBER(E17),ROUND(E17*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="H17" s="5">
         <f>IF(ISNUMBER(F17),ROUND(F17*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1453,7 +1453,7 @@
         <v>94</v>
       </c>
       <c r="D21" s="4">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>95</v>
@@ -1503,15 +1503,15 @@
         <v>97</v>
       </c>
       <c r="D23" s="5">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E23" s="2">
         <f>IF(AND(ISNUMBER(F23),ISNUMBER('Reference data'!$B$3)),F23*'Reference data'!$B$3,"Unknown")</f>
-        <v>7.1708814e-05</v>
+        <v>7.18607e-05</v>
       </c>
       <c r="F23" s="2">
         <f>IF(D23=0,0,IF(ISNUMBER('Reference data'!B17),D23*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>8.22e-05</v>
+        <v>8.2e-05</v>
       </c>
       <c r="G23" s="5">
         <f>IF(ISNUMBER(E23),ROUND(E23*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="E28" s="2">
         <f>IF(AND(ISNUMBER(F28),ISNUMBER('Reference data'!$B$3)),F28*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.1983724e-05</v>
+        <v>2.208402e-05</v>
       </c>
       <c r="F28" s="2">
         <f>IF(D28=0,0,IF(ISNUMBER('Reference data'!E17),D28*'Reference data'!E17/1000000,"Unknown"))</f>
@@ -1650,11 +1650,11 @@
       </c>
       <c r="E32" s="2">
         <f>IF(COUNT('Turns'!E22,'Turns'!E23,'Turns'!E28)=3,SUM('Turns'!E22,'Turns'!E23,'Turns'!E28),"Unknown")</f>
-        <v>9.3692538e-05</v>
+        <v>9.394472e-05</v>
       </c>
       <c r="F32" s="2">
         <f>IF(COUNT('Turns'!F22,'Turns'!F23,'Turns'!F28)=3,SUM('Turns'!F22,'Turns'!F23,'Turns'!F28),"Unknown")</f>
-        <v>0.0001074</v>
+        <v>0.0001072</v>
       </c>
       <c r="G32" s="5">
         <f>IF(ISNUMBER(E32),ROUND(E32*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1677,11 +1677,11 @@
       </c>
       <c r="E33" s="2">
         <f>IF(COUNT('Turns'!E46,'Turns'!E61)=2,SUM('Turns'!E46,'Turns'!E61),"Unknown")</f>
-        <v>0.000223675668</v>
+        <v>0.0002243456</v>
       </c>
       <c r="F33" s="2">
         <f>IF(COUNT('Turns'!F46,'Turns'!F61)=2,SUM('Turns'!F46,'Turns'!F61),"Unknown")</f>
-        <v>0.0002564</v>
+        <v>0.000256</v>
       </c>
       <c r="G33" s="5">
         <f>IF(ISNUMBER(E33),ROUND(E33*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1703,7 +1703,7 @@
         <v>94</v>
       </c>
       <c r="D34" s="4">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>95</v>
@@ -1753,15 +1753,15 @@
         <v>97</v>
       </c>
       <c r="D36" s="5">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E36" s="2">
         <f>IF(AND(ISNUMBER(F36),ISNUMBER('Reference data'!$B$3)),F36*'Reference data'!$B$3,"Unknown")</f>
-        <v>7.9036722e-05</v>
+        <v>7.922204e-05</v>
       </c>
       <c r="F36" s="2">
         <f>IF(D36=0,0,IF(ISNUMBER('Reference data'!B17),D36*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>9.06e-05</v>
+        <v>9.04e-05</v>
       </c>
       <c r="G36" s="5">
         <f>IF(ISNUMBER(E36),ROUND(E36*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="E41" s="2">
         <f>IF(AND(ISNUMBER(F41),ISNUMBER('Reference data'!$B$3)),F41*'Reference data'!$B$3,"Unknown")</f>
-        <v>8.374752e-06</v>
+        <v>8.41296e-06</v>
       </c>
       <c r="F41" s="2">
         <f>IF(D41=0,0,IF(ISNUMBER('Reference data'!F17),D41*'Reference data'!F17/1000000,"Unknown"))</f>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="E42" s="2">
         <f>IF(AND(ISNUMBER(F42),ISNUMBER('Reference data'!$B$3)),F42*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.6749504e-05</v>
+        <v>1.682592e-05</v>
       </c>
       <c r="F42" s="2">
         <f>IF(D42=0,0,IF(ISNUMBER('Reference data'!E17),D42*'Reference data'!E17/1000000,"Unknown"))</f>
@@ -1930,11 +1930,11 @@
       </c>
       <c r="E46" s="2">
         <f>IF(COUNT('Turns'!E35,'Turns'!E36,'Turns'!E41,'Turns'!E42)=4,SUM('Turns'!E35,'Turns'!E36,'Turns'!E41,'Turns'!E42),"Unknown")</f>
-        <v>0.000104160978</v>
+        <v>0.00010446092</v>
       </c>
       <c r="F46" s="2">
         <f>IF(COUNT('Turns'!F35,'Turns'!F36,'Turns'!F41,'Turns'!F42)=4,SUM('Turns'!F35,'Turns'!F36,'Turns'!F41,'Turns'!F42),"Unknown")</f>
-        <v>0.0001194</v>
+        <v>0.0001192</v>
       </c>
       <c r="G46" s="5">
         <f>IF(ISNUMBER(E46),ROUND(E46*'Reference data'!$B$2,0),"Unknown")</f>
@@ -1995,7 +1995,7 @@
         <v>94</v>
       </c>
       <c r="D50" s="4">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>95</v>
@@ -2045,15 +2045,15 @@
         <v>97</v>
       </c>
       <c r="D52" s="5">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E52" s="2">
         <f>IF(AND(ISNUMBER(F52),ISNUMBER('Reference data'!$B$3)),F52*'Reference data'!$B$3,"Unknown")</f>
-        <v>9.1249902e-05</v>
+        <v>9.149094e-05</v>
       </c>
       <c r="F52" s="2">
         <f>IF(D52=0,0,IF(ISNUMBER('Reference data'!B17),D52*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>0.0001046</v>
+        <v>0.0001044</v>
       </c>
       <c r="G52" s="5">
         <f>IF(ISNUMBER(E52),ROUND(E52*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="E57" s="2">
         <f>IF(AND(ISNUMBER(F57),ISNUMBER('Reference data'!$B$3)),F57*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.8264788e-05</v>
+        <v>2.839374e-05</v>
       </c>
       <c r="F57" s="2">
         <f>IF(D57=0,0,IF(ISNUMBER('Reference data'!E17),D57*'Reference data'!E17/1000000,"Unknown"))</f>
@@ -2192,11 +2192,11 @@
       </c>
       <c r="E61" s="2">
         <f>IF(COUNT('Turns'!E51,'Turns'!E52,'Turns'!E57)=3,SUM('Turns'!E51,'Turns'!E52,'Turns'!E57),"Unknown")</f>
-        <v>0.00011951469</v>
+        <v>0.00011988468</v>
       </c>
       <c r="F61" s="2">
         <f>IF(COUNT('Turns'!F51,'Turns'!F52,'Turns'!F57)=3,SUM('Turns'!F51,'Turns'!F52,'Turns'!F57),"Unknown")</f>
-        <v>0.000137</v>
+        <v>0.0001368</v>
       </c>
       <c r="G61" s="5">
         <f>IF(ISNUMBER(E61),ROUND(E61*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2219,11 +2219,11 @@
       </c>
       <c r="E62" s="2">
         <f>IF(COUNT('Turns'!E75,'Turns'!E90)=2,SUM('Turns'!E75,'Turns'!E90),"Unknown")</f>
-        <v>0.000321730056</v>
+        <v>0.00032302261</v>
       </c>
       <c r="F62" s="2">
         <f>IF(COUNT('Turns'!F75,'Turns'!F90)=2,SUM('Turns'!F75,'Turns'!F90),"Unknown")</f>
-        <v>0.0003688</v>
+        <v>0.0003686</v>
       </c>
       <c r="G62" s="5">
         <f>IF(ISNUMBER(E62),ROUND(E62*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2245,7 +2245,7 @@
         <v>94</v>
       </c>
       <c r="D63" s="4">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J63" s="4" t="s">
         <v>95</v>
@@ -2295,15 +2295,15 @@
         <v>97</v>
       </c>
       <c r="D65" s="5">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E65" s="2">
         <f>IF(AND(ISNUMBER(F65),ISNUMBER('Reference data'!$B$3)),F65*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000105207822</v>
+        <v>0.00010551254</v>
       </c>
       <c r="F65" s="2">
         <f>IF(D65=0,0,IF(ISNUMBER('Reference data'!B17),D65*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>0.0001206</v>
+        <v>0.0001204</v>
       </c>
       <c r="G65" s="5">
         <f>IF(ISNUMBER(E65),ROUND(E65*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2361,7 +2361,7 @@
         <v>105</v>
       </c>
       <c r="D69" s="4">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="24" customHeight="1">
@@ -2375,15 +2375,15 @@
         <v>106</v>
       </c>
       <c r="D70" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E70" s="2">
         <f>IF(AND(ISNUMBER(F70),ISNUMBER('Reference data'!$B$3)),F70*'Reference data'!$B$3,"Unknown")</f>
-        <v>1.8843192e-05</v>
+        <v>1.998078e-05</v>
       </c>
       <c r="F70" s="2">
         <f>IF(D70=0,0,IF(ISNUMBER('Reference data'!F17),D70*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>2.16e-05</v>
+        <v>2.28e-05</v>
       </c>
       <c r="G70" s="5">
         <f>IF(ISNUMBER(E70),ROUND(E70*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="E71" s="2">
         <f>IF(AND(ISNUMBER(F71),ISNUMBER('Reference data'!$B$3)),F71*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.187376e-05</v>
+        <v>4.20648e-05</v>
       </c>
       <c r="F71" s="2">
         <f>IF(D71=0,0,IF(ISNUMBER('Reference data'!E17),D71*'Reference data'!E17/1000000,"Unknown"))</f>
@@ -2472,11 +2472,11 @@
       </c>
       <c r="E75" s="2">
         <f>IF(COUNT('Turns'!E64,'Turns'!E65,'Turns'!E70,'Turns'!E71)=4,SUM('Turns'!E64,'Turns'!E65,'Turns'!E70,'Turns'!E71),"Unknown")</f>
-        <v>0.000165924774</v>
+        <v>0.00016755812</v>
       </c>
       <c r="F75" s="2">
         <f>IF(COUNT('Turns'!F64,'Turns'!F65,'Turns'!F70,'Turns'!F71)=4,SUM('Turns'!F64,'Turns'!F65,'Turns'!F70,'Turns'!F71),"Unknown")</f>
-        <v>0.0001902</v>
+        <v>0.0001912</v>
       </c>
       <c r="G75" s="5">
         <f>IF(ISNUMBER(E75),ROUND(E75*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="E81" s="2">
         <f>IF(AND(ISNUMBER(F81),ISNUMBER('Reference data'!$B$3)),F81*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000119165742</v>
+        <v>0.00011970941</v>
       </c>
       <c r="F81" s="2">
         <f>IF(D81=0,0,IF(ISNUMBER('Reference data'!B17),D81*'Reference data'!B17/1000000,"Unknown"))</f>
@@ -2653,7 +2653,7 @@
         <v>105</v>
       </c>
       <c r="D85" s="4">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="24" customHeight="1">
@@ -2667,15 +2667,15 @@
         <v>107</v>
       </c>
       <c r="D86" s="5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E86" s="2">
         <f>IF(AND(ISNUMBER(F86),ISNUMBER('Reference data'!$B$3)),F86*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.663954e-05</v>
+        <v>3.575508e-05</v>
       </c>
       <c r="F86" s="2">
         <f>IF(D86=0,0,IF(ISNUMBER('Reference data'!E17),D86*'Reference data'!E17/1000000,"Unknown"))</f>
-        <v>4.2e-05</v>
+        <v>4.08e-05</v>
       </c>
       <c r="G86" s="5">
         <f>IF(ISNUMBER(E86),ROUND(E86*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2734,11 +2734,11 @@
       </c>
       <c r="E90" s="2">
         <f>IF(COUNT('Turns'!E80,'Turns'!E81,'Turns'!E86)=3,SUM('Turns'!E80,'Turns'!E81,'Turns'!E86),"Unknown")</f>
-        <v>0.000155805282</v>
+        <v>0.00015546449</v>
       </c>
       <c r="F90" s="2">
         <f>IF(COUNT('Turns'!F80,'Turns'!F81,'Turns'!F86)=3,SUM('Turns'!F80,'Turns'!F81,'Turns'!F86),"Unknown")</f>
-        <v>0.0001786</v>
+        <v>0.0001774</v>
       </c>
       <c r="G90" s="5">
         <f>IF(ISNUMBER(E90),ROUND(E90*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2761,11 +2761,11 @@
       </c>
       <c r="E91" s="2">
         <f>IF(COUNT('Turns'!E104)=1,SUM('Turns'!E104),"Unknown")</f>
-        <v>0.000173776104</v>
+        <v>0.00016913555</v>
       </c>
       <c r="F91" s="2">
         <f>IF(COUNT('Turns'!F104)=1,SUM('Turns'!F104),"Unknown")</f>
-        <v>0.0001992</v>
+        <v>0.000193</v>
       </c>
       <c r="G91" s="5">
         <f>IF(ISNUMBER(E91),ROUND(E91*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="H91" s="5">
         <f>IF(ISNUMBER(F91),ROUND(F91*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="92" spans="1:13" s="4" customFormat="1" ht="24" customHeight="1">
@@ -2787,7 +2787,7 @@
         <v>94</v>
       </c>
       <c r="D92" s="4">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="J92" s="4" t="s">
         <v>95</v>
@@ -2837,15 +2837,15 @@
         <v>97</v>
       </c>
       <c r="D94" s="5">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E94" s="2">
         <f>IF(AND(ISNUMBER(F94),ISNUMBER('Reference data'!$B$3)),F94*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000127714968</v>
+        <v>0.00012812237</v>
       </c>
       <c r="F94" s="2">
         <f>IF(D94=0,0,IF(ISNUMBER('Reference data'!B17),D94*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>0.0001464</v>
+        <v>0.0001462</v>
       </c>
       <c r="G94" s="5">
         <f>IF(ISNUMBER(E94),ROUND(E94*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2903,7 +2903,7 @@
         <v>105</v>
       </c>
       <c r="D98" s="4">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="99" spans="1:13" ht="24" customHeight="1">
@@ -2917,15 +2917,15 @@
         <v>106</v>
       </c>
       <c r="D99" s="5">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E99" s="2">
         <f>IF(AND(ISNUMBER(F99),ISNUMBER('Reference data'!$B$3)),F99*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.3030568e-05</v>
+        <v>1.787754e-05</v>
       </c>
       <c r="F99" s="2">
         <f>IF(D99=0,0,IF(ISNUMBER('Reference data'!F17),D99*'Reference data'!F17/1000000,"Unknown"))</f>
-        <v>2.64e-05</v>
+        <v>2.04e-05</v>
       </c>
       <c r="G99" s="5">
         <f>IF(ISNUMBER(E99),ROUND(E99*'Reference data'!$B$2,0),"Unknown")</f>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="H99" s="5">
         <f>IF(ISNUMBER(F99),ROUND(F99*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="24" customHeight="1">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="E100" s="2">
         <f>IF(AND(ISNUMBER(F100),ISNUMBER('Reference data'!$B$3)),F100*'Reference data'!$B$3,"Unknown")</f>
-        <v>2.3030568e-05</v>
+        <v>2.313564e-05</v>
       </c>
       <c r="F100" s="2">
         <f>IF(D100=0,0,IF(ISNUMBER('Reference data'!E17),D100*'Reference data'!E17/1000000,"Unknown"))</f>
@@ -3014,11 +3014,11 @@
       </c>
       <c r="E104" s="2">
         <f>IF(COUNT('Turns'!E93,'Turns'!E94,'Turns'!E99,'Turns'!E100)=4,SUM('Turns'!E93,'Turns'!E94,'Turns'!E99,'Turns'!E100),"Unknown")</f>
-        <v>0.000173776104</v>
+        <v>0.00016913555</v>
       </c>
       <c r="F104" s="2">
         <f>IF(COUNT('Turns'!F93,'Turns'!F94,'Turns'!F99,'Turns'!F100)=4,SUM('Turns'!F93,'Turns'!F94,'Turns'!F99,'Turns'!F100),"Unknown")</f>
-        <v>0.0001992</v>
+        <v>0.000193</v>
       </c>
       <c r="G104" s="5">
         <f>IF(ISNUMBER(E104),ROUND(E104*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="H104" s="5">
         <f>IF(ISNUMBER(F104),ROUND(F104*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="K104" s="4" t="s">
         <v>111</v>
@@ -3041,11 +3041,11 @@
       </c>
       <c r="E105" s="2">
         <f>IF(COUNT('Turns'!E118)=1,SUM('Turns'!E118),"Unknown")</f>
-        <v>0.000219313818</v>
+        <v>0.00021926277</v>
       </c>
       <c r="F105" s="2">
         <f>IF(COUNT('Turns'!F118)=1,SUM('Turns'!F118),"Unknown")</f>
-        <v>0.0002514</v>
+        <v>0.0002502</v>
       </c>
       <c r="G105" s="5">
         <f>IF(ISNUMBER(E105),ROUND(E105*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3067,7 +3067,7 @@
         <v>94</v>
       </c>
       <c r="D106" s="4">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="J106" s="4" t="s">
         <v>95</v>
@@ -3117,15 +3117,15 @@
         <v>97</v>
       </c>
       <c r="D108" s="5">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="E108" s="2">
         <f>IF(AND(ISNUMBER(F108),ISNUMBER('Reference data'!$B$3)),F108*'Reference data'!$B$3,"Unknown")</f>
-        <v>0.000139753674</v>
+        <v>0.00013933965</v>
       </c>
       <c r="F108" s="2">
         <f>IF(D108=0,0,IF(ISNUMBER('Reference data'!B17),D108*'Reference data'!B17/1000000,"Unknown"))</f>
-        <v>0.0001602</v>
+        <v>0.000159</v>
       </c>
       <c r="G108" s="5">
         <f>IF(ISNUMBER(E108),ROUND(E108*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="E113" s="2">
         <f>IF(AND(ISNUMBER(F113),ISNUMBER('Reference data'!$B$3)),F113*'Reference data'!$B$3,"Unknown")</f>
-        <v>4.9201668e-05</v>
+        <v>4.942614e-05</v>
       </c>
       <c r="F113" s="2">
         <f>IF(D113=0,0,IF(ISNUMBER('Reference data'!F17),D113*'Reference data'!F17/1000000,"Unknown"))</f>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="E114" s="2">
         <f>IF(AND(ISNUMBER(F114),ISNUMBER('Reference data'!$B$3)),F114*'Reference data'!$B$3,"Unknown")</f>
-        <v>3.0358476e-05</v>
+        <v>3.049698e-05</v>
       </c>
       <c r="F114" s="2">
         <f>IF(D114=0,0,IF(ISNUMBER('Reference data'!E17),D114*'Reference data'!E17/1000000,"Unknown"))</f>
@@ -3294,11 +3294,11 @@
       </c>
       <c r="E118" s="2">
         <f>IF(COUNT('Turns'!E107,'Turns'!E108,'Turns'!E113,'Turns'!E114)=4,SUM('Turns'!E107,'Turns'!E108,'Turns'!E113,'Turns'!E114),"Unknown")</f>
-        <v>0.000219313818</v>
+        <v>0.00021926277</v>
       </c>
       <c r="F118" s="2">
         <f>IF(COUNT('Turns'!F107,'Turns'!F108,'Turns'!F113,'Turns'!F114)=4,SUM('Turns'!F107,'Turns'!F108,'Turns'!F113,'Turns'!F114),"Unknown")</f>
-        <v>0.0002514</v>
+        <v>0.0002502</v>
       </c>
       <c r="G118" s="5">
         <f>IF(ISNUMBER(E118),ROUND(E118*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3456,15 +3456,15 @@
       </c>
       <c r="J2" s="2">
         <f>IF(COUNT('Turns'!D5,'Turns'!D23)=2,SUM('Turns'!D5,'Turns'!D23),"Unknown")</f>
-        <v>743.0</v>
+        <v>742.0</v>
       </c>
       <c r="K2" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E23)=2,SUM('Turns'!E5,'Turns'!E23),"Unknown")</f>
-        <v>0.000129634182</v>
+        <v>0.00013005034</v>
       </c>
       <c r="L2" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F23)=2,SUM('Turns'!F5,'Turns'!F23),"Unknown")</f>
-        <v>0.0001486</v>
+        <v>0.0001484</v>
       </c>
       <c r="M2" s="2">
         <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="T2" s="2">
         <f>IF(COUNT('Turns'!E13,'Turns'!E28)=2,SUM('Turns'!E13,'Turns'!E28),"Unknown")</f>
-        <v>3.8733228e-05</v>
+        <v>3.890994e-05</v>
       </c>
       <c r="U2" s="2">
         <f>IF(COUNT('Turns'!F13,'Turns'!F28)=2,SUM('Turns'!F13,'Turns'!F28),"Unknown")</f>
@@ -3501,23 +3501,23 @@
       </c>
       <c r="V2" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="W2" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>1.046844e-05</v>
+        <v>9.46458e-06</v>
       </c>
       <c r="X2" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>1.2e-05</v>
+        <v>1.08e-05</v>
       </c>
       <c r="Y2" s="2">
         <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
-        <v>0.00017883585</v>
+        <v>0.00017842486</v>
       </c>
       <c r="Z2" s="2">
         <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
-        <v>0.000205</v>
+        <v>0.0002036</v>
       </c>
       <c r="AA2" s="5">
         <f>IF(ISNUMBER(Y2),ROUND(Y2*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3525,10 +3525,10 @@
       </c>
       <c r="AB2" s="5">
         <f>IF(ISNUMBER(Z2),ROUND(Z2*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="AD2" s="1">
-        <v>2057.073</v>
+        <v>2259.556</v>
       </c>
       <c r="AE2" s="1" t="s">
         <v>159</v>
@@ -3561,15 +3561,15 @@
       </c>
       <c r="J3" s="2">
         <f>IF(COUNT('Turns'!D5,'Turns'!D23)=2,SUM('Turns'!D5,'Turns'!D23),"Unknown")</f>
-        <v>743.0</v>
+        <v>742.0</v>
       </c>
       <c r="K3" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E23)=2,SUM('Turns'!E5,'Turns'!E23),"Unknown")</f>
-        <v>0.000129634182</v>
+        <v>0.00013005034</v>
       </c>
       <c r="L3" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F23)=2,SUM('Turns'!F5,'Turns'!F23),"Unknown")</f>
-        <v>0.0001486</v>
+        <v>0.0001484</v>
       </c>
       <c r="M3" s="2">
         <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="T3" s="2">
         <f>IF(COUNT('Turns'!E13,'Turns'!E28)=2,SUM('Turns'!E13,'Turns'!E28),"Unknown")</f>
-        <v>3.8733228e-05</v>
+        <v>3.890994e-05</v>
       </c>
       <c r="U3" s="2">
         <f>IF(COUNT('Turns'!F13,'Turns'!F28)=2,SUM('Turns'!F13,'Turns'!F28),"Unknown")</f>
@@ -3606,23 +3606,23 @@
       </c>
       <c r="V3" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="W3" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>1.046844e-05</v>
+        <v>9.46458e-06</v>
       </c>
       <c r="X3" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>1.2e-05</v>
+        <v>1.08e-05</v>
       </c>
       <c r="Y3" s="2">
         <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
-        <v>0.00017883585</v>
+        <v>0.00017842486</v>
       </c>
       <c r="Z3" s="2">
         <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
-        <v>0.000205</v>
+        <v>0.0002036</v>
       </c>
       <c r="AA3" s="5">
         <f>IF(ISNUMBER(Y3),ROUND(Y3*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3630,10 +3630,10 @@
       </c>
       <c r="AB3" s="5">
         <f>IF(ISNUMBER(Z3),ROUND(Z3*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="AD3" s="1">
-        <v>2053.805</v>
+        <v>2257.386</v>
       </c>
       <c r="AE3" s="1" t="s">
         <v>159</v>
@@ -3666,15 +3666,15 @@
       </c>
       <c r="J4" s="2">
         <f>IF(COUNT('Turns'!D5,'Turns'!D23)=2,SUM('Turns'!D5,'Turns'!D23),"Unknown")</f>
-        <v>743.0</v>
+        <v>742.0</v>
       </c>
       <c r="K4" s="2">
         <f>IF(COUNT('Turns'!E5,'Turns'!E23)=2,SUM('Turns'!E5,'Turns'!E23),"Unknown")</f>
-        <v>0.000129634182</v>
+        <v>0.00013005034</v>
       </c>
       <c r="L4" s="2">
         <f>IF(COUNT('Turns'!F5,'Turns'!F23)=2,SUM('Turns'!F5,'Turns'!F23),"Unknown")</f>
-        <v>0.0001486</v>
+        <v>0.0001484</v>
       </c>
       <c r="M4" s="2">
         <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="T4" s="2">
         <f>IF(COUNT('Turns'!E13,'Turns'!E28)=2,SUM('Turns'!E13,'Turns'!E28),"Unknown")</f>
-        <v>3.8733228e-05</v>
+        <v>3.890994e-05</v>
       </c>
       <c r="U4" s="2">
         <f>IF(COUNT('Turns'!F13,'Turns'!F28)=2,SUM('Turns'!F13,'Turns'!F28),"Unknown")</f>
@@ -3711,23 +3711,23 @@
       </c>
       <c r="V4" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="W4" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>1.046844e-05</v>
+        <v>9.46458e-06</v>
       </c>
       <c r="X4" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>1.2e-05</v>
+        <v>1.08e-05</v>
       </c>
       <c r="Y4" s="2">
         <f>IF(COUNT('Turns'!E17,'Turns'!E32)=2,SUM('Turns'!E17,'Turns'!E32),"Unknown")</f>
-        <v>0.00017883585</v>
+        <v>0.00017842486</v>
       </c>
       <c r="Z4" s="2">
         <f>IF(COUNT('Turns'!F17,'Turns'!F32)=2,SUM('Turns'!F17,'Turns'!F32),"Unknown")</f>
-        <v>0.000205</v>
+        <v>0.0002036</v>
       </c>
       <c r="AA4" s="5">
         <f>IF(ISNUMBER(Y4),ROUND(Y4*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3735,10 +3735,10 @@
       </c>
       <c r="AB4" s="5">
         <f>IF(ISNUMBER(Z4),ROUND(Z4*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="AD4" s="1">
-        <v>2052.502</v>
+        <v>2256.115</v>
       </c>
       <c r="AE4" s="1" t="s">
         <v>159</v>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="K5" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>5.7925368e-05</v>
+        <v>5.818964e-05</v>
       </c>
       <c r="L5" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="T5" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>1.6749504e-05</v>
+        <v>1.682592e-05</v>
       </c>
       <c r="U5" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
@@ -3813,34 +3813,34 @@
       </c>
       <c r="V5" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="W5" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>1.046844e-05</v>
+        <v>9.46458e-06</v>
       </c>
       <c r="X5" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>1.2e-05</v>
+        <v>1.08e-05</v>
       </c>
       <c r="Y5" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>8.5143312e-05</v>
+        <v>8.448014e-05</v>
       </c>
       <c r="Z5" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>9.76e-05</v>
+        <v>9.64e-05</v>
       </c>
       <c r="AA5" s="5">
         <f>IF(ISNUMBER(Y5),ROUND(Y5*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="AB5" s="5">
         <f>IF(ISNUMBER(Z5),ROUND(Z5*'Reference data'!$B$2,0),"Unknown")</f>
         <v>10.0</v>
       </c>
       <c r="AD5" s="1">
-        <v>1245.423</v>
+        <v>1251.252</v>
       </c>
       <c r="AE5" s="1" t="s">
         <v>159</v>
@@ -3880,7 +3880,7 @@
       </c>
       <c r="K6" s="2">
         <f>IF(COUNT('Turns'!E5)=1,SUM('Turns'!E5),"Unknown")</f>
-        <v>5.7925368e-05</v>
+        <v>5.818964e-05</v>
       </c>
       <c r="L6" s="2">
         <f>IF(COUNT('Turns'!F5)=1,SUM('Turns'!F5),"Unknown")</f>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="T6" s="2">
         <f>IF(COUNT('Turns'!E13)=1,SUM('Turns'!E13),"Unknown")</f>
-        <v>1.6749504e-05</v>
+        <v>1.682592e-05</v>
       </c>
       <c r="U6" s="2">
         <f>IF(COUNT('Turns'!F13)=1,SUM('Turns'!F13),"Unknown")</f>
@@ -3918,27 +3918,27 @@
       </c>
       <c r="V6" s="2">
         <f>IF(COUNT('Turns'!D12)=1,SUM('Turns'!D12),"Unknown")</f>
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="W6" s="2">
         <f>IF(COUNT('Turns'!E12)=1,SUM('Turns'!E12),"Unknown")</f>
-        <v>1.046844e-05</v>
+        <v>9.46458e-06</v>
       </c>
       <c r="X6" s="2">
         <f>IF(COUNT('Turns'!F12)=1,SUM('Turns'!F12),"Unknown")</f>
-        <v>1.2e-05</v>
+        <v>1.08e-05</v>
       </c>
       <c r="Y6" s="2">
         <f>IF(COUNT('Turns'!E17)=1,SUM('Turns'!E17),"Unknown")</f>
-        <v>8.5143312e-05</v>
+        <v>8.448014e-05</v>
       </c>
       <c r="Z6" s="2">
         <f>IF(COUNT('Turns'!F17)=1,SUM('Turns'!F17),"Unknown")</f>
-        <v>9.76e-05</v>
+        <v>9.64e-05</v>
       </c>
       <c r="AA6" s="5">
         <f>IF(ISNUMBER(Y6),ROUND(Y6*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="AB6" s="5">
         <f>IF(ISNUMBER(Z6),ROUND(Z6*'Reference data'!$B$2,0),"Unknown")</f>
@@ -3948,7 +3948,7 @@
         <v>93</v>
       </c>
       <c r="AD6" s="1">
-        <v>1239.611</v>
+        <v>1248.048</v>
       </c>
       <c r="AE6" s="1" t="s">
         <v>172</v>
@@ -3980,7 +3980,7 @@
         <v>165</v>
       </c>
       <c r="AD7" s="1">
-        <v>4.191</v>
+        <v>1.766</v>
       </c>
       <c r="AE7" s="1" t="s">
         <v>176</v>
@@ -4012,7 +4012,7 @@
         <v>175</v>
       </c>
       <c r="AD8" s="1">
-        <v>1.12</v>
+        <v>0.444</v>
       </c>
       <c r="AE8" s="1" t="s">
         <v>176</v>
@@ -4045,15 +4045,15 @@
       </c>
       <c r="J9" s="2">
         <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
-        <v>411.0</v>
+        <v>410.0</v>
       </c>
       <c r="K9" s="2">
         <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>7.1708814e-05</v>
+        <v>7.18607e-05</v>
       </c>
       <c r="L9" s="2">
         <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
-        <v>8.22e-05</v>
+        <v>8.2e-05</v>
       </c>
       <c r="M9" s="2">
         <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
@@ -4082,7 +4082,7 @@
       </c>
       <c r="T9" s="2">
         <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>2.1983724e-05</v>
+        <v>2.208402e-05</v>
       </c>
       <c r="U9" s="2">
         <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
@@ -4099,11 +4099,11 @@
       </c>
       <c r="Y9" s="2">
         <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>9.3692538e-05</v>
+        <v>9.394472e-05</v>
       </c>
       <c r="Z9" s="2">
         <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>0.0001074</v>
+        <v>0.0001072</v>
       </c>
       <c r="AA9" s="5">
         <f>IF(ISNUMBER(Y9),ROUND(Y9*'Reference data'!$B$2,0),"Unknown")</f>
@@ -4114,7 +4114,7 @@
         <v>11.0</v>
       </c>
       <c r="AD9" s="1">
-        <v>796.875</v>
+        <v>999.922</v>
       </c>
       <c r="AE9" s="1" t="s">
         <v>159</v>
@@ -4137,7 +4137,7 @@
         <v>111</v>
       </c>
       <c r="F10" s="1">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>171</v>
@@ -4150,15 +4150,15 @@
       </c>
       <c r="J10" s="2">
         <f>IF(COUNT('Turns'!D23)=1,SUM('Turns'!D23),"Unknown")</f>
-        <v>411.0</v>
+        <v>410.0</v>
       </c>
       <c r="K10" s="2">
         <f>IF(COUNT('Turns'!E23)=1,SUM('Turns'!E23),"Unknown")</f>
-        <v>7.1708814e-05</v>
+        <v>7.18607e-05</v>
       </c>
       <c r="L10" s="2">
         <f>IF(COUNT('Turns'!F23)=1,SUM('Turns'!F23),"Unknown")</f>
-        <v>8.22e-05</v>
+        <v>8.2e-05</v>
       </c>
       <c r="M10" s="2">
         <f>IF(COUNT('Turns'!D22)=1,SUM('Turns'!D22),"Unknown")</f>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="T10" s="2">
         <f>IF(COUNT('Turns'!E28)=1,SUM('Turns'!E28),"Unknown")</f>
-        <v>2.1983724e-05</v>
+        <v>2.208402e-05</v>
       </c>
       <c r="U10" s="2">
         <f>IF(COUNT('Turns'!F28)=1,SUM('Turns'!F28),"Unknown")</f>
@@ -4204,11 +4204,11 @@
       </c>
       <c r="Y10" s="2">
         <f>IF(COUNT('Turns'!E32)=1,SUM('Turns'!E32),"Unknown")</f>
-        <v>9.3692538e-05</v>
+        <v>9.394472e-05</v>
       </c>
       <c r="Z10" s="2">
         <f>IF(COUNT('Turns'!F32)=1,SUM('Turns'!F32),"Unknown")</f>
-        <v>0.0001074</v>
+        <v>0.0001072</v>
       </c>
       <c r="AA10" s="5">
         <f>IF(ISNUMBER(Y10),ROUND(Y10*'Reference data'!$B$2,0),"Unknown")</f>
@@ -4222,7 +4222,7 @@
         <v>118</v>
       </c>
       <c r="AD10" s="1">
-        <v>793.284</v>
+        <v>998.653</v>
       </c>
       <c r="AE10" s="1" t="s">
         <v>172</v>
@@ -4252,15 +4252,15 @@
       </c>
       <c r="J11" s="2">
         <f>IF(COUNT('Turns'!D36,'Turns'!D52)=2,SUM('Turns'!D36,'Turns'!D52),"Unknown")</f>
-        <v>976.0</v>
+        <v>974.0</v>
       </c>
       <c r="K11" s="2">
         <f>IF(COUNT('Turns'!E36,'Turns'!E52)=2,SUM('Turns'!E36,'Turns'!E52),"Unknown")</f>
-        <v>0.000170286624</v>
+        <v>0.00017071298</v>
       </c>
       <c r="L11" s="2">
         <f>IF(COUNT('Turns'!F36,'Turns'!F52)=2,SUM('Turns'!F36,'Turns'!F52),"Unknown")</f>
-        <v>0.0001952</v>
+        <v>0.0001948</v>
       </c>
       <c r="M11" s="2">
         <f>IF(COUNT('Turns'!D35,'Turns'!D51)=2,SUM('Turns'!D35,'Turns'!D51),"Unknown")</f>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="T11" s="2">
         <f>IF(COUNT('Turns'!E42,'Turns'!E57)=2,SUM('Turns'!E42,'Turns'!E57),"Unknown")</f>
-        <v>4.5014292e-05</v>
+        <v>4.521966e-05</v>
       </c>
       <c r="U11" s="2">
         <f>IF(COUNT('Turns'!F42,'Turns'!F57)=2,SUM('Turns'!F42,'Turns'!F57),"Unknown")</f>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="W11" s="2">
         <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>8.374752e-06</v>
+        <v>8.41296e-06</v>
       </c>
       <c r="X11" s="2">
         <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
@@ -4309,11 +4309,11 @@
       </c>
       <c r="Y11" s="2">
         <f>IF(COUNT('Turns'!E46,'Turns'!E61)=2,SUM('Turns'!E46,'Turns'!E61),"Unknown")</f>
-        <v>0.000223675668</v>
+        <v>0.0002243456</v>
       </c>
       <c r="Z11" s="2">
         <f>IF(COUNT('Turns'!F46,'Turns'!F61)=2,SUM('Turns'!F46,'Turns'!F61),"Unknown")</f>
-        <v>0.0002564</v>
+        <v>0.000256</v>
       </c>
       <c r="AA11" s="5">
         <f>IF(ISNUMBER(Y11),ROUND(Y11*'Reference data'!$B$2,0),"Unknown")</f>
@@ -4324,7 +4324,7 @@
         <v>26.0</v>
       </c>
       <c r="AD11" s="1">
-        <v>1929.992</v>
+        <v>1969.275</v>
       </c>
       <c r="AE11" s="1" t="s">
         <v>159</v>
@@ -4357,15 +4357,15 @@
       </c>
       <c r="J12" s="2">
         <f>IF(COUNT('Turns'!D36,'Turns'!D52)=2,SUM('Turns'!D36,'Turns'!D52),"Unknown")</f>
-        <v>976.0</v>
+        <v>974.0</v>
       </c>
       <c r="K12" s="2">
         <f>IF(COUNT('Turns'!E36,'Turns'!E52)=2,SUM('Turns'!E36,'Turns'!E52),"Unknown")</f>
-        <v>0.000170286624</v>
+        <v>0.00017071298</v>
       </c>
       <c r="L12" s="2">
         <f>IF(COUNT('Turns'!F36,'Turns'!F52)=2,SUM('Turns'!F36,'Turns'!F52),"Unknown")</f>
-        <v>0.0001952</v>
+        <v>0.0001948</v>
       </c>
       <c r="M12" s="2">
         <f>IF(COUNT('Turns'!D35,'Turns'!D51)=2,SUM('Turns'!D35,'Turns'!D51),"Unknown")</f>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="T12" s="2">
         <f>IF(COUNT('Turns'!E42,'Turns'!E57)=2,SUM('Turns'!E42,'Turns'!E57),"Unknown")</f>
-        <v>4.5014292e-05</v>
+        <v>4.521966e-05</v>
       </c>
       <c r="U12" s="2">
         <f>IF(COUNT('Turns'!F42,'Turns'!F57)=2,SUM('Turns'!F42,'Turns'!F57),"Unknown")</f>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="W12" s="2">
         <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>8.374752e-06</v>
+        <v>8.41296e-06</v>
       </c>
       <c r="X12" s="2">
         <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
@@ -4414,11 +4414,11 @@
       </c>
       <c r="Y12" s="2">
         <f>IF(COUNT('Turns'!E46,'Turns'!E61)=2,SUM('Turns'!E46,'Turns'!E61),"Unknown")</f>
-        <v>0.000223675668</v>
+        <v>0.0002243456</v>
       </c>
       <c r="Z12" s="2">
         <f>IF(COUNT('Turns'!F46,'Turns'!F61)=2,SUM('Turns'!F46,'Turns'!F61),"Unknown")</f>
-        <v>0.0002564</v>
+        <v>0.000256</v>
       </c>
       <c r="AA12" s="5">
         <f>IF(ISNUMBER(Y12),ROUND(Y12*'Reference data'!$B$2,0),"Unknown")</f>
@@ -4429,7 +4429,7 @@
         <v>26.0</v>
       </c>
       <c r="AD12" s="1">
-        <v>1927.933</v>
+        <v>1967.602</v>
       </c>
       <c r="AE12" s="1" t="s">
         <v>159</v>
@@ -4462,15 +4462,15 @@
       </c>
       <c r="J13" s="2">
         <f>IF(COUNT('Turns'!D36,'Turns'!D52)=2,SUM('Turns'!D36,'Turns'!D52),"Unknown")</f>
-        <v>976.0</v>
+        <v>974.0</v>
       </c>
       <c r="K13" s="2">
         <f>IF(COUNT('Turns'!E36,'Turns'!E52)=2,SUM('Turns'!E36,'Turns'!E52),"Unknown")</f>
-        <v>0.000170286624</v>
+        <v>0.00017071298</v>
       </c>
       <c r="L13" s="2">
         <f>IF(COUNT('Turns'!F36,'Turns'!F52)=2,SUM('Turns'!F36,'Turns'!F52),"Unknown")</f>
-        <v>0.0001952</v>
+        <v>0.0001948</v>
       </c>
       <c r="M13" s="2">
         <f>IF(COUNT('Turns'!D35,'Turns'!D51)=2,SUM('Turns'!D35,'Turns'!D51),"Unknown")</f>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="T13" s="2">
         <f>IF(COUNT('Turns'!E42,'Turns'!E57)=2,SUM('Turns'!E42,'Turns'!E57),"Unknown")</f>
-        <v>4.5014292e-05</v>
+        <v>4.521966e-05</v>
       </c>
       <c r="U13" s="2">
         <f>IF(COUNT('Turns'!F42,'Turns'!F57)=2,SUM('Turns'!F42,'Turns'!F57),"Unknown")</f>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="W13" s="2">
         <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>8.374752e-06</v>
+        <v>8.41296e-06</v>
       </c>
       <c r="X13" s="2">
         <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
@@ -4519,11 +4519,11 @@
       </c>
       <c r="Y13" s="2">
         <f>IF(COUNT('Turns'!E46,'Turns'!E61)=2,SUM('Turns'!E46,'Turns'!E61),"Unknown")</f>
-        <v>0.000223675668</v>
+        <v>0.0002243456</v>
       </c>
       <c r="Z13" s="2">
         <f>IF(COUNT('Turns'!F46,'Turns'!F61)=2,SUM('Turns'!F46,'Turns'!F61),"Unknown")</f>
-        <v>0.0002564</v>
+        <v>0.000256</v>
       </c>
       <c r="AA13" s="5">
         <f>IF(ISNUMBER(Y13),ROUND(Y13*'Reference data'!$B$2,0),"Unknown")</f>
@@ -4534,7 +4534,7 @@
         <v>26.0</v>
       </c>
       <c r="AD13" s="1">
-        <v>1926.7</v>
+        <v>1966.716</v>
       </c>
       <c r="AE13" s="1" t="s">
         <v>159</v>
@@ -4567,15 +4567,15 @@
       </c>
       <c r="J14" s="2">
         <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
-        <v>453.0</v>
+        <v>452.0</v>
       </c>
       <c r="K14" s="2">
         <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>7.9036722e-05</v>
+        <v>7.922204e-05</v>
       </c>
       <c r="L14" s="2">
         <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
-        <v>9.06e-05</v>
+        <v>9.04e-05</v>
       </c>
       <c r="M14" s="2">
         <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="T14" s="2">
         <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
-        <v>1.6749504e-05</v>
+        <v>1.682592e-05</v>
       </c>
       <c r="U14" s="2">
         <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="W14" s="2">
         <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>8.374752e-06</v>
+        <v>8.41296e-06</v>
       </c>
       <c r="X14" s="2">
         <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
@@ -4624,11 +4624,11 @@
       </c>
       <c r="Y14" s="2">
         <f>IF(COUNT('Turns'!E46)=1,SUM('Turns'!E46),"Unknown")</f>
-        <v>0.000104160978</v>
+        <v>0.00010446092</v>
       </c>
       <c r="Z14" s="2">
         <f>IF(COUNT('Turns'!F46)=1,SUM('Turns'!F46),"Unknown")</f>
-        <v>0.0001194</v>
+        <v>0.0001192</v>
       </c>
       <c r="AA14" s="5">
         <f>IF(ISNUMBER(Y14),ROUND(Y14*'Reference data'!$B$2,0),"Unknown")</f>
@@ -4639,7 +4639,7 @@
         <v>12.0</v>
       </c>
       <c r="AD14" s="1">
-        <v>970.307</v>
+        <v>1026.998</v>
       </c>
       <c r="AE14" s="1" t="s">
         <v>159</v>
@@ -4662,7 +4662,7 @@
         <v>111</v>
       </c>
       <c r="F15" s="1">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>171</v>
@@ -4675,15 +4675,15 @@
       </c>
       <c r="J15" s="2">
         <f>IF(COUNT('Turns'!D36)=1,SUM('Turns'!D36),"Unknown")</f>
-        <v>453.0</v>
+        <v>452.0</v>
       </c>
       <c r="K15" s="2">
         <f>IF(COUNT('Turns'!E36)=1,SUM('Turns'!E36),"Unknown")</f>
-        <v>7.9036722e-05</v>
+        <v>7.922204e-05</v>
       </c>
       <c r="L15" s="2">
         <f>IF(COUNT('Turns'!F36)=1,SUM('Turns'!F36),"Unknown")</f>
-        <v>9.06e-05</v>
+        <v>9.04e-05</v>
       </c>
       <c r="M15" s="2">
         <f>IF(COUNT('Turns'!D35)=1,SUM('Turns'!D35),"Unknown")</f>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="T15" s="2">
         <f>IF(COUNT('Turns'!E42)=1,SUM('Turns'!E42),"Unknown")</f>
-        <v>1.6749504e-05</v>
+        <v>1.682592e-05</v>
       </c>
       <c r="U15" s="2">
         <f>IF(COUNT('Turns'!F42)=1,SUM('Turns'!F42),"Unknown")</f>
@@ -4724,7 +4724,7 @@
       </c>
       <c r="W15" s="2">
         <f>IF(COUNT('Turns'!E41)=1,SUM('Turns'!E41),"Unknown")</f>
-        <v>8.374752e-06</v>
+        <v>8.41296e-06</v>
       </c>
       <c r="X15" s="2">
         <f>IF(COUNT('Turns'!F41)=1,SUM('Turns'!F41),"Unknown")</f>
@@ -4732,11 +4732,11 @@
       </c>
       <c r="Y15" s="2">
         <f>IF(COUNT('Turns'!E46)=1,SUM('Turns'!E46),"Unknown")</f>
-        <v>0.000104160978</v>
+        <v>0.00010446092</v>
       </c>
       <c r="Z15" s="2">
         <f>IF(COUNT('Turns'!F46)=1,SUM('Turns'!F46),"Unknown")</f>
-        <v>0.0001194</v>
+        <v>0.0001192</v>
       </c>
       <c r="AA15" s="5">
         <f>IF(ISNUMBER(Y15),ROUND(Y15*'Reference data'!$B$2,0),"Unknown")</f>
@@ -4750,7 +4750,7 @@
         <v>124</v>
       </c>
       <c r="AD15" s="1">
-        <v>967.854</v>
+        <v>1025.367</v>
       </c>
       <c r="AE15" s="1" t="s">
         <v>172</v>
@@ -4782,7 +4782,7 @@
         <v>183</v>
       </c>
       <c r="AD16" s="1">
-        <v>2.488</v>
+        <v>1.571</v>
       </c>
       <c r="AE16" s="1" t="s">
         <v>176</v>
@@ -4814,7 +4814,7 @@
         <v>185</v>
       </c>
       <c r="AD17" s="1">
-        <v>0.53</v>
+        <v>0.415</v>
       </c>
       <c r="AE17" s="1" t="s">
         <v>176</v>
@@ -4847,15 +4847,15 @@
       </c>
       <c r="J18" s="2">
         <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
-        <v>523.0</v>
+        <v>522.0</v>
       </c>
       <c r="K18" s="2">
         <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
-        <v>9.1249902e-05</v>
+        <v>9.149094e-05</v>
       </c>
       <c r="L18" s="2">
         <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
-        <v>0.0001046</v>
+        <v>0.0001044</v>
       </c>
       <c r="M18" s="2">
         <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="T18" s="2">
         <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
-        <v>2.8264788e-05</v>
+        <v>2.839374e-05</v>
       </c>
       <c r="U18" s="2">
         <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
@@ -4901,11 +4901,11 @@
       </c>
       <c r="Y18" s="2">
         <f>IF(COUNT('Turns'!E61)=1,SUM('Turns'!E61),"Unknown")</f>
-        <v>0.00011951469</v>
+        <v>0.00011988468</v>
       </c>
       <c r="Z18" s="2">
         <f>IF(COUNT('Turns'!F61)=1,SUM('Turns'!F61),"Unknown")</f>
-        <v>0.000137</v>
+        <v>0.0001368</v>
       </c>
       <c r="AA18" s="5">
         <f>IF(ISNUMBER(Y18),ROUND(Y18*'Reference data'!$B$2,0),"Unknown")</f>
@@ -4916,7 +4916,7 @@
         <v>14.0</v>
       </c>
       <c r="AD18" s="1">
-        <v>949.933</v>
+        <v>935.38</v>
       </c>
       <c r="AE18" s="1" t="s">
         <v>159</v>
@@ -4939,7 +4939,7 @@
         <v>111</v>
       </c>
       <c r="F19" s="1">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>171</v>
@@ -4952,15 +4952,15 @@
       </c>
       <c r="J19" s="2">
         <f>IF(COUNT('Turns'!D52)=1,SUM('Turns'!D52),"Unknown")</f>
-        <v>523.0</v>
+        <v>522.0</v>
       </c>
       <c r="K19" s="2">
         <f>IF(COUNT('Turns'!E52)=1,SUM('Turns'!E52),"Unknown")</f>
-        <v>9.1249902e-05</v>
+        <v>9.149094e-05</v>
       </c>
       <c r="L19" s="2">
         <f>IF(COUNT('Turns'!F52)=1,SUM('Turns'!F52),"Unknown")</f>
-        <v>0.0001046</v>
+        <v>0.0001044</v>
       </c>
       <c r="M19" s="2">
         <f>IF(COUNT('Turns'!D51)=1,SUM('Turns'!D51),"Unknown")</f>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="T19" s="2">
         <f>IF(COUNT('Turns'!E57)=1,SUM('Turns'!E57),"Unknown")</f>
-        <v>2.8264788e-05</v>
+        <v>2.839374e-05</v>
       </c>
       <c r="U19" s="2">
         <f>IF(COUNT('Turns'!F57)=1,SUM('Turns'!F57),"Unknown")</f>
@@ -5006,11 +5006,11 @@
       </c>
       <c r="Y19" s="2">
         <f>IF(COUNT('Turns'!E61)=1,SUM('Turns'!E61),"Unknown")</f>
-        <v>0.00011951469</v>
+        <v>0.00011988468</v>
       </c>
       <c r="Z19" s="2">
         <f>IF(COUNT('Turns'!F61)=1,SUM('Turns'!F61),"Unknown")</f>
-        <v>0.000137</v>
+        <v>0.0001368</v>
       </c>
       <c r="AA19" s="5">
         <f>IF(ISNUMBER(Y19),ROUND(Y19*'Reference data'!$B$2,0),"Unknown")</f>
@@ -5024,7 +5024,7 @@
         <v>131</v>
       </c>
       <c r="AD19" s="1">
-        <v>947.78</v>
+        <v>934.181</v>
       </c>
       <c r="AE19" s="1" t="s">
         <v>172</v>
@@ -5054,15 +5054,15 @@
       </c>
       <c r="J20" s="2">
         <f>IF(COUNT('Turns'!D65,'Turns'!D81)=2,SUM('Turns'!D65,'Turns'!D81),"Unknown")</f>
-        <v>1286.0</v>
+        <v>1285.0</v>
       </c>
       <c r="K20" s="2">
         <f>IF(COUNT('Turns'!E65,'Turns'!E81)=2,SUM('Turns'!E65,'Turns'!E81),"Unknown")</f>
-        <v>0.000224373564</v>
+        <v>0.00022522195</v>
       </c>
       <c r="L20" s="2">
         <f>IF(COUNT('Turns'!F65,'Turns'!F81)=2,SUM('Turns'!F65,'Turns'!F81),"Unknown")</f>
-        <v>0.0002572</v>
+        <v>0.000257</v>
       </c>
       <c r="M20" s="2">
         <f>IF(COUNT('Turns'!D64,'Turns'!D80)=2,SUM('Turns'!D64,'Turns'!D80),"Unknown")</f>
@@ -5087,35 +5087,35 @@
       </c>
       <c r="S20" s="2">
         <f>IF(COUNT('Turns'!D71,'Turns'!D86)=2,SUM('Turns'!D71,'Turns'!D86),"Unknown")</f>
-        <v>75.0</v>
+        <v>74.0</v>
       </c>
       <c r="T20" s="2">
         <f>IF(COUNT('Turns'!E71,'Turns'!E86)=2,SUM('Turns'!E71,'Turns'!E86),"Unknown")</f>
-        <v>7.85133e-05</v>
+        <v>7.781988e-05</v>
       </c>
       <c r="U20" s="2">
         <f>IF(COUNT('Turns'!F71,'Turns'!F86)=2,SUM('Turns'!F71,'Turns'!F86),"Unknown")</f>
-        <v>9e-05</v>
+        <v>8.88e-05</v>
       </c>
       <c r="V20" s="2">
         <f>IF(COUNT('Turns'!D70)=1,SUM('Turns'!D70),"Unknown")</f>
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="W20" s="2">
         <f>IF(COUNT('Turns'!E70)=1,SUM('Turns'!E70),"Unknown")</f>
-        <v>1.8843192e-05</v>
+        <v>1.998078e-05</v>
       </c>
       <c r="X20" s="2">
         <f>IF(COUNT('Turns'!F70)=1,SUM('Turns'!F70),"Unknown")</f>
-        <v>2.16e-05</v>
+        <v>2.28e-05</v>
       </c>
       <c r="Y20" s="2">
         <f>IF(COUNT('Turns'!E75,'Turns'!E90)=2,SUM('Turns'!E75,'Turns'!E90),"Unknown")</f>
-        <v>0.000321730056</v>
+        <v>0.00032302261</v>
       </c>
       <c r="Z20" s="2">
         <f>IF(COUNT('Turns'!F75,'Turns'!F90)=2,SUM('Turns'!F75,'Turns'!F90),"Unknown")</f>
-        <v>0.0003688</v>
+        <v>0.0003686</v>
       </c>
       <c r="AA20" s="5">
         <f>IF(ISNUMBER(Y20),ROUND(Y20*'Reference data'!$B$2,0),"Unknown")</f>
@@ -5126,7 +5126,7 @@
         <v>37.0</v>
       </c>
       <c r="AD20" s="1">
-        <v>5181.025</v>
+        <v>2413.279</v>
       </c>
       <c r="AE20" s="1" t="s">
         <v>159</v>
@@ -5159,15 +5159,15 @@
       </c>
       <c r="J21" s="2">
         <f>IF(COUNT('Turns'!D65,'Turns'!D81)=2,SUM('Turns'!D65,'Turns'!D81),"Unknown")</f>
-        <v>1286.0</v>
+        <v>1285.0</v>
       </c>
       <c r="K21" s="2">
         <f>IF(COUNT('Turns'!E65,'Turns'!E81)=2,SUM('Turns'!E65,'Turns'!E81),"Unknown")</f>
-        <v>0.000224373564</v>
+        <v>0.00022522195</v>
       </c>
       <c r="L21" s="2">
         <f>IF(COUNT('Turns'!F65,'Turns'!F81)=2,SUM('Turns'!F65,'Turns'!F81),"Unknown")</f>
-        <v>0.0002572</v>
+        <v>0.000257</v>
       </c>
       <c r="M21" s="2">
         <f>IF(COUNT('Turns'!D64,'Turns'!D80)=2,SUM('Turns'!D64,'Turns'!D80),"Unknown")</f>
@@ -5192,35 +5192,35 @@
       </c>
       <c r="S21" s="2">
         <f>IF(COUNT('Turns'!D71,'Turns'!D86)=2,SUM('Turns'!D71,'Turns'!D86),"Unknown")</f>
-        <v>75.0</v>
+        <v>74.0</v>
       </c>
       <c r="T21" s="2">
         <f>IF(COUNT('Turns'!E71,'Turns'!E86)=2,SUM('Turns'!E71,'Turns'!E86),"Unknown")</f>
-        <v>7.85133e-05</v>
+        <v>7.781988e-05</v>
       </c>
       <c r="U21" s="2">
         <f>IF(COUNT('Turns'!F71,'Turns'!F86)=2,SUM('Turns'!F71,'Turns'!F86),"Unknown")</f>
-        <v>9e-05</v>
+        <v>8.88e-05</v>
       </c>
       <c r="V21" s="2">
         <f>IF(COUNT('Turns'!D70)=1,SUM('Turns'!D70),"Unknown")</f>
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="W21" s="2">
         <f>IF(COUNT('Turns'!E70)=1,SUM('Turns'!E70),"Unknown")</f>
-        <v>1.8843192e-05</v>
+        <v>1.998078e-05</v>
       </c>
       <c r="X21" s="2">
         <f>IF(COUNT('Turns'!F70)=1,SUM('Turns'!F70),"Unknown")</f>
-        <v>2.16e-05</v>
+        <v>2.28e-05</v>
       </c>
       <c r="Y21" s="2">
         <f>IF(COUNT('Turns'!E75,'Turns'!E90)=2,SUM('Turns'!E75,'Turns'!E90),"Unknown")</f>
-        <v>0.000321730056</v>
+        <v>0.00032302261</v>
       </c>
       <c r="Z21" s="2">
         <f>IF(COUNT('Turns'!F75,'Turns'!F90)=2,SUM('Turns'!F75,'Turns'!F90),"Unknown")</f>
-        <v>0.0003688</v>
+        <v>0.0003686</v>
       </c>
       <c r="AA21" s="5">
         <f>IF(ISNUMBER(Y21),ROUND(Y21*'Reference data'!$B$2,0),"Unknown")</f>
@@ -5231,7 +5231,7 @@
         <v>37.0</v>
       </c>
       <c r="AD21" s="1">
-        <v>5178.645</v>
+        <v>2411.401</v>
       </c>
       <c r="AE21" s="1" t="s">
         <v>159</v>
@@ -5264,15 +5264,15 @@
       </c>
       <c r="J22" s="2">
         <f>IF(COUNT('Turns'!D65,'Turns'!D81)=2,SUM('Turns'!D65,'Turns'!D81),"Unknown")</f>
-        <v>1286.0</v>
+        <v>1285.0</v>
       </c>
       <c r="K22" s="2">
         <f>IF(COUNT('Turns'!E65,'Turns'!E81)=2,SUM('Turns'!E65,'Turns'!E81),"Unknown")</f>
-        <v>0.000224373564</v>
+        <v>0.00022522195</v>
       </c>
       <c r="L22" s="2">
         <f>IF(COUNT('Turns'!F65,'Turns'!F81)=2,SUM('Turns'!F65,'Turns'!F81),"Unknown")</f>
-        <v>0.0002572</v>
+        <v>0.000257</v>
       </c>
       <c r="M22" s="2">
         <f>IF(COUNT('Turns'!D64,'Turns'!D80)=2,SUM('Turns'!D64,'Turns'!D80),"Unknown")</f>
@@ -5297,35 +5297,35 @@
       </c>
       <c r="S22" s="2">
         <f>IF(COUNT('Turns'!D71,'Turns'!D86)=2,SUM('Turns'!D71,'Turns'!D86),"Unknown")</f>
-        <v>75.0</v>
+        <v>74.0</v>
       </c>
       <c r="T22" s="2">
         <f>IF(COUNT('Turns'!E71,'Turns'!E86)=2,SUM('Turns'!E71,'Turns'!E86),"Unknown")</f>
-        <v>7.85133e-05</v>
+        <v>7.781988e-05</v>
       </c>
       <c r="U22" s="2">
         <f>IF(COUNT('Turns'!F71,'Turns'!F86)=2,SUM('Turns'!F71,'Turns'!F86),"Unknown")</f>
-        <v>9e-05</v>
+        <v>8.88e-05</v>
       </c>
       <c r="V22" s="2">
         <f>IF(COUNT('Turns'!D70)=1,SUM('Turns'!D70),"Unknown")</f>
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="W22" s="2">
         <f>IF(COUNT('Turns'!E70)=1,SUM('Turns'!E70),"Unknown")</f>
-        <v>1.8843192e-05</v>
+        <v>1.998078e-05</v>
       </c>
       <c r="X22" s="2">
         <f>IF(COUNT('Turns'!F70)=1,SUM('Turns'!F70),"Unknown")</f>
-        <v>2.16e-05</v>
+        <v>2.28e-05</v>
       </c>
       <c r="Y22" s="2">
         <f>IF(COUNT('Turns'!E75,'Turns'!E90)=2,SUM('Turns'!E75,'Turns'!E90),"Unknown")</f>
-        <v>0.000321730056</v>
+        <v>0.00032302261</v>
       </c>
       <c r="Z22" s="2">
         <f>IF(COUNT('Turns'!F75,'Turns'!F90)=2,SUM('Turns'!F75,'Turns'!F90),"Unknown")</f>
-        <v>0.0003688</v>
+        <v>0.0003686</v>
       </c>
       <c r="AA22" s="5">
         <f>IF(ISNUMBER(Y22),ROUND(Y22*'Reference data'!$B$2,0),"Unknown")</f>
@@ -5336,7 +5336,7 @@
         <v>37.0</v>
       </c>
       <c r="AD22" s="1">
-        <v>5176.686</v>
+        <v>2410.536</v>
       </c>
       <c r="AE22" s="1" t="s">
         <v>159</v>
@@ -5369,15 +5369,15 @@
       </c>
       <c r="J23" s="2">
         <f>IF(COUNT('Turns'!D65)=1,SUM('Turns'!D65),"Unknown")</f>
-        <v>603.0</v>
+        <v>602.0</v>
       </c>
       <c r="K23" s="2">
         <f>IF(COUNT('Turns'!E65)=1,SUM('Turns'!E65),"Unknown")</f>
-        <v>0.000105207822</v>
+        <v>0.00010551254</v>
       </c>
       <c r="L23" s="2">
         <f>IF(COUNT('Turns'!F65)=1,SUM('Turns'!F65),"Unknown")</f>
-        <v>0.0001206</v>
+        <v>0.0001204</v>
       </c>
       <c r="M23" s="2">
         <f>IF(COUNT('Turns'!D64)=1,SUM('Turns'!D64),"Unknown")</f>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="T23" s="2">
         <f>IF(COUNT('Turns'!E71)=1,SUM('Turns'!E71),"Unknown")</f>
-        <v>4.187376e-05</v>
+        <v>4.20648e-05</v>
       </c>
       <c r="U23" s="2">
         <f>IF(COUNT('Turns'!F71)=1,SUM('Turns'!F71),"Unknown")</f>
@@ -5414,23 +5414,23 @@
       </c>
       <c r="V23" s="2">
         <f>IF(COUNT('Turns'!D70)=1,SUM('Turns'!D70),"Unknown")</f>
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="W23" s="2">
         <f>IF(COUNT('Turns'!E70)=1,SUM('Turns'!E70),"Unknown")</f>
-        <v>1.8843192e-05</v>
+        <v>1.998078e-05</v>
       </c>
       <c r="X23" s="2">
         <f>IF(COUNT('Turns'!F70)=1,SUM('Turns'!F70),"Unknown")</f>
-        <v>2.16e-05</v>
+        <v>2.28e-05</v>
       </c>
       <c r="Y23" s="2">
         <f>IF(COUNT('Turns'!E75)=1,SUM('Turns'!E75),"Unknown")</f>
-        <v>0.000165924774</v>
+        <v>0.00016755812</v>
       </c>
       <c r="Z23" s="2">
         <f>IF(COUNT('Turns'!F75)=1,SUM('Turns'!F75),"Unknown")</f>
-        <v>0.0001902</v>
+        <v>0.0001912</v>
       </c>
       <c r="AA23" s="5">
         <f>IF(ISNUMBER(Y23),ROUND(Y23*'Reference data'!$B$2,0),"Unknown")</f>
@@ -5441,7 +5441,7 @@
         <v>19.0</v>
       </c>
       <c r="AD23" s="1">
-        <v>3118.554</v>
+        <v>1440.661</v>
       </c>
       <c r="AE23" s="1" t="s">
         <v>159</v>
@@ -5464,7 +5464,7 @@
         <v>111</v>
       </c>
       <c r="F24" s="1">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>171</v>
@@ -5477,15 +5477,15 @@
       </c>
       <c r="J24" s="2">
         <f>IF(COUNT('Turns'!D65)=1,SUM('Turns'!D65),"Unknown")</f>
-        <v>603.0</v>
+        <v>602.0</v>
       </c>
       <c r="K24" s="2">
         <f>IF(COUNT('Turns'!E65)=1,SUM('Turns'!E65),"Unknown")</f>
-        <v>0.000105207822</v>
+        <v>0.00010551254</v>
       </c>
       <c r="L24" s="2">
         <f>IF(COUNT('Turns'!F65)=1,SUM('Turns'!F65),"Unknown")</f>
-        <v>0.0001206</v>
+        <v>0.0001204</v>
       </c>
       <c r="M24" s="2">
         <f>IF(COUNT('Turns'!D64)=1,SUM('Turns'!D64),"Unknown")</f>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="T24" s="2">
         <f>IF(COUNT('Turns'!E71)=1,SUM('Turns'!E71),"Unknown")</f>
-        <v>4.187376e-05</v>
+        <v>4.20648e-05</v>
       </c>
       <c r="U24" s="2">
         <f>IF(COUNT('Turns'!F71)=1,SUM('Turns'!F71),"Unknown")</f>
@@ -5522,23 +5522,23 @@
       </c>
       <c r="V24" s="2">
         <f>IF(COUNT('Turns'!D70)=1,SUM('Turns'!D70),"Unknown")</f>
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="W24" s="2">
         <f>IF(COUNT('Turns'!E70)=1,SUM('Turns'!E70),"Unknown")</f>
-        <v>1.8843192e-05</v>
+        <v>1.998078e-05</v>
       </c>
       <c r="X24" s="2">
         <f>IF(COUNT('Turns'!F70)=1,SUM('Turns'!F70),"Unknown")</f>
-        <v>2.16e-05</v>
+        <v>2.28e-05</v>
       </c>
       <c r="Y24" s="2">
         <f>IF(COUNT('Turns'!E75)=1,SUM('Turns'!E75),"Unknown")</f>
-        <v>0.000165924774</v>
+        <v>0.00016755812</v>
       </c>
       <c r="Z24" s="2">
         <f>IF(COUNT('Turns'!F75)=1,SUM('Turns'!F75),"Unknown")</f>
-        <v>0.0001902</v>
+        <v>0.0001912</v>
       </c>
       <c r="AA24" s="5">
         <f>IF(ISNUMBER(Y24),ROUND(Y24*'Reference data'!$B$2,0),"Unknown")</f>
@@ -5552,7 +5552,7 @@
         <v>135</v>
       </c>
       <c r="AD24" s="1">
-        <v>3115.678</v>
+        <v>1439.134</v>
       </c>
       <c r="AE24" s="1" t="s">
         <v>172</v>
@@ -5584,7 +5584,7 @@
         <v>191</v>
       </c>
       <c r="AD25" s="1">
-        <v>3.727</v>
+        <v>1.593</v>
       </c>
       <c r="AE25" s="1" t="s">
         <v>176</v>
@@ -5616,7 +5616,7 @@
         <v>193</v>
       </c>
       <c r="AD26" s="1">
-        <v>1.037</v>
+        <v>0.407</v>
       </c>
       <c r="AE26" s="1" t="s">
         <v>176</v>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="K27" s="2">
         <f>IF(COUNT('Turns'!E81)=1,SUM('Turns'!E81),"Unknown")</f>
-        <v>0.000119165742</v>
+        <v>0.00011970941</v>
       </c>
       <c r="L27" s="2">
         <f>IF(COUNT('Turns'!F81)=1,SUM('Turns'!F81),"Unknown")</f>
@@ -5682,15 +5682,15 @@
       </c>
       <c r="S27" s="2">
         <f>IF(COUNT('Turns'!D86)=1,SUM('Turns'!D86),"Unknown")</f>
-        <v>35.0</v>
+        <v>34.0</v>
       </c>
       <c r="T27" s="2">
         <f>IF(COUNT('Turns'!E86)=1,SUM('Turns'!E86),"Unknown")</f>
-        <v>3.663954e-05</v>
+        <v>3.575508e-05</v>
       </c>
       <c r="U27" s="2">
         <f>IF(COUNT('Turns'!F86)=1,SUM('Turns'!F86),"Unknown")</f>
-        <v>4.2e-05</v>
+        <v>4.08e-05</v>
       </c>
       <c r="V27" s="2">
         <v>0</v>
@@ -5703,11 +5703,11 @@
       </c>
       <c r="Y27" s="2">
         <f>IF(COUNT('Turns'!E90)=1,SUM('Turns'!E90),"Unknown")</f>
-        <v>0.000155805282</v>
+        <v>0.00015546449</v>
       </c>
       <c r="Z27" s="2">
         <f>IF(COUNT('Turns'!F90)=1,SUM('Turns'!F90),"Unknown")</f>
-        <v>0.0001786</v>
+        <v>0.0001774</v>
       </c>
       <c r="AA27" s="5">
         <f>IF(ISNUMBER(Y27),ROUND(Y27*'Reference data'!$B$2,0),"Unknown")</f>
@@ -5718,7 +5718,7 @@
         <v>18.0</v>
       </c>
       <c r="AD27" s="1">
-        <v>2048.263</v>
+        <v>965.13</v>
       </c>
       <c r="AE27" s="1" t="s">
         <v>159</v>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="K28" s="2">
         <f>IF(COUNT('Turns'!E81)=1,SUM('Turns'!E81),"Unknown")</f>
-        <v>0.000119165742</v>
+        <v>0.00011970941</v>
       </c>
       <c r="L28" s="2">
         <f>IF(COUNT('Turns'!F81)=1,SUM('Turns'!F81),"Unknown")</f>
@@ -5787,15 +5787,15 @@
       </c>
       <c r="S28" s="2">
         <f>IF(COUNT('Turns'!D86)=1,SUM('Turns'!D86),"Unknown")</f>
-        <v>35.0</v>
+        <v>34.0</v>
       </c>
       <c r="T28" s="2">
         <f>IF(COUNT('Turns'!E86)=1,SUM('Turns'!E86),"Unknown")</f>
-        <v>3.663954e-05</v>
+        <v>3.575508e-05</v>
       </c>
       <c r="U28" s="2">
         <f>IF(COUNT('Turns'!F86)=1,SUM('Turns'!F86),"Unknown")</f>
-        <v>4.2e-05</v>
+        <v>4.08e-05</v>
       </c>
       <c r="V28" s="2">
         <v>0</v>
@@ -5808,11 +5808,11 @@
       </c>
       <c r="Y28" s="2">
         <f>IF(COUNT('Turns'!E90)=1,SUM('Turns'!E90),"Unknown")</f>
-        <v>0.000155805282</v>
+        <v>0.00015546449</v>
       </c>
       <c r="Z28" s="2">
         <f>IF(COUNT('Turns'!F90)=1,SUM('Turns'!F90),"Unknown")</f>
-        <v>0.0001786</v>
+        <v>0.0001774</v>
       </c>
       <c r="AA28" s="5">
         <f>IF(ISNUMBER(Y28),ROUND(Y28*'Reference data'!$B$2,0),"Unknown")</f>
@@ -5826,7 +5826,7 @@
         <v>143</v>
       </c>
       <c r="AD28" s="1">
-        <v>2045.756</v>
+        <v>963.926</v>
       </c>
       <c r="AE28" s="1" t="s">
         <v>172</v>
@@ -5856,15 +5856,15 @@
       </c>
       <c r="J29" s="2">
         <f>IF(COUNT('Turns'!D94)=1,SUM('Turns'!D94),"Unknown")</f>
-        <v>732.0</v>
+        <v>731.0</v>
       </c>
       <c r="K29" s="2">
         <f>IF(COUNT('Turns'!E94)=1,SUM('Turns'!E94),"Unknown")</f>
-        <v>0.000127714968</v>
+        <v>0.00012812237</v>
       </c>
       <c r="L29" s="2">
         <f>IF(COUNT('Turns'!F94)=1,SUM('Turns'!F94),"Unknown")</f>
-        <v>0.0001464</v>
+        <v>0.0001462</v>
       </c>
       <c r="M29" s="2">
         <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="T29" s="2">
         <f>IF(COUNT('Turns'!E100)=1,SUM('Turns'!E100),"Unknown")</f>
-        <v>2.3030568e-05</v>
+        <v>2.313564e-05</v>
       </c>
       <c r="U29" s="2">
         <f>IF(COUNT('Turns'!F100)=1,SUM('Turns'!F100),"Unknown")</f>
@@ -5901,23 +5901,23 @@
       </c>
       <c r="V29" s="2">
         <f>IF(COUNT('Turns'!D99)=1,SUM('Turns'!D99),"Unknown")</f>
-        <v>22.0</v>
+        <v>17.0</v>
       </c>
       <c r="W29" s="2">
         <f>IF(COUNT('Turns'!E99)=1,SUM('Turns'!E99),"Unknown")</f>
-        <v>2.3030568e-05</v>
+        <v>1.787754e-05</v>
       </c>
       <c r="X29" s="2">
         <f>IF(COUNT('Turns'!F99)=1,SUM('Turns'!F99),"Unknown")</f>
-        <v>2.64e-05</v>
+        <v>2.04e-05</v>
       </c>
       <c r="Y29" s="2">
         <f>IF(COUNT('Turns'!E104)=1,SUM('Turns'!E104),"Unknown")</f>
-        <v>0.000173776104</v>
+        <v>0.00016913555</v>
       </c>
       <c r="Z29" s="2">
         <f>IF(COUNT('Turns'!F104)=1,SUM('Turns'!F104),"Unknown")</f>
-        <v>0.0001992</v>
+        <v>0.000193</v>
       </c>
       <c r="AA29" s="5">
         <f>IF(ISNUMBER(Y29),ROUND(Y29*'Reference data'!$B$2,0),"Unknown")</f>
@@ -5925,10 +5925,10 @@
       </c>
       <c r="AB29" s="5">
         <f>IF(ISNUMBER(Z29),ROUND(Z29*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="AD29" s="1">
-        <v>1449.498</v>
+        <v>3742.393</v>
       </c>
       <c r="AE29" s="1" t="s">
         <v>159</v>
@@ -5961,15 +5961,15 @@
       </c>
       <c r="J30" s="2">
         <f>IF(COUNT('Turns'!D94)=1,SUM('Turns'!D94),"Unknown")</f>
-        <v>732.0</v>
+        <v>731.0</v>
       </c>
       <c r="K30" s="2">
         <f>IF(COUNT('Turns'!E94)=1,SUM('Turns'!E94),"Unknown")</f>
-        <v>0.000127714968</v>
+        <v>0.00012812237</v>
       </c>
       <c r="L30" s="2">
         <f>IF(COUNT('Turns'!F94)=1,SUM('Turns'!F94),"Unknown")</f>
-        <v>0.0001464</v>
+        <v>0.0001462</v>
       </c>
       <c r="M30" s="2">
         <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
@@ -5998,7 +5998,7 @@
       </c>
       <c r="T30" s="2">
         <f>IF(COUNT('Turns'!E100)=1,SUM('Turns'!E100),"Unknown")</f>
-        <v>2.3030568e-05</v>
+        <v>2.313564e-05</v>
       </c>
       <c r="U30" s="2">
         <f>IF(COUNT('Turns'!F100)=1,SUM('Turns'!F100),"Unknown")</f>
@@ -6006,23 +6006,23 @@
       </c>
       <c r="V30" s="2">
         <f>IF(COUNT('Turns'!D99)=1,SUM('Turns'!D99),"Unknown")</f>
-        <v>22.0</v>
+        <v>17.0</v>
       </c>
       <c r="W30" s="2">
         <f>IF(COUNT('Turns'!E99)=1,SUM('Turns'!E99),"Unknown")</f>
-        <v>2.3030568e-05</v>
+        <v>1.787754e-05</v>
       </c>
       <c r="X30" s="2">
         <f>IF(COUNT('Turns'!F99)=1,SUM('Turns'!F99),"Unknown")</f>
-        <v>2.64e-05</v>
+        <v>2.04e-05</v>
       </c>
       <c r="Y30" s="2">
         <f>IF(COUNT('Turns'!E104)=1,SUM('Turns'!E104),"Unknown")</f>
-        <v>0.000173776104</v>
+        <v>0.00016913555</v>
       </c>
       <c r="Z30" s="2">
         <f>IF(COUNT('Turns'!F104)=1,SUM('Turns'!F104),"Unknown")</f>
-        <v>0.0001992</v>
+        <v>0.000193</v>
       </c>
       <c r="AA30" s="5">
         <f>IF(ISNUMBER(Y30),ROUND(Y30*'Reference data'!$B$2,0),"Unknown")</f>
@@ -6030,10 +6030,10 @@
       </c>
       <c r="AB30" s="5">
         <f>IF(ISNUMBER(Z30),ROUND(Z30*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="AD30" s="1">
-        <v>1447.526</v>
+        <v>3740.46</v>
       </c>
       <c r="AE30" s="1" t="s">
         <v>159</v>
@@ -6066,15 +6066,15 @@
       </c>
       <c r="J31" s="2">
         <f>IF(COUNT('Turns'!D94)=1,SUM('Turns'!D94),"Unknown")</f>
-        <v>732.0</v>
+        <v>731.0</v>
       </c>
       <c r="K31" s="2">
         <f>IF(COUNT('Turns'!E94)=1,SUM('Turns'!E94),"Unknown")</f>
-        <v>0.000127714968</v>
+        <v>0.00012812237</v>
       </c>
       <c r="L31" s="2">
         <f>IF(COUNT('Turns'!F94)=1,SUM('Turns'!F94),"Unknown")</f>
-        <v>0.0001464</v>
+        <v>0.0001462</v>
       </c>
       <c r="M31" s="2">
         <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="T31" s="2">
         <f>IF(COUNT('Turns'!E100)=1,SUM('Turns'!E100),"Unknown")</f>
-        <v>2.3030568e-05</v>
+        <v>2.313564e-05</v>
       </c>
       <c r="U31" s="2">
         <f>IF(COUNT('Turns'!F100)=1,SUM('Turns'!F100),"Unknown")</f>
@@ -6111,23 +6111,23 @@
       </c>
       <c r="V31" s="2">
         <f>IF(COUNT('Turns'!D99)=1,SUM('Turns'!D99),"Unknown")</f>
-        <v>22.0</v>
+        <v>17.0</v>
       </c>
       <c r="W31" s="2">
         <f>IF(COUNT('Turns'!E99)=1,SUM('Turns'!E99),"Unknown")</f>
-        <v>2.3030568e-05</v>
+        <v>1.787754e-05</v>
       </c>
       <c r="X31" s="2">
         <f>IF(COUNT('Turns'!F99)=1,SUM('Turns'!F99),"Unknown")</f>
-        <v>2.64e-05</v>
+        <v>2.04e-05</v>
       </c>
       <c r="Y31" s="2">
         <f>IF(COUNT('Turns'!E104)=1,SUM('Turns'!E104),"Unknown")</f>
-        <v>0.000173776104</v>
+        <v>0.00016913555</v>
       </c>
       <c r="Z31" s="2">
         <f>IF(COUNT('Turns'!F104)=1,SUM('Turns'!F104),"Unknown")</f>
-        <v>0.0001992</v>
+        <v>0.000193</v>
       </c>
       <c r="AA31" s="5">
         <f>IF(ISNUMBER(Y31),ROUND(Y31*'Reference data'!$B$2,0),"Unknown")</f>
@@ -6135,10 +6135,10 @@
       </c>
       <c r="AB31" s="5">
         <f>IF(ISNUMBER(Z31),ROUND(Z31*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="AD31" s="1">
-        <v>1446.481</v>
+        <v>3739.662</v>
       </c>
       <c r="AE31" s="1" t="s">
         <v>159</v>
@@ -6171,15 +6171,15 @@
       </c>
       <c r="J32" s="2">
         <f>IF(COUNT('Turns'!D94)=1,SUM('Turns'!D94),"Unknown")</f>
-        <v>732.0</v>
+        <v>731.0</v>
       </c>
       <c r="K32" s="2">
         <f>IF(COUNT('Turns'!E94)=1,SUM('Turns'!E94),"Unknown")</f>
-        <v>0.000127714968</v>
+        <v>0.00012812237</v>
       </c>
       <c r="L32" s="2">
         <f>IF(COUNT('Turns'!F94)=1,SUM('Turns'!F94),"Unknown")</f>
-        <v>0.0001464</v>
+        <v>0.0001462</v>
       </c>
       <c r="M32" s="2">
         <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="T32" s="2">
         <f>IF(COUNT('Turns'!E100)=1,SUM('Turns'!E100),"Unknown")</f>
-        <v>2.3030568e-05</v>
+        <v>2.313564e-05</v>
       </c>
       <c r="U32" s="2">
         <f>IF(COUNT('Turns'!F100)=1,SUM('Turns'!F100),"Unknown")</f>
@@ -6216,23 +6216,23 @@
       </c>
       <c r="V32" s="2">
         <f>IF(COUNT('Turns'!D99)=1,SUM('Turns'!D99),"Unknown")</f>
-        <v>22.0</v>
+        <v>17.0</v>
       </c>
       <c r="W32" s="2">
         <f>IF(COUNT('Turns'!E99)=1,SUM('Turns'!E99),"Unknown")</f>
-        <v>2.3030568e-05</v>
+        <v>1.787754e-05</v>
       </c>
       <c r="X32" s="2">
         <f>IF(COUNT('Turns'!F99)=1,SUM('Turns'!F99),"Unknown")</f>
-        <v>2.64e-05</v>
+        <v>2.04e-05</v>
       </c>
       <c r="Y32" s="2">
         <f>IF(COUNT('Turns'!E104)=1,SUM('Turns'!E104),"Unknown")</f>
-        <v>0.000173776104</v>
+        <v>0.00016913555</v>
       </c>
       <c r="Z32" s="2">
         <f>IF(COUNT('Turns'!F104)=1,SUM('Turns'!F104),"Unknown")</f>
-        <v>0.0001992</v>
+        <v>0.000193</v>
       </c>
       <c r="AA32" s="5">
         <f>IF(ISNUMBER(Y32),ROUND(Y32*'Reference data'!$B$2,0),"Unknown")</f>
@@ -6240,10 +6240,10 @@
       </c>
       <c r="AB32" s="5">
         <f>IF(ISNUMBER(Z32),ROUND(Z32*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="AD32" s="1">
-        <v>1443.792</v>
+        <v>3737.865</v>
       </c>
       <c r="AE32" s="1" t="s">
         <v>159</v>
@@ -6266,7 +6266,7 @@
         <v>111</v>
       </c>
       <c r="F33" s="1">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>171</v>
@@ -6279,15 +6279,15 @@
       </c>
       <c r="J33" s="2">
         <f>IF(COUNT('Turns'!D94)=1,SUM('Turns'!D94),"Unknown")</f>
-        <v>732.0</v>
+        <v>731.0</v>
       </c>
       <c r="K33" s="2">
         <f>IF(COUNT('Turns'!E94)=1,SUM('Turns'!E94),"Unknown")</f>
-        <v>0.000127714968</v>
+        <v>0.00012812237</v>
       </c>
       <c r="L33" s="2">
         <f>IF(COUNT('Turns'!F94)=1,SUM('Turns'!F94),"Unknown")</f>
-        <v>0.0001464</v>
+        <v>0.0001462</v>
       </c>
       <c r="M33" s="2">
         <f>IF(COUNT('Turns'!D93)=1,SUM('Turns'!D93),"Unknown")</f>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="T33" s="2">
         <f>IF(COUNT('Turns'!E100)=1,SUM('Turns'!E100),"Unknown")</f>
-        <v>2.3030568e-05</v>
+        <v>2.313564e-05</v>
       </c>
       <c r="U33" s="2">
         <f>IF(COUNT('Turns'!F100)=1,SUM('Turns'!F100),"Unknown")</f>
@@ -6324,23 +6324,23 @@
       </c>
       <c r="V33" s="2">
         <f>IF(COUNT('Turns'!D99)=1,SUM('Turns'!D99),"Unknown")</f>
-        <v>22.0</v>
+        <v>17.0</v>
       </c>
       <c r="W33" s="2">
         <f>IF(COUNT('Turns'!E99)=1,SUM('Turns'!E99),"Unknown")</f>
-        <v>2.3030568e-05</v>
+        <v>1.787754e-05</v>
       </c>
       <c r="X33" s="2">
         <f>IF(COUNT('Turns'!F99)=1,SUM('Turns'!F99),"Unknown")</f>
-        <v>2.64e-05</v>
+        <v>2.04e-05</v>
       </c>
       <c r="Y33" s="2">
         <f>IF(COUNT('Turns'!E104)=1,SUM('Turns'!E104),"Unknown")</f>
-        <v>0.000173776104</v>
+        <v>0.00016913555</v>
       </c>
       <c r="Z33" s="2">
         <f>IF(COUNT('Turns'!F104)=1,SUM('Turns'!F104),"Unknown")</f>
-        <v>0.0001992</v>
+        <v>0.000193</v>
       </c>
       <c r="AA33" s="5">
         <f>IF(ISNUMBER(Y33),ROUND(Y33*'Reference data'!$B$2,0),"Unknown")</f>
@@ -6348,13 +6348,13 @@
       </c>
       <c r="AB33" s="5">
         <f>IF(ISNUMBER(Z33),ROUND(Z33*'Reference data'!$B$2,0),"Unknown")</f>
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="AC33" s="1" t="s">
         <v>147</v>
       </c>
       <c r="AD33" s="1">
-        <v>1441.526</v>
+        <v>3736.307</v>
       </c>
       <c r="AE33" s="1" t="s">
         <v>172</v>
@@ -6384,15 +6384,15 @@
       </c>
       <c r="J34" s="2">
         <f>IF(COUNT('Turns'!D108)=1,SUM('Turns'!D108),"Unknown")</f>
-        <v>801.0</v>
+        <v>795.0</v>
       </c>
       <c r="K34" s="2">
         <f>IF(COUNT('Turns'!E108)=1,SUM('Turns'!E108),"Unknown")</f>
-        <v>0.000139753674</v>
+        <v>0.00013933965</v>
       </c>
       <c r="L34" s="2">
         <f>IF(COUNT('Turns'!F108)=1,SUM('Turns'!F108),"Unknown")</f>
-        <v>0.0001602</v>
+        <v>0.000159</v>
       </c>
       <c r="M34" s="2">
         <f>IF(COUNT('Turns'!D107)=1,SUM('Turns'!D107),"Unknown")</f>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="T34" s="2">
         <f>IF(COUNT('Turns'!E114)=1,SUM('Turns'!E114),"Unknown")</f>
-        <v>3.0358476e-05</v>
+        <v>3.049698e-05</v>
       </c>
       <c r="U34" s="2">
         <f>IF(COUNT('Turns'!F114)=1,SUM('Turns'!F114),"Unknown")</f>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="W34" s="2">
         <f>IF(COUNT('Turns'!E113)=1,SUM('Turns'!E113),"Unknown")</f>
-        <v>4.9201668e-05</v>
+        <v>4.942614e-05</v>
       </c>
       <c r="X34" s="2">
         <f>IF(COUNT('Turns'!F113)=1,SUM('Turns'!F113),"Unknown")</f>
@@ -6441,11 +6441,11 @@
       </c>
       <c r="Y34" s="2">
         <f>IF(COUNT('Turns'!E118)=1,SUM('Turns'!E118),"Unknown")</f>
-        <v>0.000219313818</v>
+        <v>0.00021926277</v>
       </c>
       <c r="Z34" s="2">
         <f>IF(COUNT('Turns'!F118)=1,SUM('Turns'!F118),"Unknown")</f>
-        <v>0.0002514</v>
+        <v>0.0002502</v>
       </c>
       <c r="AA34" s="5">
         <f>IF(ISNUMBER(Y34),ROUND(Y34*'Reference data'!$B$2,0),"Unknown")</f>
@@ -6456,7 +6456,7 @@
         <v>25.0</v>
       </c>
       <c r="AD34" s="1">
-        <v>1427.932</v>
+        <v>1583.076</v>
       </c>
       <c r="AE34" s="1" t="s">
         <v>159</v>
@@ -6489,15 +6489,15 @@
       </c>
       <c r="J35" s="2">
         <f>IF(COUNT('Turns'!D108)=1,SUM('Turns'!D108),"Unknown")</f>
-        <v>801.0</v>
+        <v>795.0</v>
       </c>
       <c r="K35" s="2">
         <f>IF(COUNT('Turns'!E108)=1,SUM('Turns'!E108),"Unknown")</f>
-        <v>0.000139753674</v>
+        <v>0.00013933965</v>
       </c>
       <c r="L35" s="2">
         <f>IF(COUNT('Turns'!F108)=1,SUM('Turns'!F108),"Unknown")</f>
-        <v>0.0001602</v>
+        <v>0.000159</v>
       </c>
       <c r="M35" s="2">
         <f>IF(COUNT('Turns'!D107)=1,SUM('Turns'!D107),"Unknown")</f>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="T35" s="2">
         <f>IF(COUNT('Turns'!E114)=1,SUM('Turns'!E114),"Unknown")</f>
-        <v>3.0358476e-05</v>
+        <v>3.049698e-05</v>
       </c>
       <c r="U35" s="2">
         <f>IF(COUNT('Turns'!F114)=1,SUM('Turns'!F114),"Unknown")</f>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="W35" s="2">
         <f>IF(COUNT('Turns'!E113)=1,SUM('Turns'!E113),"Unknown")</f>
-        <v>4.9201668e-05</v>
+        <v>4.942614e-05</v>
       </c>
       <c r="X35" s="2">
         <f>IF(COUNT('Turns'!F113)=1,SUM('Turns'!F113),"Unknown")</f>
@@ -6546,11 +6546,11 @@
       </c>
       <c r="Y35" s="2">
         <f>IF(COUNT('Turns'!E118)=1,SUM('Turns'!E118),"Unknown")</f>
-        <v>0.000219313818</v>
+        <v>0.00021926277</v>
       </c>
       <c r="Z35" s="2">
         <f>IF(COUNT('Turns'!F118)=1,SUM('Turns'!F118),"Unknown")</f>
-        <v>0.0002514</v>
+        <v>0.0002502</v>
       </c>
       <c r="AA35" s="5">
         <f>IF(ISNUMBER(Y35),ROUND(Y35*'Reference data'!$B$2,0),"Unknown")</f>
@@ -6561,7 +6561,7 @@
         <v>25.0</v>
       </c>
       <c r="AD35" s="1">
-        <v>1426.061</v>
+        <v>1579.203</v>
       </c>
       <c r="AE35" s="1" t="s">
         <v>159</v>
@@ -6594,15 +6594,15 @@
       </c>
       <c r="J36" s="2">
         <f>IF(COUNT('Turns'!D108)=1,SUM('Turns'!D108),"Unknown")</f>
-        <v>801.0</v>
+        <v>795.0</v>
       </c>
       <c r="K36" s="2">
         <f>IF(COUNT('Turns'!E108)=1,SUM('Turns'!E108),"Unknown")</f>
-        <v>0.000139753674</v>
+        <v>0.00013933965</v>
       </c>
       <c r="L36" s="2">
         <f>IF(COUNT('Turns'!F108)=1,SUM('Turns'!F108),"Unknown")</f>
-        <v>0.0001602</v>
+        <v>0.000159</v>
       </c>
       <c r="M36" s="2">
         <f>IF(COUNT('Turns'!D107)=1,SUM('Turns'!D107),"Unknown")</f>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="T36" s="2">
         <f>IF(COUNT('Turns'!E114)=1,SUM('Turns'!E114),"Unknown")</f>
-        <v>3.0358476e-05</v>
+        <v>3.049698e-05</v>
       </c>
       <c r="U36" s="2">
         <f>IF(COUNT('Turns'!F114)=1,SUM('Turns'!F114),"Unknown")</f>
@@ -6643,7 +6643,7 @@
       </c>
       <c r="W36" s="2">
         <f>IF(COUNT('Turns'!E113)=1,SUM('Turns'!E113),"Unknown")</f>
-        <v>4.9201668e-05</v>
+        <v>4.942614e-05</v>
       </c>
       <c r="X36" s="2">
         <f>IF(COUNT('Turns'!F113)=1,SUM('Turns'!F113),"Unknown")</f>
@@ -6651,11 +6651,11 @@
       </c>
       <c r="Y36" s="2">
         <f>IF(COUNT('Turns'!E118)=1,SUM('Turns'!E118),"Unknown")</f>
-        <v>0.000219313818</v>
+        <v>0.00021926277</v>
       </c>
       <c r="Z36" s="2">
         <f>IF(COUNT('Turns'!F118)=1,SUM('Turns'!F118),"Unknown")</f>
-        <v>0.0002514</v>
+        <v>0.0002502</v>
       </c>
       <c r="AA36" s="5">
         <f>IF(ISNUMBER(Y36),ROUND(Y36*'Reference data'!$B$2,0),"Unknown")</f>
@@ -6666,7 +6666,7 @@
         <v>25.0</v>
       </c>
       <c r="AD36" s="1">
-        <v>1425.191</v>
+        <v>1577.497</v>
       </c>
       <c r="AE36" s="1" t="s">
         <v>159</v>
@@ -6699,15 +6699,15 @@
       </c>
       <c r="J37" s="2">
         <f>IF(COUNT('Turns'!D108)=1,SUM('Turns'!D108),"Unknown")</f>
-        <v>801.0</v>
+        <v>795.0</v>
       </c>
       <c r="K37" s="2">
         <f>IF(COUNT('Turns'!E108)=1,SUM('Turns'!E108),"Unknown")</f>
-        <v>0.000139753674</v>
+        <v>0.00013933965</v>
       </c>
       <c r="L37" s="2">
         <f>IF(COUNT('Turns'!F108)=1,SUM('Turns'!F108),"Unknown")</f>
-        <v>0.0001602</v>
+        <v>0.000159</v>
       </c>
       <c r="M37" s="2">
         <f>IF(COUNT('Turns'!D107)=1,SUM('Turns'!D107),"Unknown")</f>
@@ -6736,7 +6736,7 @@
       </c>
       <c r="T37" s="2">
         <f>IF(COUNT('Turns'!E114)=1,SUM('Turns'!E114),"Unknown")</f>
-        <v>3.0358476e-05</v>
+        <v>3.049698e-05</v>
       </c>
       <c r="U37" s="2">
         <f>IF(COUNT('Turns'!F114)=1,SUM('Turns'!F114),"Unknown")</f>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="W37" s="2">
         <f>IF(COUNT('Turns'!E113)=1,SUM('Turns'!E113),"Unknown")</f>
-        <v>4.9201668e-05</v>
+        <v>4.942614e-05</v>
       </c>
       <c r="X37" s="2">
         <f>IF(COUNT('Turns'!F113)=1,SUM('Turns'!F113),"Unknown")</f>
@@ -6756,11 +6756,11 @@
       </c>
       <c r="Y37" s="2">
         <f>IF(COUNT('Turns'!E118)=1,SUM('Turns'!E118),"Unknown")</f>
-        <v>0.000219313818</v>
+        <v>0.00021926277</v>
       </c>
       <c r="Z37" s="2">
         <f>IF(COUNT('Turns'!F118)=1,SUM('Turns'!F118),"Unknown")</f>
-        <v>0.0002514</v>
+        <v>0.0002502</v>
       </c>
       <c r="AA37" s="5">
         <f>IF(ISNUMBER(Y37),ROUND(Y37*'Reference data'!$B$2,0),"Unknown")</f>
@@ -6771,7 +6771,7 @@
         <v>25.0</v>
       </c>
       <c r="AD37" s="1">
-        <v>1423.234</v>
+        <v>1574.343</v>
       </c>
       <c r="AE37" s="1" t="s">
         <v>159</v>
@@ -6794,7 +6794,7 @@
         <v>111</v>
       </c>
       <c r="F38" s="1">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>171</v>
@@ -6807,15 +6807,15 @@
       </c>
       <c r="J38" s="2">
         <f>IF(COUNT('Turns'!D108)=1,SUM('Turns'!D108),"Unknown")</f>
-        <v>801.0</v>
+        <v>795.0</v>
       </c>
       <c r="K38" s="2">
         <f>IF(COUNT('Turns'!E108)=1,SUM('Turns'!E108),"Unknown")</f>
-        <v>0.000139753674</v>
+        <v>0.00013933965</v>
       </c>
       <c r="L38" s="2">
         <f>IF(COUNT('Turns'!F108)=1,SUM('Turns'!F108),"Unknown")</f>
-        <v>0.0001602</v>
+        <v>0.000159</v>
       </c>
       <c r="M38" s="2">
         <f>IF(COUNT('Turns'!D107)=1,SUM('Turns'!D107),"Unknown")</f>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="T38" s="2">
         <f>IF(COUNT('Turns'!E114)=1,SUM('Turns'!E114),"Unknown")</f>
-        <v>3.0358476e-05</v>
+        <v>3.049698e-05</v>
       </c>
       <c r="U38" s="2">
         <f>IF(COUNT('Turns'!F114)=1,SUM('Turns'!F114),"Unknown")</f>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="W38" s="2">
         <f>IF(COUNT('Turns'!E113)=1,SUM('Turns'!E113),"Unknown")</f>
-        <v>4.9201668e-05</v>
+        <v>4.942614e-05</v>
       </c>
       <c r="X38" s="2">
         <f>IF(COUNT('Turns'!F113)=1,SUM('Turns'!F113),"Unknown")</f>
@@ -6864,11 +6864,11 @@
       </c>
       <c r="Y38" s="2">
         <f>IF(COUNT('Turns'!E118)=1,SUM('Turns'!E118),"Unknown")</f>
-        <v>0.000219313818</v>
+        <v>0.00021926277</v>
       </c>
       <c r="Z38" s="2">
         <f>IF(COUNT('Turns'!F118)=1,SUM('Turns'!F118),"Unknown")</f>
-        <v>0.0002514</v>
+        <v>0.0002502</v>
       </c>
       <c r="AA38" s="5">
         <f>IF(ISNUMBER(Y38),ROUND(Y38*'Reference data'!$B$2,0),"Unknown")</f>
@@ -6882,7 +6882,7 @@
         <v>152</v>
       </c>
       <c r="AD38" s="1">
-        <v>1421.315</v>
+        <v>1571.863</v>
       </c>
       <c r="AE38" s="1" t="s">
         <v>172</v>
@@ -6940,7 +6940,7 @@
         <v>43</v>
       </c>
       <c r="B3" s="2">
-        <v>0.87237</v>
+        <v>0.87635</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>44</v>
